--- a/database/event/5607/event_5607_evp_summary.xlsx
+++ b/database/event/5607/event_5607_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1843</v>
+        <v>8.1717</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6791</v>
+        <v>2.6749</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8849</v>
+        <v>2.8117</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1843</v>
+        <v>8.1717</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6841</v>
+        <v>1.6715</v>
       </c>
       <c r="G2" t="n">
         <v>6.5002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6841</v>
+        <v>1.6715</v>
       </c>
       <c r="I2" t="n">
         <v>1.6998</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8119</v>
+        <v>7.7992</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5572</v>
+        <v>2.553</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7345</v>
+        <v>2.6633</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8119</v>
+        <v>7.7992</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7052</v>
+        <v>1.6925</v>
       </c>
       <c r="G3" t="n">
         <v>6.1067</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7052</v>
+        <v>1.6925</v>
       </c>
       <c r="I3" t="n">
         <v>1.7211</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5679</v>
+        <v>7.5393</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4773</v>
+        <v>2.4679</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6359</v>
+        <v>2.5597</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5679</v>
+        <v>7.5393</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5584</v>
+        <v>2.5299</v>
       </c>
       <c r="G4" t="n">
         <v>5.0095</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5584</v>
+        <v>2.5299</v>
       </c>
       <c r="I4" t="n">
         <v>2.5943</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8387</v>
+        <v>6.8259</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2386</v>
+        <v>2.2344</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3413</v>
+        <v>2.2755</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8387</v>
+        <v>6.8259</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7184</v>
+        <v>1.7056</v>
       </c>
       <c r="G5" t="n">
         <v>5.1203</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7184</v>
+        <v>1.7056</v>
       </c>
       <c r="I5" t="n">
         <v>1.7344</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8666</v>
+        <v>5.8537</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9204</v>
+        <v>1.9162</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9486</v>
+        <v>1.8882</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8666</v>
+        <v>5.8537</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7429</v>
+        <v>1.73</v>
       </c>
       <c r="G6" t="n">
         <v>4.1237</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7429</v>
+        <v>1.73</v>
       </c>
       <c r="I6" t="n">
         <v>1.7592</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9361</v>
+        <v>4.9251</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6158</v>
+        <v>1.6122</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5727</v>
+        <v>1.5183</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9361</v>
+        <v>4.9251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9799</v>
+        <v>0.9689</v>
       </c>
       <c r="G7" t="n">
         <v>3.9562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9799</v>
+        <v>0.9689</v>
       </c>
       <c r="I7" t="n">
         <v>0.9936</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.312</v>
+        <v>2.3033</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7568</v>
+        <v>0.754</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4737</v>
       </c>
       <c r="E8" t="n">
-        <v>2.312</v>
+        <v>2.3033</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1597</v>
+        <v>1.151</v>
       </c>
       <c r="G8" t="n">
         <v>1.1523</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1597</v>
+        <v>1.151</v>
       </c>
       <c r="I8" t="n">
         <v>1.1705</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.204</v>
+        <v>2.1913</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7215</v>
+        <v>0.7173</v>
       </c>
       <c r="D9" t="n">
-        <v>0.469</v>
+        <v>0.4291</v>
       </c>
       <c r="E9" t="n">
-        <v>2.204</v>
+        <v>2.1913</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7045</v>
+        <v>1.6918</v>
       </c>
       <c r="G9" t="n">
         <v>0.4995</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7045</v>
+        <v>1.6918</v>
       </c>
       <c r="I9" t="n">
         <v>1.7204</v>
@@ -870,7 +870,7 @@
         <v>0.6878</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4275</v>
+        <v>0.3932</v>
       </c>
       <c r="E10" t="n">
         <v>2.1013</v>
@@ -916,7 +916,7 @@
         <v>0.5992</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3182</v>
+        <v>0.2854</v>
       </c>
       <c r="E11" t="n">
         <v>1.8306</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7868</v>
+        <v>1.7813</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5849</v>
+        <v>0.5831</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3005</v>
+        <v>0.2658</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7868</v>
+        <v>1.7813</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7458</v>
+        <v>0.7403</v>
       </c>
       <c r="G12" t="n">
         <v>1.041</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7458</v>
+        <v>0.7403</v>
       </c>
       <c r="I12" t="n">
         <v>0.7528</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7536</v>
+        <v>1.7406</v>
       </c>
       <c r="C13" t="n">
-        <v>0.574</v>
+        <v>0.5698</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2871</v>
+        <v>0.2495</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7536</v>
+        <v>1.7406</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7474</v>
+        <v>1.7344</v>
       </c>
       <c r="G13" t="n">
         <v>0.0062</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7474</v>
+        <v>1.7344</v>
       </c>
       <c r="I13" t="n">
         <v>1.7637</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7437</v>
+        <v>1.7355</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5708</v>
+        <v>0.5681</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2831</v>
+        <v>0.2475</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7437</v>
+        <v>1.7355</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1107</v>
+        <v>1.1025</v>
       </c>
       <c r="G14" t="n">
         <v>0.633</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1107</v>
+        <v>1.1025</v>
       </c>
       <c r="I14" t="n">
         <v>1.1211</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.287</v>
+        <v>1.271</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4213</v>
+        <v>0.4161</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="E15" t="n">
-        <v>1.287</v>
+        <v>1.271</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4397</v>
+        <v>1.4237</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1527</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4397</v>
+        <v>1.4237</v>
       </c>
       <c r="I15" t="n">
         <v>1.4599</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0201</v>
+        <v>1.0268</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3339</v>
+        <v>0.3361</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0348</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0201</v>
+        <v>1.0268</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9077</v>
+        <v>-0.901</v>
       </c>
       <c r="G16" t="n">
         <v>1.9278</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9077</v>
+        <v>-0.901</v>
       </c>
       <c r="I16" t="n">
         <v>-0.9162</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9169</v>
+        <v>0.9153</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3001</v>
+        <v>0.2996</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.051</v>
+        <v>-0.0793</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9169</v>
+        <v>0.9153</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2131</v>
+        <v>0.2115</v>
       </c>
       <c r="G17" t="n">
         <v>0.7038</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2131</v>
+        <v>0.2115</v>
       </c>
       <c r="I17" t="n">
         <v>0.2151</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8551</v>
+        <v>0.85</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2799</v>
+        <v>0.2782</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0759</v>
+        <v>-0.1053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8551</v>
+        <v>0.85</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4604</v>
+        <v>0.4553</v>
       </c>
       <c r="G18" t="n">
         <v>0.3947</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4604</v>
+        <v>0.4553</v>
       </c>
       <c r="I18" t="n">
         <v>0.4669</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7396</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2453</v>
+        <v>0.2421</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1186</v>
+        <v>-0.1493</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7396</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3267</v>
+        <v>1.3168</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5772</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3267</v>
+        <v>1.3168</v>
       </c>
       <c r="I19" t="n">
         <v>1.3391</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2026</v>
+        <v>0.1975</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0663</v>
+        <v>0.0646</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3395</v>
+        <v>-0.3652</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2026</v>
+        <v>0.1975</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6867</v>
+        <v>0.6816</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4841</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6867</v>
+        <v>0.6816</v>
       </c>
       <c r="I20" t="n">
         <v>0.6931</v>
@@ -1376,7 +1376,7 @@
         <v>0.0447</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3661</v>
+        <v>-0.3894</v>
       </c>
       <c r="E21" t="n">
         <v>0.1367</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1137</v>
+        <v>0.1118</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0372</v>
+        <v>0.0366</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3754</v>
+        <v>-0.3994</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1137</v>
+        <v>0.1118</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5033</v>
+        <v>0.5014</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3896</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5033</v>
+        <v>0.5014</v>
       </c>
       <c r="I22" t="n">
         <v>0.5056</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0502</v>
+        <v>-0.0505</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0164</v>
+        <v>-0.0165</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4416</v>
+        <v>-0.464</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0502</v>
+        <v>-0.0505</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0683</v>
+        <v>0.068</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1185</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0683</v>
+        <v>0.068</v>
       </c>
       <c r="I23" t="n">
         <v>0.06859999999999999</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1055</v>
+        <v>-0.106</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0345</v>
+        <v>-0.0347</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.464</v>
+        <v>-0.4861</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1055</v>
+        <v>-0.106</v>
       </c>
       <c r="F24" t="n">
-        <v>0.149</v>
+        <v>0.1485</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2545</v>
       </c>
       <c r="H24" t="n">
-        <v>0.149</v>
+        <v>0.1485</v>
       </c>
       <c r="I24" t="n">
         <v>0.1497</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1213</v>
+        <v>-0.1249</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0397</v>
+        <v>-0.0409</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4704</v>
+        <v>-0.4937</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1213</v>
+        <v>-0.1249</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9162</v>
+        <v>0.3098</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0375</v>
+        <v>-0.4347</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9162</v>
+        <v>0.3098</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9247</v>
+        <v>0.3098</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0375</v>
+        <v>-0.4347</v>
       </c>
       <c r="K25" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L25" t="n">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1128000000000001</v>
+        <v>-0.1249</v>
       </c>
       <c r="N25" t="n">
-        <v>210</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1249</v>
+        <v>-0.1282</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0409</v>
+        <v>-0.042</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4718</v>
+        <v>-0.495</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1249</v>
+        <v>-0.1282</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3098</v>
+        <v>0.9093</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4347</v>
+        <v>-1.0375</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3098</v>
+        <v>0.9093</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3098</v>
+        <v>0.9247</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4347</v>
+        <v>-1.0375</v>
       </c>
       <c r="K26" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L26" t="n">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1249</v>
+        <v>-0.1128000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
@@ -1652,7 +1652,7 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.509</v>
+        <v>-0.5303</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2169</v>
@@ -1698,7 +1698,7 @@
         <v>-0.129</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5805</v>
+        <v>-0.6009</v>
       </c>
       <c r="E28" t="n">
         <v>-0.394</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5111</v>
+        <v>-0.5089</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1673</v>
+        <v>-0.1666</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6278</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5111</v>
+        <v>-0.5089</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2953</v>
+        <v>-0.2931</v>
       </c>
       <c r="G29" t="n">
         <v>-0.2158</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2953</v>
+        <v>-0.2931</v>
       </c>
       <c r="I29" t="n">
         <v>-0.2981</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5651</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1853</v>
+        <v>-0.185</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.65</v>
+        <v>-0.669</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5651</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1214</v>
+        <v>-0.1205</v>
       </c>
       <c r="G30" t="n">
         <v>-0.4446</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1214</v>
+        <v>-0.1205</v>
       </c>
       <c r="I30" t="n">
         <v>-0.1225</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7388</v>
+        <v>-0.7272</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2418</v>
+        <v>-0.238</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7198</v>
+        <v>-0.7336</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7388</v>
+        <v>-0.7272</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0453</v>
+        <v>-1.0337</v>
       </c>
       <c r="G31" t="n">
         <v>0.3065</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0453</v>
+        <v>-1.0337</v>
       </c>
       <c r="I31" t="n">
         <v>-1.06</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.758</v>
+        <v>-0.7603</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2481</v>
+        <v>-0.2489</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7276</v>
+        <v>-0.7468</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.758</v>
+        <v>-0.7603</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3019</v>
+        <v>0.2996</v>
       </c>
       <c r="G32" t="n">
         <v>-1.0599</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3019</v>
+        <v>0.2996</v>
       </c>
       <c r="I32" t="n">
         <v>0.3047</v>
@@ -1928,7 +1928,7 @@
         <v>-0.3172</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8128</v>
+        <v>-0.83</v>
       </c>
       <c r="E33" t="n">
         <v>-0.969</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2779</v>
+        <v>-1.2771</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4183</v>
+        <v>-0.418</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9376</v>
+        <v>-0.9527</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2779</v>
+        <v>-1.2771</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.3199</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3772</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.3199</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.3226</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3772</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2779</v>
+        <v>-1.2798</v>
       </c>
       <c r="N34" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2783</v>
+        <v>-1.2779</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4184</v>
+        <v>-0.4183</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9378</v>
+        <v>-0.953</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2783</v>
+        <v>-1.2779</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3211</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.3772</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3211</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3226</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.3772</v>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L35" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2798</v>
+        <v>-1.2779</v>
       </c>
       <c r="N35" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.286</v>
+        <v>-1.2842</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.421</v>
+        <v>-0.4204</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9409</v>
+        <v>-0.9555</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.286</v>
+        <v>-1.2842</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4813</v>
+        <v>-0.4795</v>
       </c>
       <c r="G36" t="n">
         <v>-0.8047</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4813</v>
+        <v>-0.4795</v>
       </c>
       <c r="I36" t="n">
         <v>-0.4835</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4595</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0031</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4037</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4269</v>
+        <v>-1.4238</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4671</v>
+        <v>-0.4661</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9978</v>
+        <v>-1.0112</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4269</v>
+        <v>-1.4238</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4148</v>
+        <v>-0.4117</v>
       </c>
       <c r="G38" t="n">
         <v>-1.0121</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4148</v>
+        <v>-0.4117</v>
       </c>
       <c r="I38" t="n">
         <v>-0.4187</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6832</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2645</v>
+        <v>-1.2754</v>
       </c>
       <c r="E39" t="n">
         <v>-2.0871</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1575</v>
+        <v>-2.1483</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7062</v>
+        <v>-0.7032</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2929</v>
+        <v>-1.2998</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1575</v>
+        <v>-2.1483</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2335</v>
+        <v>-1.2243</v>
       </c>
       <c r="G40" t="n">
         <v>-0.924</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2335</v>
+        <v>-1.2243</v>
       </c>
       <c r="I40" t="n">
         <v>-1.245</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.9339</v>
+        <v>-3.9242</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2877</v>
+        <v>-1.2846</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0106</v>
+        <v>-2.0073</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.9339</v>
+        <v>-3.9242</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2975</v>
+        <v>-1.2878</v>
       </c>
       <c r="G41" t="n">
         <v>-2.6364</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2975</v>
+        <v>-1.2878</v>
       </c>
       <c r="I41" t="n">
         <v>-1.3096</v>

--- a/database/event/5607/event_5607_evp_summary.xlsx
+++ b/database/event/5607/event_5607_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.1717</v>
+        <v>8.4359</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6749</v>
+        <v>2.7614</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8117</v>
+        <v>3.1704</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1717</v>
+        <v>8.4359</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6715</v>
+        <v>2.8349</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5002</v>
+        <v>5.601</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6715</v>
+        <v>2.8651</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6998</v>
+        <v>3.1057</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6504</v>
+        <v>5.601</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>219</v>
       </c>
       <c r="M2" t="n">
-        <v>8.350200000000001</v>
+        <v>8.7067</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7992</v>
+        <v>7.0956</v>
       </c>
       <c r="C3" t="n">
-        <v>2.553</v>
+        <v>2.3227</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6633</v>
+        <v>2.5653</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7992</v>
+        <v>7.0956</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6925</v>
+        <v>1.7517</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1067</v>
+        <v>5.3438</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6925</v>
+        <v>1.7517</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7211</v>
+        <v>1.8988</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1067</v>
+        <v>5.3438</v>
       </c>
       <c r="K3" t="n">
         <v>45</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.8278</v>
+        <v>7.242599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>250</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5393</v>
+        <v>6.6569</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4679</v>
+        <v>2.1791</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5597</v>
+        <v>2.3672</v>
       </c>
       <c r="E4" t="n">
-        <v>7.5393</v>
+        <v>6.6569</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5299</v>
+        <v>1.9914</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0095</v>
+        <v>4.6655</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5299</v>
+        <v>1.9914</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5943</v>
+        <v>2.1586</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0095</v>
+        <v>4.6655</v>
       </c>
       <c r="K4" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="M4" t="n">
-        <v>7.6038</v>
+        <v>6.8241</v>
       </c>
       <c r="N4" t="n">
-        <v>359</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8259</v>
+        <v>6.4341</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2344</v>
+        <v>2.1061</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2755</v>
+        <v>2.2667</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8259</v>
+        <v>6.4341</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7056</v>
+        <v>2.4848</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1203</v>
+        <v>3.9493</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7056</v>
+        <v>2.4848</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7344</v>
+        <v>2.8042</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1203</v>
+        <v>3.9493</v>
       </c>
       <c r="K5" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="L5" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8547</v>
+        <v>6.7535</v>
       </c>
       <c r="N5" t="n">
-        <v>250</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.8537</v>
+        <v>5.9479</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9162</v>
+        <v>1.947</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8882</v>
+        <v>2.0472</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8537</v>
+        <v>5.9479</v>
       </c>
       <c r="F6" t="n">
-        <v>1.73</v>
+        <v>2.3024</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1237</v>
+        <v>3.6455</v>
       </c>
       <c r="H6" t="n">
-        <v>1.73</v>
+        <v>2.3024</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7592</v>
+        <v>2.4957</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1237</v>
+        <v>3.6455</v>
       </c>
       <c r="K6" t="n">
         <v>45</v>
@@ -713,7 +713,7 @@
         <v>205</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8829</v>
+        <v>6.1412</v>
       </c>
       <c r="N6" t="n">
         <v>250</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9251</v>
+        <v>4.2696</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6122</v>
+        <v>1.3976</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5183</v>
+        <v>1.2895</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9251</v>
+        <v>4.2696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9689</v>
+        <v>1.0556</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9562</v>
+        <v>3.214</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9689</v>
+        <v>1.0556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9936</v>
+        <v>1.1913</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9562</v>
+        <v>3.214</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>227</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9498</v>
+        <v>4.4053</v>
       </c>
       <c r="N7" t="n">
         <v>359</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3033</v>
+        <v>2.8286</v>
       </c>
       <c r="C8" t="n">
-        <v>0.754</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4737</v>
+        <v>0.639</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3033</v>
+        <v>2.8286</v>
       </c>
       <c r="F8" t="n">
-        <v>1.151</v>
+        <v>2.6989</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1523</v>
+        <v>0.1297</v>
       </c>
       <c r="H8" t="n">
-        <v>1.151</v>
+        <v>2.6989</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1705</v>
+        <v>2.9255</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1523</v>
+        <v>0.1297</v>
       </c>
       <c r="K8" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3228</v>
+        <v>3.0552</v>
       </c>
       <c r="N8" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1913</v>
+        <v>2.2759</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7173</v>
+        <v>0.745</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4291</v>
+        <v>0.3894</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1913</v>
+        <v>2.2759</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6918</v>
+        <v>1.8455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4995</v>
+        <v>0.4304</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6918</v>
+        <v>1.8455</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7204</v>
+        <v>2.0004</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4995</v>
+        <v>0.4304</v>
       </c>
       <c r="K9" t="n">
         <v>52</v>
@@ -851,7 +851,7 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2199</v>
+        <v>2.4308</v>
       </c>
       <c r="N9" t="n">
         <v>183</v>
@@ -860,173 +860,173 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1013</v>
+        <v>2.16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6878</v>
+        <v>0.7071</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3932</v>
+        <v>0.3371</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1013</v>
+        <v>2.16</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3527</v>
+        <v>1.0484</v>
       </c>
       <c r="G10" t="n">
-        <v>2.454</v>
+        <v>1.1116</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3527</v>
+        <v>1.0484</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3527</v>
+        <v>1.1364</v>
       </c>
       <c r="J10" t="n">
-        <v>2.454</v>
+        <v>1.1116</v>
       </c>
       <c r="K10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L10" t="n">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1013</v>
+        <v>2.248</v>
       </c>
       <c r="N10" t="n">
-        <v>283</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8306</v>
+        <v>1.9399</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5992</v>
+        <v>0.635</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2854</v>
+        <v>0.2378</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8306</v>
+        <v>1.9399</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9742</v>
+        <v>1.6013</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8048</v>
+        <v>0.3386</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9742</v>
+        <v>1.6013</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9742</v>
+        <v>1.8071</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8048</v>
+        <v>0.3386</v>
       </c>
       <c r="K11" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8306</v>
+        <v>2.1457</v>
       </c>
       <c r="N11" t="n">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7813</v>
+        <v>1.91</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5831</v>
+        <v>0.6252</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2658</v>
+        <v>0.2243</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7813</v>
+        <v>1.91</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7403</v>
+        <v>1.2265</v>
       </c>
       <c r="G12" t="n">
-        <v>1.041</v>
+        <v>0.6835</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7403</v>
+        <v>1.2265</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7528</v>
+        <v>1.3295</v>
       </c>
       <c r="J12" t="n">
-        <v>1.041</v>
+        <v>0.6835</v>
       </c>
       <c r="K12" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="L12" t="n">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7938</v>
+        <v>2.013</v>
       </c>
       <c r="N12" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7406</v>
+        <v>1.8761</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5698</v>
+        <v>0.6141</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2495</v>
+        <v>0.209</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7406</v>
+        <v>1.8761</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7344</v>
+        <v>0.8502</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0062</v>
+        <v>1.0259</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7344</v>
+        <v>0.8502</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7637</v>
+        <v>0.9216</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0062</v>
+        <v>1.0259</v>
       </c>
       <c r="K13" t="n">
         <v>76</v>
@@ -1035,7 +1035,7 @@
         <v>134</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7699</v>
+        <v>1.9475</v>
       </c>
       <c r="N13" t="n">
         <v>210</v>
@@ -1044,173 +1044,173 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7355</v>
+        <v>1.7743</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5681</v>
+        <v>0.5808</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2475</v>
+        <v>0.163</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7355</v>
+        <v>1.7743</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1025</v>
+        <v>-0.1313</v>
       </c>
       <c r="G14" t="n">
-        <v>0.633</v>
+        <v>1.9056</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1025</v>
+        <v>-0.1313</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1211</v>
+        <v>-0.1313</v>
       </c>
       <c r="J14" t="n">
-        <v>0.633</v>
+        <v>1.9056</v>
       </c>
       <c r="K14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7541</v>
+        <v>1.7743</v>
       </c>
       <c r="N14" t="n">
-        <v>250</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.271</v>
+        <v>1.5401</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4161</v>
+        <v>0.5041</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0625</v>
+        <v>0.0573</v>
       </c>
       <c r="E15" t="n">
-        <v>1.271</v>
+        <v>1.5401</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4237</v>
+        <v>-0.6569</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1527</v>
+        <v>2.197</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4237</v>
+        <v>-0.6569</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4599</v>
+        <v>-0.6569</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1527</v>
+        <v>2.197</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3072</v>
+        <v>1.5401</v>
       </c>
       <c r="N15" t="n">
-        <v>359</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0268</v>
+        <v>1.4585</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3361</v>
+        <v>0.4774</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0348</v>
+        <v>0.0204</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0268</v>
+        <v>1.4585</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.901</v>
+        <v>0.7592</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9278</v>
+        <v>0.6993</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.901</v>
+        <v>0.7592</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9162</v>
+        <v>0.8568</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9278</v>
+        <v>0.6993</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L16" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0116</v>
+        <v>1.5561</v>
       </c>
       <c r="N16" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9153</v>
+        <v>1.4584</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2996</v>
+        <v>0.4774</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0793</v>
+        <v>0.0204</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9153</v>
+        <v>1.4584</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2115</v>
+        <v>-0.3506</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7038</v>
+        <v>1.809</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2115</v>
+        <v>-0.3506</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2151</v>
+        <v>-0.38</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7038</v>
+        <v>1.809</v>
       </c>
       <c r="K17" t="n">
         <v>123</v>
@@ -1219,7 +1219,7 @@
         <v>219</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9189000000000001</v>
+        <v>1.429</v>
       </c>
       <c r="N17" t="n">
         <v>342</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.85</v>
+        <v>1.0819</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2782</v>
+        <v>0.3542</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1053</v>
+        <v>-0.1496</v>
       </c>
       <c r="E18" t="n">
-        <v>0.85</v>
+        <v>1.0819</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4553</v>
+        <v>1.2638</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3947</v>
+        <v>-0.1819</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4553</v>
+        <v>1.2638</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4669</v>
+        <v>1.3699</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3947</v>
+        <v>-0.1819</v>
       </c>
       <c r="K18" t="n">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="L18" t="n">
-        <v>227</v>
+        <v>131</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8615999999999999</v>
+        <v>1.188</v>
       </c>
       <c r="N18" t="n">
-        <v>359</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7396</v>
+        <v>0.6387</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2421</v>
+        <v>0.2091</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1493</v>
+        <v>-0.3497</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7396</v>
+        <v>0.6387</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3168</v>
+        <v>0.3078</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5772</v>
+        <v>0.3309</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3168</v>
+        <v>0.3078</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3391</v>
+        <v>0.3336</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5772</v>
+        <v>0.3309</v>
       </c>
       <c r="K19" t="n">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="L19" t="n">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7618999999999999</v>
+        <v>0.6645000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>183</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1975</v>
+        <v>0.4346</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0646</v>
+        <v>0.1423</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3652</v>
+        <v>-0.4418</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1975</v>
+        <v>0.4346</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6816</v>
+        <v>1.0522</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4841</v>
+        <v>-0.6176</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6816</v>
+        <v>1.0522</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6931</v>
+        <v>1.1405</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4841</v>
+        <v>-0.6176</v>
       </c>
       <c r="K20" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L20" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2090000000000001</v>
+        <v>0.5229</v>
       </c>
       <c r="N20" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1367</v>
+        <v>0.4271</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0447</v>
+        <v>0.1398</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3894</v>
+        <v>-0.4452</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1367</v>
+        <v>0.4271</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8806</v>
+        <v>-0.5817</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0173</v>
+        <v>1.0088</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8806</v>
+        <v>-0.5817</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8806</v>
+        <v>-0.5817</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0173</v>
+        <v>1.0088</v>
       </c>
       <c r="K21" t="n">
         <v>54</v>
@@ -1403,7 +1403,7 @@
         <v>229</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1367</v>
+        <v>0.4270999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>283</v>
@@ -1412,81 +1412,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1118</v>
+        <v>0.3665</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0366</v>
+        <v>0.12</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3994</v>
+        <v>-0.4726</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1118</v>
+        <v>0.3665</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5014</v>
+        <v>0.6327</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3896</v>
+        <v>-0.2662</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5014</v>
+        <v>0.6327</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5056</v>
+        <v>0.6858</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3896</v>
+        <v>-0.2662</v>
       </c>
       <c r="K22" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L22" t="n">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="M22" t="n">
-        <v>0.116</v>
+        <v>0.4196</v>
       </c>
       <c r="N22" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0505</v>
+        <v>0.1864</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0165</v>
+        <v>0.061</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.464</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0505</v>
+        <v>0.1864</v>
       </c>
       <c r="F23" t="n">
-        <v>0.068</v>
+        <v>0.4812</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1185</v>
+        <v>-0.2948</v>
       </c>
       <c r="H23" t="n">
-        <v>0.068</v>
+        <v>0.4812</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.501</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1185</v>
+        <v>-0.2948</v>
       </c>
       <c r="K23" t="n">
         <v>76</v>
@@ -1495,7 +1495,7 @@
         <v>58</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0499</v>
+        <v>0.2062</v>
       </c>
       <c r="N23" t="n">
         <v>134</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.106</v>
+        <v>0.1793</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0347</v>
+        <v>0.0587</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4861</v>
+        <v>-0.5571</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.106</v>
+        <v>0.1793</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1485</v>
+        <v>0.4657</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2545</v>
+        <v>-0.2864</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1485</v>
+        <v>0.4657</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1497</v>
+        <v>0.5048</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2545</v>
+        <v>-0.2864</v>
       </c>
       <c r="K24" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="L24" t="n">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1048</v>
+        <v>0.2184</v>
       </c>
       <c r="N24" t="n">
-        <v>134</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1249</v>
+        <v>0.1441</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0409</v>
+        <v>0.0472</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4937</v>
+        <v>-0.573</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1249</v>
+        <v>0.1441</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3098</v>
+        <v>0.1084</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4347</v>
+        <v>0.0357</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3098</v>
+        <v>0.1084</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3098</v>
+        <v>0.1175</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4347</v>
+        <v>0.0357</v>
       </c>
       <c r="K25" t="n">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="L25" t="n">
-        <v>47</v>
+        <v>219</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1249</v>
+        <v>0.1532</v>
       </c>
       <c r="N25" t="n">
-        <v>99</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1282</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.042</v>
+        <v>0.0261</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.495</v>
+        <v>-0.602</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1282</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9093</v>
+        <v>0.1837</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.0375</v>
+        <v>-0.104</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9093</v>
+        <v>0.1837</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9247</v>
+        <v>0.1913</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.0375</v>
+        <v>-0.104</v>
       </c>
       <c r="K26" t="n">
         <v>76</v>
       </c>
       <c r="L26" t="n">
+        <v>58</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="N26" t="n">
         <v>134</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-0.1128000000000001</v>
-      </c>
-      <c r="N26" t="n">
-        <v>210</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2169</v>
+        <v>0.0565</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5303</v>
+        <v>-0.6125</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2169</v>
+        <v>0.0565</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5819</v>
+        <v>0.2727</v>
       </c>
       <c r="G27" t="n">
-        <v>0.365</v>
+        <v>-0.2162</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5819</v>
+        <v>0.2727</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5819</v>
+        <v>0.2839</v>
       </c>
       <c r="J27" t="n">
-        <v>0.365</v>
+        <v>-0.2162</v>
       </c>
       <c r="K27" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L27" t="n">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2169</v>
+        <v>0.06769999999999998</v>
       </c>
       <c r="N27" t="n">
-        <v>283</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.394</v>
+        <v>0.0111</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.129</v>
+        <v>0.0036</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6009</v>
+        <v>-0.633</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.394</v>
+        <v>0.0111</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3466</v>
+        <v>-0.4168</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.7406</v>
+        <v>0.4279</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3466</v>
+        <v>-0.4168</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3466</v>
+        <v>-0.4168</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.7406</v>
+        <v>0.4279</v>
       </c>
       <c r="K28" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L28" t="n">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.394</v>
+        <v>0.0111</v>
       </c>
       <c r="N28" t="n">
-        <v>99</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5089</v>
+        <v>-0.0054</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1666</v>
+        <v>-0.0018</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6405</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5089</v>
+        <v>-0.0054</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2931</v>
+        <v>-0.5657</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2158</v>
+        <v>0.5603</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2931</v>
+        <v>-0.5657</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2981</v>
+        <v>-0.6384</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2158</v>
+        <v>0.5603</v>
       </c>
       <c r="K29" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L29" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5139</v>
+        <v>-0.07809999999999995</v>
       </c>
       <c r="N29" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5651</v>
+        <v>-0.0479</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.185</v>
+        <v>-0.0157</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.669</v>
+        <v>-0.6596</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5651</v>
+        <v>-0.0479</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1205</v>
+        <v>0.135</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4446</v>
+        <v>-0.1829</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1205</v>
+        <v>0.135</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1225</v>
+        <v>0.1463</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4446</v>
+        <v>-0.1829</v>
       </c>
       <c r="K30" t="n">
         <v>76</v>
@@ -1817,7 +1817,7 @@
         <v>134</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5670999999999999</v>
+        <v>-0.03659999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>210</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7272</v>
+        <v>-0.0752</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.238</v>
+        <v>-0.0246</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7336</v>
+        <v>-0.672</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7272</v>
+        <v>-0.0752</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0337</v>
+        <v>0.2812</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3065</v>
+        <v>-0.3564</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0337</v>
+        <v>0.2812</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.06</v>
+        <v>0.2812</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3065</v>
+        <v>-0.3564</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="L31" t="n">
-        <v>227</v>
+        <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7535000000000001</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>359</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7603</v>
+        <v>-0.1705</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2489</v>
+        <v>-0.0558</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7468</v>
+        <v>-0.715</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7603</v>
+        <v>-0.1705</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2996</v>
+        <v>0.3289</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.0599</v>
+        <v>-0.4994</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2996</v>
+        <v>0.3289</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3047</v>
+        <v>0.3289</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0599</v>
+        <v>-0.4994</v>
       </c>
       <c r="K32" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="L32" t="n">
-        <v>205</v>
+        <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7552000000000001</v>
+        <v>-0.1705</v>
       </c>
       <c r="N32" t="n">
-        <v>250</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.969</v>
+        <v>-0.6168</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3172</v>
+        <v>-0.2019</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.83</v>
+        <v>-0.9165</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.969</v>
+        <v>-0.6168</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6647</v>
+        <v>-0.4246</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3043</v>
+        <v>-0.1922</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6647</v>
+        <v>-0.4246</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6647</v>
+        <v>-0.4246</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3043</v>
+        <v>-0.1922</v>
       </c>
       <c r="K33" t="n">
         <v>52</v>
@@ -1955,7 +1955,7 @@
         <v>47</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.969</v>
+        <v>-0.6168</v>
       </c>
       <c r="N33" t="n">
         <v>99</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.2771</v>
+        <v>-0.6233</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.418</v>
+        <v>-0.204</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9527</v>
+        <v>-0.9194</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.2771</v>
+        <v>-0.6233</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3199</v>
+        <v>0.0054</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.6287</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3199</v>
+        <v>0.0054</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3226</v>
+        <v>0.0056</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.6287</v>
       </c>
       <c r="K34" t="n">
         <v>76</v>
@@ -2001,7 +2001,7 @@
         <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.2798</v>
+        <v>-0.6231</v>
       </c>
       <c r="N34" t="n">
         <v>134</v>
@@ -2010,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.2779</v>
+        <v>-0.6243</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4183</v>
+        <v>-0.2044</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.953</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2779</v>
+        <v>-0.6243</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.0775</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3772</v>
+        <v>-0.5468</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.0775</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3772</v>
+        <v>-0.5468</v>
       </c>
       <c r="K35" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L35" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2779</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2842</v>
+        <v>-0.7078</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4204</v>
+        <v>-0.2317</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9555</v>
+        <v>-0.9576</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2842</v>
+        <v>-0.7078</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4795</v>
+        <v>-0.5806</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8047</v>
+        <v>-0.1272</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4795</v>
+        <v>-0.5806</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4835</v>
+        <v>-0.5806</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8047</v>
+        <v>-0.1272</v>
       </c>
       <c r="K36" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L36" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2882</v>
+        <v>-0.7078</v>
       </c>
       <c r="N36" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4037</v>
+        <v>-0.7923</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4595</v>
+        <v>-0.2594</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0031</v>
+        <v>-0.9957</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4037</v>
+        <v>-0.7923</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4037</v>
+        <v>-0.1116</v>
       </c>
       <c r="G37" t="n">
-        <v>-1</v>
+        <v>-0.6807</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4037</v>
+        <v>-0.1116</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4037</v>
+        <v>-0.121</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.6807</v>
       </c>
       <c r="K37" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4037</v>
+        <v>-0.8017</v>
       </c>
       <c r="N37" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4238</v>
+        <v>-1.185</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4661</v>
+        <v>-0.3879</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0112</v>
+        <v>-1.173</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4238</v>
+        <v>-1.185</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4117</v>
+        <v>-0.2774</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0121</v>
+        <v>-0.9076</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4117</v>
+        <v>-0.2774</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4187</v>
+        <v>-0.2774</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.0121</v>
+        <v>-0.9076</v>
       </c>
       <c r="K38" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L38" t="n">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.4308</v>
+        <v>-1.185</v>
       </c>
       <c r="N38" t="n">
-        <v>210</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0871</v>
+        <v>-1.2411</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6832</v>
+        <v>-0.4063</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2754</v>
+        <v>-1.1983</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0871</v>
+        <v>-1.2411</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1967</v>
+        <v>0.289</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.2838</v>
+        <v>-1.5301</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1967</v>
+        <v>0.289</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1967</v>
+        <v>0.289</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.2838</v>
+        <v>-1.5301</v>
       </c>
       <c r="K39" t="n">
         <v>54</v>
@@ -2231,7 +2231,7 @@
         <v>229</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.0871</v>
+        <v>-1.2411</v>
       </c>
       <c r="N39" t="n">
         <v>283</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1483</v>
+        <v>-1.4536</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7032</v>
+        <v>-0.4758</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2998</v>
+        <v>-1.2942</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1483</v>
+        <v>-1.4536</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2243</v>
+        <v>-1.0349</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.924</v>
+        <v>-0.4187</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2243</v>
+        <v>-1.0349</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.245</v>
+        <v>-1.1218</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.924</v>
+        <v>-0.4187</v>
       </c>
       <c r="K40" t="n">
         <v>52</v>
@@ -2277,7 +2277,7 @@
         <v>131</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.169</v>
+        <v>-1.5405</v>
       </c>
       <c r="N40" t="n">
         <v>183</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.9242</v>
+        <v>-2.9687</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2846</v>
+        <v>-0.9718</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0073</v>
+        <v>-1.9782</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.9242</v>
+        <v>-2.9687</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2878</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.6364</v>
+        <v>-2.2565</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2878</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3096</v>
+        <v>-0.772</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.6364</v>
+        <v>-2.2565</v>
       </c>
       <c r="K41" t="n">
         <v>123</v>
@@ -2323,7 +2323,7 @@
         <v>219</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.946</v>
+        <v>-3.0285</v>
       </c>
       <c r="N41" t="n">
         <v>342</v>
@@ -2429,10 +2429,10 @@
         <v>1.91</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9274</v>
+        <v>1.6222</v>
       </c>
       <c r="J2" t="n">
-        <v>53.9672</v>
+        <v>45.4216</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7709</v>
+        <v>0.7991</v>
       </c>
       <c r="J3" t="n">
-        <v>21.5852</v>
+        <v>22.3748</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3668</v>
+        <v>0.4472</v>
       </c>
       <c r="J4" t="n">
-        <v>10.2704</v>
+        <v>12.5216</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0481</v>
+        <v>0.0298</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3468</v>
+        <v>0.8344</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3179</v>
+        <v>-0.2346</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.901199999999999</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3379</v>
+        <v>0.3658</v>
       </c>
       <c r="J7" t="n">
-        <v>9.4612</v>
+        <v>10.2424</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1766</v>
+        <v>-0.1397</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.9448</v>
+        <v>-3.9116</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2327</v>
+        <v>-0.1708</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.5156</v>
+        <v>-4.7824</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.76</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3952</v>
+        <v>-0.2585</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.0656</v>
+        <v>-7.238</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.58</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6428</v>
+        <v>-0.4289</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.9984</v>
+        <v>-12.0092</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3019</v>
+        <v>0.2441</v>
       </c>
       <c r="J12" t="n">
-        <v>6.6418</v>
+        <v>5.3702</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2153</v>
+        <v>0.1592</v>
       </c>
       <c r="J13" t="n">
-        <v>4.7366</v>
+        <v>3.5024</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3198</v>
+        <v>-0.2109</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.0356</v>
+        <v>-4.6398</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.7</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4859</v>
+        <v>-0.3175</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.6898</v>
+        <v>-6.985</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6575</v>
+        <v>-0.4394</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.465</v>
+        <v>-9.6668</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7227</v>
+        <v>0.6461</v>
       </c>
       <c r="J17" t="n">
-        <v>15.8994</v>
+        <v>14.2142</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.41</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.5158</v>
       </c>
       <c r="J18" t="n">
-        <v>12.7842</v>
+        <v>11.3476</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.31</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4514</v>
+        <v>0.4042</v>
       </c>
       <c r="J19" t="n">
-        <v>9.9308</v>
+        <v>8.8924</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.139</v>
+        <v>0.1603</v>
       </c>
       <c r="J20" t="n">
-        <v>3.058</v>
+        <v>3.5266</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.89</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2973</v>
+        <v>-0.171</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.5406</v>
+        <v>-3.762</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.57</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3058</v>
+        <v>1.2036</v>
       </c>
       <c r="J22" t="n">
-        <v>30.0334</v>
+        <v>27.6828</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8637</v>
+        <v>0.9002</v>
       </c>
       <c r="J23" t="n">
-        <v>19.8651</v>
+        <v>20.7046</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7623</v>
+        <v>0.8142</v>
       </c>
       <c r="J24" t="n">
-        <v>17.5329</v>
+        <v>18.7266</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.623</v>
+        <v>0.7043</v>
       </c>
       <c r="J25" t="n">
-        <v>14.329</v>
+        <v>16.1989</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0427</v>
+        <v>0.125</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9821</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4537</v>
+        <v>0.5259</v>
       </c>
       <c r="J27" t="n">
-        <v>10.4351</v>
+        <v>12.0957</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.315</v>
+        <v>-0.2384</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.245</v>
+        <v>-5.4832</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.74</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3776</v>
+        <v>-0.2659</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.684799999999999</v>
+        <v>-6.1157</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.66</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.3404</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.6748</v>
+        <v>-7.8292</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8696</v>
+        <v>-0.6008</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.0008</v>
+        <v>-13.8184</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8118</v>
+        <v>0.7814</v>
       </c>
       <c r="J32" t="n">
-        <v>22.7304</v>
+        <v>21.8792</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4032</v>
+        <v>0.3573</v>
       </c>
       <c r="J33" t="n">
-        <v>11.2896</v>
+        <v>10.0044</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3751</v>
+        <v>-0.232</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.5028</v>
+        <v>-6.496</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4036</v>
+        <v>-0.252</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.3008</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.76</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4452</v>
+        <v>-0.2815</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.4656</v>
+        <v>-7.882</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4268</v>
+        <v>0.3591</v>
       </c>
       <c r="J37" t="n">
-        <v>11.9504</v>
+        <v>10.0548</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4129</v>
+        <v>0.3467</v>
       </c>
       <c r="J38" t="n">
-        <v>11.5612</v>
+        <v>9.707599999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2793</v>
+        <v>0.2318</v>
       </c>
       <c r="J39" t="n">
-        <v>7.8204</v>
+        <v>6.4904</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0861</v>
+        <v>0.0911</v>
       </c>
       <c r="J40" t="n">
-        <v>2.4108</v>
+        <v>2.5508</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5206</v>
+        <v>-0.3353</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.5768</v>
+        <v>-9.388400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4682</v>
+        <v>1.3004</v>
       </c>
       <c r="J42" t="n">
-        <v>39.6414</v>
+        <v>35.1108</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5834</v>
+        <v>0.5728</v>
       </c>
       <c r="J43" t="n">
-        <v>15.7518</v>
+        <v>15.4656</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J44" t="n">
-        <v>2.1438</v>
+        <v>3.6477</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0434</v>
+        <v>0.1005</v>
       </c>
       <c r="J45" t="n">
-        <v>1.1718</v>
+        <v>2.7135</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.6593</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.2564</v>
+        <v>-17.8011</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.43</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7034</v>
+        <v>0.8691</v>
       </c>
       <c r="J47" t="n">
-        <v>18.9918</v>
+        <v>23.4657</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1613</v>
+        <v>0.1543</v>
       </c>
       <c r="J48" t="n">
-        <v>4.3551</v>
+        <v>4.1661</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3062</v>
+        <v>-0.191</v>
       </c>
       <c r="J49" t="n">
-        <v>-8.2674</v>
+        <v>-5.157</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4674</v>
+        <v>-0.3002</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.6198</v>
+        <v>-8.105399999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5861</v>
+        <v>-0.3854</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.8247</v>
+        <v>-10.4058</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3447</v>
+        <v>1.225</v>
       </c>
       <c r="J52" t="n">
-        <v>30.9281</v>
+        <v>28.175</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1465</v>
+        <v>1.1003</v>
       </c>
       <c r="J53" t="n">
-        <v>26.3695</v>
+        <v>25.3069</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3141</v>
+        <v>0.395</v>
       </c>
       <c r="J54" t="n">
-        <v>7.2243</v>
+        <v>9.085000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2329</v>
+        <v>0.3137</v>
       </c>
       <c r="J55" t="n">
-        <v>5.3567</v>
+        <v>7.2151</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0562</v>
+        <v>0.1348</v>
       </c>
       <c r="J56" t="n">
-        <v>1.2926</v>
+        <v>3.1004</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0585</v>
+        <v>-0.0625</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.3455</v>
+        <v>-1.4375</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0585</v>
+        <v>-0.0625</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.3455</v>
+        <v>-1.4375</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.87</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.215</v>
+        <v>-0.153</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.945</v>
+        <v>-3.519</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3116</v>
+        <v>-0.203</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1668</v>
+        <v>-4.669</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.42</v>
+        <v>-0.2719</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.66</v>
+        <v>-6.2537</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.36</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9832</v>
+        <v>0.9643</v>
       </c>
       <c r="J62" t="n">
-        <v>33.4288</v>
+        <v>32.7862</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>17.9758</v>
+        <v>17.2584</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4445</v>
+        <v>0.4298</v>
       </c>
       <c r="J64" t="n">
-        <v>15.113</v>
+        <v>14.6132</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4149</v>
+        <v>0.4035</v>
       </c>
       <c r="J65" t="n">
-        <v>14.1066</v>
+        <v>13.719</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9546</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-32.4564</v>
+        <v>-31.4466</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4225</v>
+        <v>0.4857</v>
       </c>
       <c r="J67" t="n">
-        <v>14.365</v>
+        <v>16.5138</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2725</v>
+        <v>0.295</v>
       </c>
       <c r="J68" t="n">
-        <v>9.265000000000001</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.92</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1814</v>
+        <v>-0.1085</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.1676</v>
+        <v>-3.689</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2846</v>
+        <v>-0.174</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.676399999999999</v>
+        <v>-5.916</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4745</v>
+        <v>-0.3041</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.133</v>
+        <v>-10.3394</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.81</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6937</v>
+        <v>1.4619</v>
       </c>
       <c r="J72" t="n">
-        <v>33.874</v>
+        <v>29.238</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.68</v>
       </c>
       <c r="I73" t="n">
-        <v>1.4587</v>
+        <v>1.3116</v>
       </c>
       <c r="J73" t="n">
-        <v>29.174</v>
+        <v>26.232</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7229</v>
+        <v>0.8373</v>
       </c>
       <c r="J74" t="n">
-        <v>14.458</v>
+        <v>16.746</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4739</v>
+        <v>0.5847</v>
       </c>
       <c r="J75" t="n">
-        <v>9.478</v>
+        <v>11.694</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.257</v>
+        <v>0.3579</v>
       </c>
       <c r="J76" t="n">
-        <v>5.14</v>
+        <v>7.158</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.79</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.2258</v>
+        <v>-0.1967</v>
       </c>
       <c r="J77" t="n">
-        <v>-4.516</v>
+        <v>-3.934</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.68</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4005</v>
+        <v>-0.3083</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.01</v>
+        <v>-6.166</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.63</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4997</v>
+        <v>-0.3528</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.994</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.596</v>
+        <v>-0.4077</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.92</v>
+        <v>-8.154</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6252</v>
+        <v>-0.4263</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.504</v>
+        <v>-8.526</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.84</v>
       </c>
       <c r="I82" t="n">
-        <v>1.7796</v>
+        <v>1.5149</v>
       </c>
       <c r="J82" t="n">
-        <v>40.9308</v>
+        <v>34.8427</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.44</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0175</v>
+        <v>1.0342</v>
       </c>
       <c r="J83" t="n">
-        <v>23.4025</v>
+        <v>23.7866</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9507</v>
+        <v>0.9883</v>
       </c>
       <c r="J84" t="n">
-        <v>21.8661</v>
+        <v>22.7309</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.332</v>
+        <v>0.4276</v>
       </c>
       <c r="J85" t="n">
-        <v>7.636</v>
+        <v>9.8348</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3726</v>
+        <v>-0.2878</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.569800000000001</v>
+        <v>-6.6194</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1857</v>
+        <v>-0.1623</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.2711</v>
+        <v>-3.7329</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2021</v>
+        <v>-0.1731</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.6483</v>
+        <v>-3.9813</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2672</v>
+        <v>-0.2149</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.1456</v>
+        <v>-4.9427</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5417</v>
+        <v>-0.3647</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.4591</v>
+        <v>-8.3881</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.52</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6919</v>
+        <v>-0.4676</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.9137</v>
+        <v>-10.7548</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6928</v>
+        <v>1.4615</v>
       </c>
       <c r="J92" t="n">
-        <v>37.2416</v>
+        <v>32.153</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.56</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2261</v>
+        <v>1.1703</v>
       </c>
       <c r="J93" t="n">
-        <v>26.9742</v>
+        <v>25.7466</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.37</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7891</v>
+        <v>0.9019</v>
       </c>
       <c r="J94" t="n">
-        <v>17.3602</v>
+        <v>19.8418</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.32</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6773</v>
+        <v>0.7926</v>
       </c>
       <c r="J95" t="n">
-        <v>14.9006</v>
+        <v>17.4372</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2815</v>
+        <v>0.3839</v>
       </c>
       <c r="J96" t="n">
-        <v>6.193</v>
+        <v>8.4458</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1212</v>
+        <v>0.0867</v>
       </c>
       <c r="J97" t="n">
-        <v>2.6664</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.88</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1277</v>
+        <v>-0.1218</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.8094</v>
+        <v>-2.6796</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4436</v>
+        <v>-0.3021</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.7592</v>
+        <v>-6.6462</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5904</v>
+        <v>-0.3957</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.9888</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.52</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6965</v>
+        <v>-0.4704</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.323</v>
+        <v>-10.3488</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4982</v>
+        <v>0.4002</v>
       </c>
       <c r="J102" t="n">
-        <v>13.9496</v>
+        <v>11.2056</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.97</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0362</v>
+        <v>-0.0421</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.0136</v>
+        <v>-1.1788</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2805</v>
+        <v>-0.1777</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.854</v>
+        <v>-4.9756</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.84</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.297</v>
+        <v>-0.188</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.316000000000001</v>
+        <v>-5.264</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.581</v>
+        <v>-0.3823</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.268</v>
+        <v>-10.7044</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.707</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>19.796</v>
+        <v>14.1848</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4053</v>
+        <v>0.3455</v>
       </c>
       <c r="J108" t="n">
-        <v>11.3484</v>
+        <v>9.673999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3616</v>
+        <v>0.3177</v>
       </c>
       <c r="J109" t="n">
-        <v>10.1248</v>
+        <v>8.8956</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0123</v>
+        <v>0.0445</v>
       </c>
       <c r="J110" t="n">
-        <v>0.3444</v>
+        <v>1.246</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.9</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2709</v>
+        <v>-0.1537</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.5852</v>
+        <v>-4.3036</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0994</v>
+        <v>0.7866</v>
       </c>
       <c r="J112" t="n">
-        <v>31.8826</v>
+        <v>22.8114</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>1.0575</v>
+        <v>0.7602</v>
       </c>
       <c r="J113" t="n">
-        <v>30.6675</v>
+        <v>22.0458</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1292</v>
       </c>
       <c r="J114" t="n">
-        <v>1.9604</v>
+        <v>3.7468</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0487</v>
+        <v>0.0164</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.4123</v>
+        <v>0.4756</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4355</v>
+        <v>-0.364</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.6295</v>
+        <v>-10.556</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3502</v>
+        <v>0.3685</v>
       </c>
       <c r="J117" t="n">
-        <v>10.1558</v>
+        <v>10.6865</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2561</v>
+        <v>0.2748</v>
       </c>
       <c r="J118" t="n">
-        <v>7.4269</v>
+        <v>7.9692</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1483</v>
+        <v>0.1459</v>
       </c>
       <c r="J119" t="n">
-        <v>4.3007</v>
+        <v>4.2311</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3162</v>
+        <v>-0.1948</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.1698</v>
+        <v>-5.6492</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5407</v>
+        <v>-0.3517</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.6803</v>
+        <v>-10.1993</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.38</v>
       </c>
       <c r="I122" t="n">
-        <v>1.0168</v>
+        <v>0.7308</v>
       </c>
       <c r="J122" t="n">
-        <v>28.4704</v>
+        <v>20.4624</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.43</v>
+        <v>0.3882</v>
       </c>
       <c r="J123" t="n">
-        <v>12.04</v>
+        <v>10.8696</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1921</v>
+        <v>0.2348</v>
       </c>
       <c r="J124" t="n">
-        <v>5.3788</v>
+        <v>6.5744</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1921</v>
+        <v>0.2348</v>
       </c>
       <c r="J125" t="n">
-        <v>5.3788</v>
+        <v>6.5744</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3906</v>
+        <v>-0.3225</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.9368</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4588</v>
+        <v>0.4505</v>
       </c>
       <c r="J127" t="n">
-        <v>12.8464</v>
+        <v>12.614</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="J128" t="n">
-        <v>1.9068</v>
+        <v>1.3412</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="J129" t="n">
-        <v>1.9068</v>
+        <v>1.3412</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1703</v>
+        <v>-0.1061</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.7684</v>
+        <v>-2.9708</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6983</v>
+        <v>-0.4691</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.5524</v>
+        <v>-13.1348</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.73</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6311</v>
+        <v>1.1387</v>
       </c>
       <c r="J132" t="n">
-        <v>42.4086</v>
+        <v>29.6062</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.7274</v>
       </c>
       <c r="J133" t="n">
-        <v>25.6464</v>
+        <v>18.9124</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4006</v>
+        <v>0.4178</v>
       </c>
       <c r="J134" t="n">
-        <v>10.4156</v>
+        <v>10.8628</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1537</v>
+        <v>0.2314</v>
       </c>
       <c r="J135" t="n">
-        <v>3.9962</v>
+        <v>6.0164</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4918</v>
+        <v>-0.417</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.7868</v>
+        <v>-10.842</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.97</v>
       </c>
       <c r="I137" t="n">
-        <v>0.0111</v>
+        <v>-0.0234</v>
       </c>
       <c r="J137" t="n">
-        <v>0.2886</v>
+        <v>-0.6084000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0101</v>
+        <v>-0.0375</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.2626</v>
+        <v>-0.975</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2641</v>
+        <v>-0.1969</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.8666</v>
+        <v>-5.1194</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4266</v>
+        <v>-0.2825</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.0916</v>
+        <v>-7.345</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6857</v>
+        <v>-0.461</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.8282</v>
+        <v>-11.986</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2819</v>
+        <v>-0.2358</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.9199</v>
+        <v>-4.9518</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.75</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2819</v>
+        <v>-0.2358</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.9199</v>
+        <v>-4.9518</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.61</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.526</v>
+        <v>-0.369</v>
       </c>
       <c r="J144" t="n">
-        <v>-11.046</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6052</v>
+        <v>-0.4148</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.7092</v>
+        <v>-8.710800000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7046</v>
+        <v>-0.4804</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.7966</v>
+        <v>-10.0884</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.04</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1838</v>
+        <v>0.7894</v>
       </c>
       <c r="J147" t="n">
-        <v>24.8598</v>
+        <v>16.5774</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6383</v>
+        <v>0.4924</v>
       </c>
       <c r="J148" t="n">
-        <v>13.4043</v>
+        <v>10.3404</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.41</v>
       </c>
       <c r="I149" t="n">
-        <v>0.489</v>
+        <v>0.4268</v>
       </c>
       <c r="J149" t="n">
-        <v>10.269</v>
+        <v>8.9628</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.4</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4766</v>
+        <v>0.4205</v>
       </c>
       <c r="J150" t="n">
-        <v>10.0086</v>
+        <v>8.830500000000001</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.12</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1099</v>
+        <v>0.1469</v>
       </c>
       <c r="J151" t="n">
-        <v>2.3079</v>
+        <v>3.0849</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1348</v>
+        <v>0.8174</v>
       </c>
       <c r="J152" t="n">
-        <v>28.37</v>
+        <v>20.435</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6813</v>
+        <v>0.5572</v>
       </c>
       <c r="J153" t="n">
-        <v>17.0325</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6171</v>
+        <v>0.531</v>
       </c>
       <c r="J154" t="n">
-        <v>15.4275</v>
+        <v>13.275</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.4762</v>
       </c>
       <c r="J155" t="n">
-        <v>12.665</v>
+        <v>11.905</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1247</v>
+        <v>0.2019</v>
       </c>
       <c r="J156" t="n">
-        <v>3.1175</v>
+        <v>5.0475</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2401</v>
+        <v>0.2381</v>
       </c>
       <c r="J157" t="n">
-        <v>6.0025</v>
+        <v>5.9525</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1914</v>
+        <v>-0.1496</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.785</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2284</v>
+        <v>-0.1703</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.71</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4379</v>
+        <v>-0.2866</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.9475</v>
+        <v>-7.165</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.55</v>
+        <v>-0.3627</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.75</v>
+        <v>-9.067500000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5352</v>
+        <v>0.485</v>
       </c>
       <c r="J162" t="n">
-        <v>15.5208</v>
+        <v>14.065</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.92</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1509</v>
+        <v>-0.1041</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.3761</v>
+        <v>-3.0189</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.743</v>
+        <v>-4.8778</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4065</v>
+        <v>-0.2591</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.7885</v>
+        <v>-7.5139</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4209</v>
+        <v>-0.2689</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.2061</v>
+        <v>-7.7981</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.38</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5758</v>
+        <v>0.5008</v>
       </c>
       <c r="J167" t="n">
-        <v>16.6982</v>
+        <v>14.5232</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4866</v>
+        <v>0.4196</v>
       </c>
       <c r="J168" t="n">
-        <v>14.1114</v>
+        <v>12.1684</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1005</v>
+        <v>0.1148</v>
       </c>
       <c r="J169" t="n">
-        <v>2.9145</v>
+        <v>3.3292</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0579</v>
+        <v>-0.0132</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.6791</v>
+        <v>-0.3828</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.96</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1582</v>
+        <v>-0.078</v>
       </c>
       <c r="J171" t="n">
-        <v>-4.5878</v>
+        <v>-2.262</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6228</v>
+        <v>1.4159</v>
       </c>
       <c r="J172" t="n">
-        <v>32.456</v>
+        <v>28.318</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.4</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8582</v>
+        <v>0.9615</v>
       </c>
       <c r="J173" t="n">
-        <v>17.164</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.38</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8126</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>16.252</v>
+        <v>18.458</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7901</v>
+        <v>0.9023</v>
       </c>
       <c r="J175" t="n">
-        <v>15.802</v>
+        <v>18.046</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.28</v>
       </c>
       <c r="I176" t="n">
-        <v>0.5883</v>
+        <v>0.7024</v>
       </c>
       <c r="J176" t="n">
-        <v>11.766</v>
+        <v>14.048</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2412</v>
+        <v>0.2425</v>
       </c>
       <c r="J177" t="n">
-        <v>4.824</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.86</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.122</v>
+        <v>-0.1231</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.44</v>
+        <v>-2.462</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5111</v>
+        <v>-0.3551</v>
       </c>
       <c r="J179" t="n">
-        <v>-10.222</v>
+        <v>-7.102</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.54</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4385</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.914</v>
+        <v>-8.77</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.24</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.021</v>
+        <v>-0.7209</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.42</v>
+        <v>-14.418</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0606</v>
+        <v>1.0246</v>
       </c>
       <c r="J182" t="n">
-        <v>28.6362</v>
+        <v>27.6642</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4874</v>
+        <v>0.4479</v>
       </c>
       <c r="J183" t="n">
-        <v>13.1598</v>
+        <v>12.0933</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1136</v>
+        <v>0.1234</v>
       </c>
       <c r="J184" t="n">
-        <v>3.0672</v>
+        <v>3.3318</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4438</v>
+        <v>-0.3879</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.9826</v>
+        <v>-10.4733</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8248</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>-22.2696</v>
+        <v>-21.1896</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.437</v>
+        <v>0.5254</v>
       </c>
       <c r="J187" t="n">
-        <v>11.799</v>
+        <v>14.1858</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.23</v>
       </c>
       <c r="I188" t="n">
-        <v>0.381</v>
+        <v>0.4573</v>
       </c>
       <c r="J188" t="n">
-        <v>10.287</v>
+        <v>12.3471</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.141</v>
+        <v>0.2045</v>
       </c>
       <c r="J189" t="n">
-        <v>3.807</v>
+        <v>5.5215</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0667</v>
+        <v>0.1194</v>
       </c>
       <c r="J190" t="n">
-        <v>1.8009</v>
+        <v>3.2238</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.02</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0039</v>
+        <v>0.0456</v>
       </c>
       <c r="J191" t="n">
-        <v>0.1053</v>
+        <v>1.2312</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.53</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3017</v>
+        <v>1.1905</v>
       </c>
       <c r="J192" t="n">
-        <v>35.1459</v>
+        <v>32.1435</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.46</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1614</v>
+        <v>1.0997</v>
       </c>
       <c r="J193" t="n">
-        <v>31.3578</v>
+        <v>29.6919</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4447</v>
+        <v>0.4692</v>
       </c>
       <c r="J194" t="n">
-        <v>12.0069</v>
+        <v>12.6684</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5183</v>
+        <v>-0.4504</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.9941</v>
+        <v>-12.1608</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7902</v>
+        <v>-0.7421</v>
       </c>
       <c r="J196" t="n">
-        <v>-21.3354</v>
+        <v>-20.0367</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.07</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2249</v>
+        <v>0.2223</v>
       </c>
       <c r="J197" t="n">
-        <v>6.0723</v>
+        <v>6.0021</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1469</v>
+        <v>0.1258</v>
       </c>
       <c r="J198" t="n">
-        <v>3.9663</v>
+        <v>3.3966</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.82</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3133</v>
+        <v>-0.2035</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.459099999999999</v>
+        <v>-5.4945</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4066</v>
+        <v>-0.2627</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.9782</v>
+        <v>-7.0929</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5194</v>
+        <v>-0.3395</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.0238</v>
+        <v>-9.166499999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2114</v>
+        <v>1.1362</v>
       </c>
       <c r="J202" t="n">
-        <v>30.285</v>
+        <v>28.405</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8944</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>22.36</v>
+        <v>22.5175</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8944</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>22.36</v>
+        <v>22.5175</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1312</v>
+        <v>-0.0541</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.28</v>
+        <v>-1.3525</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4548</v>
+        <v>-0.3797</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.37</v>
+        <v>-9.4925</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1629</v>
+        <v>0.1554</v>
       </c>
       <c r="J207" t="n">
-        <v>4.0725</v>
+        <v>3.885</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1217</v>
+        <v>0.1066</v>
       </c>
       <c r="J208" t="n">
-        <v>3.0425</v>
+        <v>2.665</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.99</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0029</v>
+        <v>-0.0147</v>
       </c>
       <c r="J209" t="n">
-        <v>0.0725</v>
+        <v>-0.3675</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.785</v>
+        <v>-5.5275</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.532500000000001</v>
+        <v>-6.0275</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2301</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>49.204</v>
+        <v>34.616</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5131</v>
+        <v>0.4099</v>
       </c>
       <c r="J213" t="n">
-        <v>20.524</v>
+        <v>16.396</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.589</v>
+        <v>-0.541</v>
       </c>
       <c r="J214" t="n">
-        <v>-23.56</v>
+        <v>-21.64</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.79</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6908</v>
+        <v>-0.6459</v>
       </c>
       <c r="J215" t="n">
-        <v>-27.632</v>
+        <v>-25.836</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7399</v>
+        <v>-0.6972</v>
       </c>
       <c r="J216" t="n">
-        <v>-29.596</v>
+        <v>-27.888</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.26</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4266</v>
+        <v>0.4382</v>
       </c>
       <c r="J217" t="n">
-        <v>17.064</v>
+        <v>17.528</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.16</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2781</v>
+        <v>0.3323</v>
       </c>
       <c r="J218" t="n">
-        <v>11.124</v>
+        <v>13.292</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2614</v>
+        <v>0.3171</v>
       </c>
       <c r="J219" t="n">
-        <v>10.456</v>
+        <v>12.684</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1081</v>
+        <v>0.1649</v>
       </c>
       <c r="J220" t="n">
-        <v>4.324</v>
+        <v>6.596</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1327</v>
+        <v>-0.0623</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.308</v>
+        <v>-2.492</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.25</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4647</v>
+        <v>0.3812</v>
       </c>
       <c r="J222" t="n">
-        <v>13.941</v>
+        <v>11.436</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0551</v>
       </c>
       <c r="J223" t="n">
-        <v>2.52</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1805</v>
+        <v>-0.1083</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.415</v>
+        <v>-3.249</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2999</v>
+        <v>-0.1842</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.997</v>
+        <v>-5.526</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.274</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6359</v>
+        <v>0.4631</v>
       </c>
       <c r="J227" t="n">
-        <v>19.077</v>
+        <v>13.893</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1994</v>
+        <v>0.1654</v>
       </c>
       <c r="J228" t="n">
-        <v>5.982</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1392</v>
+        <v>0.1225</v>
       </c>
       <c r="J229" t="n">
-        <v>4.176</v>
+        <v>3.675</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.04</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0704</v>
+        <v>0.076</v>
       </c>
       <c r="J230" t="n">
-        <v>2.112</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5058</v>
+        <v>-0.3246</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.174</v>
+        <v>-9.738</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3499</v>
+        <v>0.9462</v>
       </c>
       <c r="J232" t="n">
-        <v>36.4473</v>
+        <v>25.5474</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.28</v>
       </c>
       <c r="I233" t="n">
-        <v>0.8202</v>
+        <v>0.6039</v>
       </c>
       <c r="J233" t="n">
-        <v>22.1454</v>
+        <v>16.3053</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.494</v>
+        <v>0.4108</v>
       </c>
       <c r="J234" t="n">
-        <v>13.338</v>
+        <v>11.0916</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6429</v>
+        <v>-0.5886</v>
       </c>
       <c r="J235" t="n">
-        <v>-17.3583</v>
+        <v>-15.8922</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.2215</v>
+        <v>-1.2264</v>
       </c>
       <c r="J236" t="n">
-        <v>-32.9805</v>
+        <v>-33.1128</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5515</v>
+        <v>0.525</v>
       </c>
       <c r="J237" t="n">
-        <v>14.8905</v>
+        <v>14.175</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.12</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2673</v>
+        <v>0.2909</v>
       </c>
       <c r="J238" t="n">
-        <v>7.2171</v>
+        <v>7.8543</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2226</v>
+        <v>-0.1325</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.0102</v>
+        <v>-3.5775</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3798</v>
+        <v>-0.2371</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.2546</v>
+        <v>-6.4017</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4085</v>
+        <v>-0.257</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.0295</v>
+        <v>-6.939</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.05</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1828</v>
+        <v>0.1714</v>
       </c>
       <c r="J242" t="n">
-        <v>4.9356</v>
+        <v>4.6278</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.95</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0658</v>
+        <v>-0.0648</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.7766</v>
+        <v>-1.7496</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.83</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.302</v>
+        <v>-0.1948</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.154</v>
+        <v>-5.2596</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3344</v>
+        <v>-0.2149</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.0288</v>
+        <v>-5.8023</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3807</v>
+        <v>-0.2447</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.2789</v>
+        <v>-6.6069</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9247</v>
+        <v>0.6786</v>
       </c>
       <c r="J247" t="n">
-        <v>24.9669</v>
+        <v>18.3222</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.34</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9025</v>
+        <v>0.6651</v>
       </c>
       <c r="J248" t="n">
-        <v>24.3675</v>
+        <v>17.9577</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3136</v>
+        <v>0.3524</v>
       </c>
       <c r="J249" t="n">
-        <v>8.4672</v>
+        <v>9.514799999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3136</v>
+        <v>0.3524</v>
       </c>
       <c r="J250" t="n">
-        <v>8.4672</v>
+        <v>9.514799999999999</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4657</v>
+        <v>-0.3948</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.5739</v>
+        <v>-10.6596</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2621</v>
+        <v>0.2044</v>
       </c>
       <c r="J252" t="n">
-        <v>7.863</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2456</v>
+        <v>0.1902</v>
       </c>
       <c r="J253" t="n">
-        <v>7.368</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.1</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2287</v>
+        <v>0.1758</v>
       </c>
       <c r="J254" t="n">
-        <v>6.861</v>
+        <v>5.274</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0498</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.739</v>
+        <v>-1.494</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5329</v>
+        <v>-0.3455</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.987</v>
+        <v>-10.365</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5723</v>
+        <v>0.4479</v>
       </c>
       <c r="J257" t="n">
-        <v>17.169</v>
+        <v>13.437</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2959</v>
+        <v>0.2566</v>
       </c>
       <c r="J258" t="n">
-        <v>8.877000000000001</v>
+        <v>7.698</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1584</v>
+        <v>0.135</v>
       </c>
       <c r="J259" t="n">
-        <v>4.752</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3028</v>
+        <v>-0.1816</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.084</v>
+        <v>-5.448</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.75</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4607</v>
+        <v>-0.2923</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.821</v>
+        <v>-8.769</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I262" t="n">
-        <v>0.0944</v>
+        <v>0.0649</v>
       </c>
       <c r="J262" t="n">
-        <v>2.6432</v>
+        <v>1.8172</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.93</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J263" t="n">
-        <v>-2.9596</v>
+        <v>-2.4976</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1252</v>
+        <v>-0.1009</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.5056</v>
+        <v>-2.8252</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.79</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3655</v>
+        <v>-0.2348</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.234</v>
+        <v>-6.5744</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3957</v>
+        <v>-0.2545</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.0796</v>
+        <v>-7.126</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3037</v>
+        <v>0.9179</v>
       </c>
       <c r="J267" t="n">
-        <v>36.5036</v>
+        <v>25.7012</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7464</v>
+        <v>0.571</v>
       </c>
       <c r="J268" t="n">
-        <v>20.8992</v>
+        <v>15.988</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I269" t="n">
-        <v>0.1363</v>
+        <v>0.1949</v>
       </c>
       <c r="J269" t="n">
-        <v>3.8164</v>
+        <v>5.4572</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1649</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.6172</v>
+        <v>-2.5844</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3756</v>
+        <v>-0.3026</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.5168</v>
+        <v>-8.472799999999999</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.93</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0623</v>
+        <v>-0.0735</v>
       </c>
       <c r="J272" t="n">
-        <v>-1.4329</v>
+        <v>-1.6905</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1515</v>
+        <v>-0.132</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.4845</v>
+        <v>-3.036</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2203</v>
+        <v>-0.1749</v>
       </c>
       <c r="J274" t="n">
-        <v>-5.0669</v>
+        <v>-4.0227</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4806</v>
+        <v>-0.3186</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.0538</v>
+        <v>-7.3278</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5918</v>
+        <v>-0.3939</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.6114</v>
+        <v>-9.059699999999999</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.67</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4945</v>
+        <v>1.0509</v>
       </c>
       <c r="J277" t="n">
-        <v>34.3735</v>
+        <v>24.1707</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0197</v>
+        <v>0.756</v>
       </c>
       <c r="J278" t="n">
-        <v>23.4531</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.3</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6983</v>
+        <v>0.5915</v>
       </c>
       <c r="J279" t="n">
-        <v>16.0609</v>
+        <v>13.6045</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4737</v>
+        <v>0.4687</v>
       </c>
       <c r="J280" t="n">
-        <v>10.8951</v>
+        <v>10.7801</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2958</v>
+        <v>-0.2098</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.8034</v>
+        <v>-4.8254</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.1018</v>
+        <v>0.0709</v>
       </c>
       <c r="J282" t="n">
-        <v>3.563</v>
+        <v>2.4815</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.88</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1922</v>
+        <v>-0.1427</v>
       </c>
       <c r="J283" t="n">
-        <v>-6.727</v>
+        <v>-4.9945</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2129</v>
+        <v>-0.1529</v>
       </c>
       <c r="J284" t="n">
-        <v>-7.4515</v>
+        <v>-5.3515</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2381</v>
+        <v>-0.1628</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.333500000000001</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.681</v>
+        <v>-10.8535</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1223</v>
+        <v>0.8008</v>
       </c>
       <c r="J287" t="n">
-        <v>39.2805</v>
+        <v>28.028</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8855</v>
+        <v>0.6536</v>
       </c>
       <c r="J288" t="n">
-        <v>30.9925</v>
+        <v>22.876</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3812</v>
+        <v>0.3846</v>
       </c>
       <c r="J289" t="n">
-        <v>13.342</v>
+        <v>13.461</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2448</v>
+        <v>-0.1707</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.568</v>
+        <v>-5.9745</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4624</v>
+        <v>-0.3922</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.184</v>
+        <v>-13.727</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.96</v>
       </c>
       <c r="I292" t="n">
-        <v>1.8308</v>
+        <v>1.3411</v>
       </c>
       <c r="J292" t="n">
-        <v>36.616</v>
+        <v>26.822</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.82</v>
       </c>
       <c r="I293" t="n">
-        <v>1.6761</v>
+        <v>1.1846</v>
       </c>
       <c r="J293" t="n">
-        <v>33.522</v>
+        <v>23.692</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>1.2488</v>
+        <v>0.9223</v>
       </c>
       <c r="J294" t="n">
-        <v>24.976</v>
+        <v>18.446</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2619</v>
+        <v>0.3543</v>
       </c>
       <c r="J295" t="n">
-        <v>5.238</v>
+        <v>7.086</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.07</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0512</v>
+        <v>0.1446</v>
       </c>
       <c r="J296" t="n">
-        <v>1.024</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I297" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0484</v>
       </c>
       <c r="J297" t="n">
-        <v>1.516</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.68</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3454</v>
+        <v>-0.2862</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.908</v>
+        <v>-5.724</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.41</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.7873</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>-15.746</v>
+        <v>-10.836</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.8279</v>
+        <v>-0.5708</v>
       </c>
       <c r="J300" t="n">
-        <v>-16.558</v>
+        <v>-11.416</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.37</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.8411999999999999</v>
+        <v>-0.5805</v>
       </c>
       <c r="J301" t="n">
-        <v>-16.824</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.5588</v>
+        <v>1.088</v>
       </c>
       <c r="J302" t="n">
-        <v>42.0876</v>
+        <v>29.376</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.436</v>
+        <v>0.4005</v>
       </c>
       <c r="J303" t="n">
-        <v>11.772</v>
+        <v>10.8135</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.176</v>
+        <v>0.2288</v>
       </c>
       <c r="J304" t="n">
-        <v>4.752</v>
+        <v>6.1776</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.95</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3078</v>
+        <v>-0.2355</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.310600000000001</v>
+        <v>-6.3585</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.88</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5125</v>
+        <v>-0.4457</v>
       </c>
       <c r="J306" t="n">
-        <v>-13.8375</v>
+        <v>-12.0339</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.23</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4507</v>
+        <v>0.4436</v>
       </c>
       <c r="J307" t="n">
-        <v>12.1689</v>
+        <v>11.9772</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1006</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J308" t="n">
-        <v>2.7162</v>
+        <v>2.1897</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0893</v>
+        <v>-0.0702</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.4111</v>
+        <v>-1.8954</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3801</v>
+        <v>-0.2406</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.2627</v>
+        <v>-6.4962</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5589</v>
+        <v>-0.3658</v>
       </c>
       <c r="J311" t="n">
-        <v>-15.0903</v>
+        <v>-9.8766</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.9686</v>
+        <v>0.7055</v>
       </c>
       <c r="J312" t="n">
-        <v>29.058</v>
+        <v>21.165</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6917</v>
+        <v>0.5413</v>
       </c>
       <c r="J313" t="n">
-        <v>20.751</v>
+        <v>16.239</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.23</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6414</v>
+        <v>0.5132</v>
       </c>
       <c r="J314" t="n">
-        <v>19.242</v>
+        <v>15.396</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.11</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2841</v>
+        <v>0.3338</v>
       </c>
       <c r="J315" t="n">
-        <v>8.523</v>
+        <v>10.014</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5467</v>
+        <v>-0.4799</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.401</v>
+        <v>-14.397</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.486</v>
+        <v>0.4719</v>
       </c>
       <c r="J317" t="n">
-        <v>14.58</v>
+        <v>14.157</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3883</v>
+        <v>0.3958</v>
       </c>
       <c r="J318" t="n">
-        <v>11.649</v>
+        <v>11.874</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2259</v>
+        <v>-0.1393</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.777</v>
+        <v>-4.179</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.71</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4963</v>
+        <v>-0.3204</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.889</v>
+        <v>-9.612</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.68</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.536</v>
+        <v>-0.3489</v>
       </c>
       <c r="J321" t="n">
-        <v>-16.08</v>
+        <v>-10.467</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>1.1574</v>
+        <v>0.8214</v>
       </c>
       <c r="J322" t="n">
-        <v>33.5646</v>
+        <v>23.8206</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.6653</v>
+        <v>0.5194</v>
       </c>
       <c r="J323" t="n">
-        <v>19.2937</v>
+        <v>15.0626</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.11</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3117</v>
+        <v>0.3395</v>
       </c>
       <c r="J324" t="n">
-        <v>9.039300000000001</v>
+        <v>9.845499999999999</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0474</v>
+        <v>0.1025</v>
       </c>
       <c r="J325" t="n">
-        <v>1.3746</v>
+        <v>2.9725</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6622</v>
+        <v>-0.6049</v>
       </c>
       <c r="J326" t="n">
-        <v>-19.2038</v>
+        <v>-17.5421</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.22</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4282</v>
+        <v>0.427</v>
       </c>
       <c r="J327" t="n">
-        <v>12.4178</v>
+        <v>12.383</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.12</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2785</v>
+        <v>0.2999</v>
       </c>
       <c r="J328" t="n">
-        <v>8.076499999999999</v>
+        <v>8.697100000000001</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0824</v>
+        <v>-0.0597</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.3896</v>
+        <v>-1.7313</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.74</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4574</v>
+        <v>-0.2925</v>
       </c>
       <c r="J330" t="n">
-        <v>-13.2646</v>
+        <v>-8.4825</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.73</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4711</v>
+        <v>-0.3022</v>
       </c>
       <c r="J331" t="n">
-        <v>-13.6619</v>
+        <v>-8.7638</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.54</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2639</v>
+        <v>0.9004</v>
       </c>
       <c r="J332" t="n">
-        <v>32.8614</v>
+        <v>23.4104</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.27</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6502</v>
+        <v>0.5556</v>
       </c>
       <c r="J333" t="n">
-        <v>16.9052</v>
+        <v>14.4456</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.27</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6502</v>
+        <v>0.5556</v>
       </c>
       <c r="J334" t="n">
-        <v>16.9052</v>
+        <v>14.4456</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.16</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3641</v>
+        <v>0.3999</v>
       </c>
       <c r="J335" t="n">
-        <v>9.4666</v>
+        <v>10.3974</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.15</v>
       </c>
       <c r="I336" t="n">
-        <v>0.3379</v>
+        <v>0.3847</v>
       </c>
       <c r="J336" t="n">
-        <v>8.785399999999999</v>
+        <v>10.0022</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.02</v>
       </c>
       <c r="I337" t="n">
-        <v>0.1236</v>
+        <v>0.098</v>
       </c>
       <c r="J337" t="n">
-        <v>3.2136</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0406</v>
+        <v>-0.0503</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.0556</v>
+        <v>-1.3078</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2627</v>
+        <v>-0.1735</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.8302</v>
+        <v>-4.511</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2627</v>
+        <v>-0.1735</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.8302</v>
+        <v>-4.511</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5063</v>
+        <v>-0.3303</v>
       </c>
       <c r="J341" t="n">
-        <v>-13.1638</v>
+        <v>-8.5878</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.64</v>
       </c>
       <c r="I342" t="n">
-        <v>1.444</v>
+        <v>1.0174</v>
       </c>
       <c r="J342" t="n">
-        <v>33.212</v>
+        <v>23.4002</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.62</v>
       </c>
       <c r="I343" t="n">
-        <v>1.4063</v>
+        <v>0.9931</v>
       </c>
       <c r="J343" t="n">
-        <v>32.3449</v>
+        <v>22.8413</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8465</v>
+        <v>0.656</v>
       </c>
       <c r="J344" t="n">
-        <v>19.4695</v>
+        <v>15.088</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.21</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4793</v>
+        <v>0.4702</v>
       </c>
       <c r="J345" t="n">
-        <v>11.0239</v>
+        <v>10.8146</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9458</v>
       </c>
       <c r="J346" t="n">
-        <v>-22.4089</v>
+        <v>-21.7534</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>0.0285</v>
+        <v>-0.011</v>
       </c>
       <c r="J347" t="n">
-        <v>0.6555</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.87</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1818</v>
+        <v>-0.1472</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.1814</v>
+        <v>-3.3856</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2352</v>
+        <v>-0.1784</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.4096</v>
+        <v>-4.1032</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3528</v>
+        <v>-0.2361</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.1144</v>
+        <v>-5.4303</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.61</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5986</v>
+        <v>-0.3977</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.7678</v>
+        <v>-9.1471</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5607/event_5607_evp_summary.xlsx
+++ b/database/event/5607/event_5607_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.4359</v>
+        <v>8.474600000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7614</v>
+        <v>2.7741</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1704</v>
+        <v>3.2336</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4359</v>
+        <v>8.474600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8349</v>
+        <v>2.5322</v>
       </c>
       <c r="G2" t="n">
-        <v>5.601</v>
+        <v>5.9424</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8651</v>
+        <v>2.8172</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1057</v>
+        <v>2.9643</v>
       </c>
       <c r="J2" t="n">
-        <v>5.601</v>
+        <v>5.9424</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>219</v>
       </c>
       <c r="M2" t="n">
-        <v>8.7067</v>
+        <v>8.906700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0956</v>
+        <v>7.5134</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3227</v>
+        <v>2.4594</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5653</v>
+        <v>2.7961</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0956</v>
+        <v>7.5134</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7517</v>
+        <v>1.8097</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3438</v>
+        <v>5.7037</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7517</v>
+        <v>1.8097</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8988</v>
+        <v>1.9042</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3438</v>
+        <v>5.7037</v>
       </c>
       <c r="K3" t="n">
         <v>45</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.242599999999999</v>
+        <v>7.607900000000001</v>
       </c>
       <c r="N3" t="n">
         <v>250</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6569</v>
+        <v>6.836</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1791</v>
+        <v>2.2377</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3672</v>
+        <v>2.4877</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6569</v>
+        <v>6.836</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9914</v>
+        <v>1.9789</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6655</v>
+        <v>4.8571</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9914</v>
+        <v>1.9789</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1586</v>
+        <v>2.0822</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6655</v>
+        <v>4.8571</v>
       </c>
       <c r="K4" t="n">
         <v>45</v>
@@ -621,7 +621,7 @@
         <v>205</v>
       </c>
       <c r="M4" t="n">
-        <v>6.8241</v>
+        <v>6.939299999999999</v>
       </c>
       <c r="N4" t="n">
         <v>250</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.4341</v>
+        <v>6.7087</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1061</v>
+        <v>2.196</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2667</v>
+        <v>2.4297</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4341</v>
+        <v>6.7087</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4848</v>
+        <v>2.3991</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9493</v>
+        <v>4.3096</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4848</v>
+        <v>2.526</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8042</v>
+        <v>2.7264</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9493</v>
+        <v>4.3096</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>227</v>
       </c>
       <c r="M5" t="n">
-        <v>6.7535</v>
+        <v>7.036</v>
       </c>
       <c r="N5" t="n">
         <v>359</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9479</v>
+        <v>6.1988</v>
       </c>
       <c r="C6" t="n">
-        <v>1.947</v>
+        <v>2.0291</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0472</v>
+        <v>2.1976</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9479</v>
+        <v>6.1988</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3024</v>
+        <v>2.3059</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6455</v>
+        <v>3.8929</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3024</v>
+        <v>2.3219</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4957</v>
+        <v>2.4431</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6455</v>
+        <v>3.8929</v>
       </c>
       <c r="K6" t="n">
         <v>45</v>
@@ -713,7 +713,7 @@
         <v>205</v>
       </c>
       <c r="M6" t="n">
-        <v>6.1412</v>
+        <v>6.336</v>
       </c>
       <c r="N6" t="n">
         <v>250</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2696</v>
+        <v>4.6414</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3976</v>
+        <v>1.5193</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2895</v>
+        <v>1.4887</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2696</v>
+        <v>4.6414</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0556</v>
+        <v>1.0465</v>
       </c>
       <c r="G7" t="n">
-        <v>3.214</v>
+        <v>3.5949</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0556</v>
+        <v>1.0465</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1913</v>
+        <v>1.1295</v>
       </c>
       <c r="J7" t="n">
-        <v>3.214</v>
+        <v>3.5949</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>227</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4053</v>
+        <v>4.7244</v>
       </c>
       <c r="N7" t="n">
         <v>359</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8286</v>
+        <v>2.607</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.8534</v>
       </c>
       <c r="D8" t="n">
-        <v>0.639</v>
+        <v>0.5626</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8286</v>
+        <v>2.607</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6989</v>
+        <v>2.4787</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1297</v>
+        <v>0.1283</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6989</v>
+        <v>2.7002</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9255</v>
+        <v>2.8412</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1297</v>
+        <v>0.1283</v>
       </c>
       <c r="K8" t="n">
         <v>76</v>
@@ -805,7 +805,7 @@
         <v>134</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0552</v>
+        <v>2.9695</v>
       </c>
       <c r="N8" t="n">
         <v>210</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2759</v>
+        <v>2.3205</v>
       </c>
       <c r="C9" t="n">
-        <v>0.745</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3894</v>
+        <v>0.4321</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2759</v>
+        <v>2.3205</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8455</v>
+        <v>1.8104</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4304</v>
+        <v>0.5101</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8455</v>
+        <v>1.8104</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0004</v>
+        <v>1.9049</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4304</v>
+        <v>0.5101</v>
       </c>
       <c r="K9" t="n">
         <v>52</v>
@@ -851,7 +851,7 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4308</v>
+        <v>2.415</v>
       </c>
       <c r="N9" t="n">
         <v>183</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.16</v>
+        <v>2.2923</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7071</v>
+        <v>0.7504</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3371</v>
+        <v>0.4193</v>
       </c>
       <c r="E10" t="n">
-        <v>2.16</v>
+        <v>2.2923</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0484</v>
+        <v>1.062</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1116</v>
+        <v>1.2303</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0484</v>
+        <v>1.062</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1364</v>
+        <v>1.1174</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1116</v>
+        <v>1.2303</v>
       </c>
       <c r="K10" t="n">
         <v>52</v>
@@ -897,7 +897,7 @@
         <v>131</v>
       </c>
       <c r="M10" t="n">
-        <v>2.248</v>
+        <v>2.3477</v>
       </c>
       <c r="N10" t="n">
         <v>183</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9399</v>
+        <v>2.089</v>
       </c>
       <c r="C11" t="n">
-        <v>0.635</v>
+        <v>0.6838</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2378</v>
+        <v>0.3268</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9399</v>
+        <v>2.089</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6013</v>
+        <v>1.6398</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3386</v>
+        <v>0.4492</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6013</v>
+        <v>1.6398</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8071</v>
+        <v>1.7699</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3386</v>
+        <v>0.4492</v>
       </c>
       <c r="K11" t="n">
         <v>132</v>
@@ -943,7 +943,7 @@
         <v>227</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1457</v>
+        <v>2.2191</v>
       </c>
       <c r="N11" t="n">
         <v>359</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.91</v>
+        <v>2.0699</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6252</v>
+        <v>0.6776</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2243</v>
+        <v>0.3181</v>
       </c>
       <c r="E12" t="n">
-        <v>1.91</v>
+        <v>2.0699</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2265</v>
+        <v>1.2259</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6835</v>
+        <v>0.844</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2265</v>
+        <v>1.2259</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3295</v>
+        <v>1.2899</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6835</v>
+        <v>0.844</v>
       </c>
       <c r="K12" t="n">
         <v>45</v>
@@ -989,7 +989,7 @@
         <v>205</v>
       </c>
       <c r="M12" t="n">
-        <v>2.013</v>
+        <v>2.1339</v>
       </c>
       <c r="N12" t="n">
         <v>250</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8761</v>
+        <v>1.976</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6141</v>
+        <v>0.6468</v>
       </c>
       <c r="D13" t="n">
-        <v>0.209</v>
+        <v>0.2753</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8761</v>
+        <v>1.976</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8502</v>
+        <v>0.8274</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0259</v>
+        <v>1.1486</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8502</v>
+        <v>0.8274</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9216</v>
+        <v>0.8706</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0259</v>
+        <v>1.1486</v>
       </c>
       <c r="K13" t="n">
         <v>76</v>
@@ -1035,7 +1035,7 @@
         <v>134</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9475</v>
+        <v>2.0192</v>
       </c>
       <c r="N13" t="n">
         <v>210</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7743</v>
+        <v>1.9603</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5808</v>
+        <v>0.6417</v>
       </c>
       <c r="D14" t="n">
-        <v>0.163</v>
+        <v>0.2682</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7743</v>
+        <v>1.9603</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1313</v>
+        <v>-0.1454</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9056</v>
+        <v>2.1057</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1313</v>
+        <v>-0.1454</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1313</v>
+        <v>-0.1454</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9056</v>
+        <v>2.1057</v>
       </c>
       <c r="K14" t="n">
         <v>54</v>
@@ -1081,7 +1081,7 @@
         <v>229</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7743</v>
+        <v>1.9603</v>
       </c>
       <c r="N14" t="n">
         <v>283</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5401</v>
+        <v>1.7107</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5041</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0573</v>
+        <v>0.1545</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5401</v>
+        <v>1.7107</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6569</v>
+        <v>-0.6898</v>
       </c>
       <c r="G15" t="n">
-        <v>2.197</v>
+        <v>2.4005</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6569</v>
+        <v>-0.6898</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6569</v>
+        <v>-0.6898</v>
       </c>
       <c r="J15" t="n">
-        <v>2.197</v>
+        <v>2.4005</v>
       </c>
       <c r="K15" t="n">
         <v>54</v>
@@ -1127,7 +1127,7 @@
         <v>229</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5401</v>
+        <v>1.7107</v>
       </c>
       <c r="N15" t="n">
         <v>283</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4585</v>
+        <v>1.6202</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4774</v>
+        <v>0.5304</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0204</v>
+        <v>0.1133</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4585</v>
+        <v>1.6202</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7592</v>
+        <v>0.7341</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6993</v>
+        <v>0.8861</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7592</v>
+        <v>0.7341</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8568</v>
+        <v>0.7923</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6993</v>
+        <v>0.8861</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>227</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5561</v>
+        <v>1.6784</v>
       </c>
       <c r="N16" t="n">
         <v>359</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4584</v>
+        <v>1.5914</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4774</v>
+        <v>0.5209</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0204</v>
+        <v>0.1002</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4584</v>
+        <v>1.5914</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3506</v>
+        <v>-0.3867</v>
       </c>
       <c r="G17" t="n">
-        <v>1.809</v>
+        <v>1.9781</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3506</v>
+        <v>-0.3867</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.38</v>
+        <v>-0.4069</v>
       </c>
       <c r="J17" t="n">
-        <v>1.809</v>
+        <v>1.9781</v>
       </c>
       <c r="K17" t="n">
         <v>123</v>
@@ -1219,7 +1219,7 @@
         <v>219</v>
       </c>
       <c r="M17" t="n">
-        <v>1.429</v>
+        <v>1.5712</v>
       </c>
       <c r="N17" t="n">
         <v>342</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0819</v>
+        <v>1.0724</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3542</v>
+        <v>0.351</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1496</v>
+        <v>-0.136</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0819</v>
+        <v>1.0724</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2638</v>
+        <v>1.2444</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1819</v>
+        <v>-0.172</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2638</v>
+        <v>1.2444</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3699</v>
+        <v>1.3094</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1819</v>
+        <v>-0.172</v>
       </c>
       <c r="K18" t="n">
         <v>52</v>
@@ -1265,7 +1265,7 @@
         <v>131</v>
       </c>
       <c r="M18" t="n">
-        <v>1.188</v>
+        <v>1.1374</v>
       </c>
       <c r="N18" t="n">
         <v>183</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6387</v>
+        <v>0.7852</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2091</v>
+        <v>0.257</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3497</v>
+        <v>-0.2668</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6387</v>
+        <v>0.7852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3078</v>
+        <v>0.306</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3309</v>
+        <v>0.4792</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3078</v>
+        <v>0.306</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3336</v>
+        <v>0.322</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3309</v>
+        <v>0.4792</v>
       </c>
       <c r="K19" t="n">
         <v>123</v>
@@ -1311,7 +1311,7 @@
         <v>219</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6645000000000001</v>
+        <v>0.8012</v>
       </c>
       <c r="N19" t="n">
         <v>342</v>
@@ -1320,311 +1320,311 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4346</v>
+        <v>0.498</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1423</v>
+        <v>0.163</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4418</v>
+        <v>-0.3975</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4346</v>
+        <v>0.498</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0522</v>
+        <v>-0.6131</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6176</v>
+        <v>1.1111</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0522</v>
+        <v>-0.6131</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1405</v>
+        <v>-0.6131</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6176</v>
+        <v>1.1111</v>
       </c>
       <c r="K20" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L20" t="n">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5229</v>
+        <v>0.498</v>
       </c>
       <c r="N20" t="n">
-        <v>210</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4271</v>
+        <v>0.3926</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1398</v>
+        <v>0.1285</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4452</v>
+        <v>-0.4455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4271</v>
+        <v>0.3926</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5817</v>
+        <v>0.6409</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0088</v>
+        <v>-0.2483</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5817</v>
+        <v>0.6409</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5817</v>
+        <v>0.6744</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0088</v>
+        <v>-0.2483</v>
       </c>
       <c r="K21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L21" t="n">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4270999999999999</v>
+        <v>0.4261</v>
       </c>
       <c r="N21" t="n">
-        <v>283</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3665</v>
+        <v>0.3541</v>
       </c>
       <c r="C22" t="n">
-        <v>0.12</v>
+        <v>0.1159</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4726</v>
+        <v>-0.463</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3665</v>
+        <v>0.3541</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6327</v>
+        <v>1.0115</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2662</v>
+        <v>-0.6574</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6327</v>
+        <v>1.0115</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6858</v>
+        <v>1.0643</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2662</v>
+        <v>-0.6574</v>
       </c>
       <c r="K22" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4196</v>
+        <v>0.4069</v>
       </c>
       <c r="N22" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1864</v>
+        <v>0.2776</v>
       </c>
       <c r="C23" t="n">
-        <v>0.061</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.4978</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1864</v>
+        <v>0.2776</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4812</v>
+        <v>0.473</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2948</v>
+        <v>-0.1954</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4812</v>
+        <v>0.473</v>
       </c>
       <c r="I23" t="n">
-        <v>0.501</v>
+        <v>0.4977</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2948</v>
+        <v>-0.1954</v>
       </c>
       <c r="K23" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2062</v>
+        <v>0.3023</v>
       </c>
       <c r="N23" t="n">
-        <v>134</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1793</v>
+        <v>0.274</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0587</v>
+        <v>0.0897</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5571</v>
+        <v>-0.4995</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1793</v>
+        <v>0.274</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4657</v>
+        <v>0.0538</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2864</v>
+        <v>0.2202</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4657</v>
+        <v>0.0538</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5048</v>
+        <v>0.0566</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2864</v>
+        <v>0.2202</v>
       </c>
       <c r="K24" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2184</v>
+        <v>0.2768</v>
       </c>
       <c r="N24" t="n">
-        <v>250</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1441</v>
+        <v>0.1697</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0472</v>
+        <v>0.0555</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.573</v>
+        <v>-0.547</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1441</v>
+        <v>0.1697</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1084</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0357</v>
+        <v>0.7125</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1084</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1175</v>
+        <v>-0.5858</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0357</v>
+        <v>0.7125</v>
       </c>
       <c r="K25" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L25" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1532</v>
+        <v>0.1267</v>
       </c>
       <c r="N25" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1566</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0261</v>
+        <v>0.0513</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.602</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1566</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1837</v>
+        <v>0.487</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.104</v>
+        <v>-0.3304</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1837</v>
+        <v>0.487</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1913</v>
+        <v>0.4996</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.104</v>
+        <v>-0.3304</v>
       </c>
       <c r="K26" t="n">
         <v>76</v>
@@ -1633,7 +1633,7 @@
         <v>58</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0873</v>
+        <v>0.1692</v>
       </c>
       <c r="N26" t="n">
         <v>134</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0565</v>
+        <v>0.0931</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0185</v>
+        <v>0.0305</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6125</v>
+        <v>-0.5818</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0565</v>
+        <v>0.0931</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2727</v>
+        <v>-0.4508</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.2162</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2727</v>
+        <v>-0.4508</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2839</v>
+        <v>-0.4508</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2162</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L27" t="n">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="M27" t="n">
-        <v>0.06769999999999998</v>
+        <v>0.09310000000000007</v>
       </c>
       <c r="N27" t="n">
-        <v>134</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0111</v>
+        <v>0.061</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0036</v>
+        <v>0.02</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.633</v>
+        <v>-0.5964</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0111</v>
+        <v>0.061</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4168</v>
+        <v>0.1876</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4279</v>
+        <v>-0.1266</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4168</v>
+        <v>0.1876</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4168</v>
+        <v>0.1924</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4279</v>
+        <v>-0.1266</v>
       </c>
       <c r="K28" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L28" t="n">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0111</v>
+        <v>0.0658</v>
       </c>
       <c r="N28" t="n">
-        <v>283</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0054</v>
+        <v>0.0039</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0018</v>
+        <v>0.0013</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6405</v>
+        <v>-0.6224</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0054</v>
+        <v>0.0039</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5657</v>
+        <v>0.254</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5603</v>
+        <v>-0.2501</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5657</v>
+        <v>0.254</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6384</v>
+        <v>0.2605</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5603</v>
+        <v>-0.2501</v>
       </c>
       <c r="K29" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="L29" t="n">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07809999999999995</v>
+        <v>0.01040000000000002</v>
       </c>
       <c r="N29" t="n">
-        <v>359</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0479</v>
+        <v>-0.1045</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0157</v>
+        <v>-0.0342</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6596</v>
+        <v>-0.6718</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0479</v>
+        <v>-0.1045</v>
       </c>
       <c r="F30" t="n">
-        <v>0.135</v>
+        <v>0.1161</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1829</v>
+        <v>-0.2206</v>
       </c>
       <c r="H30" t="n">
-        <v>0.135</v>
+        <v>0.1161</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1463</v>
+        <v>0.1222</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1829</v>
+        <v>-0.2206</v>
       </c>
       <c r="K30" t="n">
         <v>76</v>
@@ -1817,7 +1817,7 @@
         <v>134</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.03659999999999999</v>
+        <v>-0.09839999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>210</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0752</v>
+        <v>-0.1102</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0246</v>
+        <v>-0.0361</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.672</v>
+        <v>-0.6744</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0752</v>
+        <v>-0.1102</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2812</v>
+        <v>0.2841</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3564</v>
+        <v>-0.3943</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2812</v>
+        <v>0.2841</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2812</v>
+        <v>0.2841</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3564</v>
+        <v>-0.3943</v>
       </c>
       <c r="K31" t="n">
         <v>52</v>
@@ -1863,7 +1863,7 @@
         <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.1102</v>
       </c>
       <c r="N31" t="n">
         <v>99</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1705</v>
+        <v>-0.1737</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0558</v>
+        <v>-0.0569</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.715</v>
+        <v>-0.7033</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1705</v>
+        <v>-0.1737</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3289</v>
+        <v>0.3304</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4994</v>
+        <v>-0.5041</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3289</v>
+        <v>0.3304</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3289</v>
+        <v>0.3304</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4994</v>
+        <v>-0.5041</v>
       </c>
       <c r="K32" t="n">
         <v>52</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1705</v>
+        <v>-0.1737</v>
       </c>
       <c r="N32" t="n">
         <v>99</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6168</v>
+        <v>-0.6392</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2019</v>
+        <v>-0.2092</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9165</v>
+        <v>-0.9152</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6168</v>
+        <v>-0.6392</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4246</v>
+        <v>-0.0618</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1922</v>
+        <v>-0.5774</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4246</v>
+        <v>-0.0618</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4246</v>
+        <v>-0.0634</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1922</v>
+        <v>-0.5774</v>
       </c>
       <c r="K33" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L33" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6168</v>
+        <v>-0.6408</v>
       </c>
       <c r="N33" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6233</v>
+        <v>-0.6666</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.204</v>
+        <v>-0.2182</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9194</v>
+        <v>-0.9277</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6233</v>
+        <v>-0.6666</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0054</v>
+        <v>-0.0056</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6287</v>
+        <v>-0.661</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0054</v>
+        <v>-0.0056</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0056</v>
+        <v>-0.0057</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6287</v>
+        <v>-0.661</v>
       </c>
       <c r="K34" t="n">
         <v>76</v>
@@ -2001,7 +2001,7 @@
         <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6231</v>
+        <v>-0.6667000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>134</v>
@@ -2010,81 +2010,81 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6243</v>
+        <v>-0.7024</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2044</v>
+        <v>-0.2299</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.944</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6243</v>
+        <v>-0.7024</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0775</v>
+        <v>-0.6098</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5468</v>
+        <v>-0.0926</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0775</v>
+        <v>-0.6098</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.6098</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5468</v>
+        <v>-0.0926</v>
       </c>
       <c r="K35" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L35" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.7024</v>
       </c>
       <c r="N35" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7078</v>
+        <v>-0.7216</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2317</v>
+        <v>-0.2362</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9576</v>
+        <v>-0.9527</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7078</v>
+        <v>-0.7216</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5806</v>
+        <v>-0.4568</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1272</v>
+        <v>-0.2648</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5806</v>
+        <v>-0.4568</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5806</v>
+        <v>-0.4568</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1272</v>
+        <v>-0.2648</v>
       </c>
       <c r="K36" t="n">
         <v>52</v>
@@ -2093,7 +2093,7 @@
         <v>47</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7078</v>
+        <v>-0.7216</v>
       </c>
       <c r="N36" t="n">
         <v>99</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7923</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2594</v>
+        <v>-0.2731</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9957</v>
+        <v>-1.0039</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7923</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1116</v>
+        <v>-0.1214</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6807</v>
+        <v>-0.7128</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1116</v>
+        <v>-0.1214</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.121</v>
+        <v>-0.1277</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6807</v>
+        <v>-0.7128</v>
       </c>
       <c r="K37" t="n">
         <v>76</v>
@@ -2139,7 +2139,7 @@
         <v>134</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8017</v>
+        <v>-0.8405</v>
       </c>
       <c r="N37" t="n">
         <v>210</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.185</v>
+        <v>-1.2302</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3879</v>
+        <v>-0.4027</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.173</v>
+        <v>-1.1842</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.185</v>
+        <v>-1.2302</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2774</v>
+        <v>-0.2998</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9076</v>
+        <v>-0.9304</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2774</v>
+        <v>-0.2998</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2774</v>
+        <v>-0.2998</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9076</v>
+        <v>-0.9304</v>
       </c>
       <c r="K38" t="n">
         <v>52</v>
@@ -2185,7 +2185,7 @@
         <v>47</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.185</v>
+        <v>-1.2302</v>
       </c>
       <c r="N38" t="n">
         <v>99</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2411</v>
+        <v>-1.2628</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4063</v>
+        <v>-0.4134</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1983</v>
+        <v>-1.1991</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2411</v>
+        <v>-1.2628</v>
       </c>
       <c r="F39" t="n">
-        <v>0.289</v>
+        <v>0.2534</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.5301</v>
+        <v>-1.5162</v>
       </c>
       <c r="H39" t="n">
-        <v>0.289</v>
+        <v>0.2534</v>
       </c>
       <c r="I39" t="n">
-        <v>0.289</v>
+        <v>0.2534</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5301</v>
+        <v>-1.5162</v>
       </c>
       <c r="K39" t="n">
         <v>54</v>
@@ -2231,7 +2231,7 @@
         <v>229</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2411</v>
+        <v>-1.2628</v>
       </c>
       <c r="N39" t="n">
         <v>283</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4536</v>
+        <v>-1.3912</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4758</v>
+        <v>-0.4554</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2942</v>
+        <v>-1.2575</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4536</v>
+        <v>-1.3912</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0349</v>
+        <v>-0.9917</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4187</v>
+        <v>-0.3995</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0349</v>
+        <v>-0.9917</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1218</v>
+        <v>-1.0435</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4187</v>
+        <v>-0.3995</v>
       </c>
       <c r="K40" t="n">
         <v>52</v>
@@ -2277,7 +2277,7 @@
         <v>131</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5405</v>
+        <v>-1.443</v>
       </c>
       <c r="N40" t="n">
         <v>183</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9687</v>
+        <v>-2.9203</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9718</v>
+        <v>-0.9559</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9782</v>
+        <v>-1.9536</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9687</v>
+        <v>-2.9203</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7415</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.2565</v>
+        <v>-2.1788</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7415</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.772</v>
+        <v>-0.7802</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.2565</v>
+        <v>-2.1788</v>
       </c>
       <c r="K41" t="n">
         <v>123</v>
@@ -2323,7 +2323,7 @@
         <v>219</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0285</v>
+        <v>-2.959</v>
       </c>
       <c r="N41" t="n">
         <v>342</v>
@@ -2429,10 +2429,10 @@
         <v>1.91</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6222</v>
+        <v>1.756</v>
       </c>
       <c r="J2" t="n">
-        <v>45.4216</v>
+        <v>49.168</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7991</v>
+        <v>0.7612</v>
       </c>
       <c r="J3" t="n">
-        <v>22.3748</v>
+        <v>21.3136</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4472</v>
+        <v>0.4462</v>
       </c>
       <c r="J4" t="n">
-        <v>12.5216</v>
+        <v>12.4936</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0298</v>
+        <v>0.0553</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8344</v>
+        <v>1.5484</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2346</v>
+        <v>-0.2177</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.5688</v>
+        <v>-6.0956</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3658</v>
+        <v>0.3533</v>
       </c>
       <c r="J7" t="n">
-        <v>10.2424</v>
+        <v>9.8924</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1397</v>
+        <v>-0.1568</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.9116</v>
+        <v>-4.3904</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1708</v>
+        <v>-0.1883</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.7824</v>
+        <v>-5.2724</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.76</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2585</v>
+        <v>-0.2757</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.238</v>
+        <v>-7.7196</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.58</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4289</v>
+        <v>-0.44</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.0092</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2441</v>
+        <v>0.243</v>
       </c>
       <c r="J12" t="n">
-        <v>5.3702</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1592</v>
+        <v>0.1597</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5024</v>
+        <v>3.5134</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2109</v>
+        <v>-0.2284</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.6398</v>
+        <v>-5.0248</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.7</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3175</v>
+        <v>-0.333</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.985</v>
+        <v>-7.326</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4394</v>
+        <v>-0.4498</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.6668</v>
+        <v>-9.8956</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6461</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>14.2142</v>
+        <v>14.2494</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.41</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5158</v>
+        <v>0.5255</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3476</v>
+        <v>11.561</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.31</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4042</v>
+        <v>0.4193</v>
       </c>
       <c r="J19" t="n">
-        <v>8.8924</v>
+        <v>9.224600000000001</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1603</v>
+        <v>0.1799</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5266</v>
+        <v>3.9578</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.89</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.171</v>
+        <v>-0.1783</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.762</v>
+        <v>-3.9226</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.57</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2036</v>
+        <v>1.2363</v>
       </c>
       <c r="J22" t="n">
-        <v>27.6828</v>
+        <v>28.4349</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9002</v>
+        <v>0.8518</v>
       </c>
       <c r="J23" t="n">
-        <v>20.7046</v>
+        <v>19.5914</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8142</v>
+        <v>0.7759</v>
       </c>
       <c r="J24" t="n">
-        <v>18.7266</v>
+        <v>17.8457</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7043</v>
+        <v>0.6783</v>
       </c>
       <c r="J25" t="n">
-        <v>16.1989</v>
+        <v>15.6009</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.125</v>
+        <v>0.1504</v>
       </c>
       <c r="J26" t="n">
-        <v>2.875</v>
+        <v>3.4592</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5259</v>
+        <v>0.491</v>
       </c>
       <c r="J27" t="n">
-        <v>12.0957</v>
+        <v>11.293</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2384</v>
+        <v>-0.2583</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.4832</v>
+        <v>-5.9409</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.74</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2659</v>
+        <v>-0.2855</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.1157</v>
+        <v>-6.5665</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.66</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3404</v>
+        <v>-0.3578</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8292</v>
+        <v>-8.2294</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6008</v>
+        <v>-0.6031</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.8184</v>
+        <v>-13.8713</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7814</v>
+        <v>0.7523</v>
       </c>
       <c r="J32" t="n">
-        <v>21.8792</v>
+        <v>21.0644</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3573</v>
+        <v>0.3614</v>
       </c>
       <c r="J33" t="n">
-        <v>10.0044</v>
+        <v>10.1192</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.232</v>
+        <v>-0.2448</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.496</v>
+        <v>-6.8544</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.252</v>
+        <v>-0.2646</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.056</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.76</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2815</v>
+        <v>-0.2937</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.882</v>
+        <v>-8.223599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3591</v>
+        <v>0.3707</v>
       </c>
       <c r="J37" t="n">
-        <v>10.0548</v>
+        <v>10.3796</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3467</v>
+        <v>0.3588</v>
       </c>
       <c r="J38" t="n">
-        <v>9.707599999999999</v>
+        <v>10.0464</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2318</v>
+        <v>0.2467</v>
       </c>
       <c r="J39" t="n">
-        <v>6.4904</v>
+        <v>6.9076</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0911</v>
+        <v>0.1039</v>
       </c>
       <c r="J40" t="n">
-        <v>2.5508</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3353</v>
+        <v>-0.3452</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.388400000000001</v>
+        <v>-9.6656</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3004</v>
+        <v>1.2703</v>
       </c>
       <c r="J42" t="n">
-        <v>35.1108</v>
+        <v>34.2981</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5728</v>
+        <v>0.5538</v>
       </c>
       <c r="J43" t="n">
-        <v>15.4656</v>
+        <v>14.9526</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J44" t="n">
-        <v>3.6477</v>
+        <v>4.0203</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1005</v>
+        <v>0.1153</v>
       </c>
       <c r="J45" t="n">
-        <v>2.7135</v>
+        <v>3.1131</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6593</v>
+        <v>-0.6142</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.8011</v>
+        <v>-16.5834</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.43</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8691</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>23.4657</v>
+        <v>22.1157</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1543</v>
+        <v>0.1587</v>
       </c>
       <c r="J48" t="n">
-        <v>4.1661</v>
+        <v>4.2849</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.191</v>
+        <v>-0.2062</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.157</v>
+        <v>-5.5674</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3002</v>
+        <v>-0.314</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.105399999999999</v>
+        <v>-8.478</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3854</v>
+        <v>-0.3964</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4058</v>
+        <v>-10.7028</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.225</v>
+        <v>1.1969</v>
       </c>
       <c r="J52" t="n">
-        <v>28.175</v>
+        <v>27.5287</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1003</v>
+        <v>1.0626</v>
       </c>
       <c r="J53" t="n">
-        <v>25.3069</v>
+        <v>24.4398</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.395</v>
+        <v>0.3988</v>
       </c>
       <c r="J54" t="n">
-        <v>9.085000000000001</v>
+        <v>9.1724</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3137</v>
+        <v>0.3244</v>
       </c>
       <c r="J55" t="n">
-        <v>7.2151</v>
+        <v>7.4612</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1348</v>
+        <v>0.1573</v>
       </c>
       <c r="J56" t="n">
-        <v>3.1004</v>
+        <v>3.6179</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0625</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.4375</v>
+        <v>-1.7434</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0625</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.4375</v>
+        <v>-1.7434</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.87</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.153</v>
+        <v>-0.1696</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.519</v>
+        <v>-3.9008</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.203</v>
+        <v>-0.2201</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.669</v>
+        <v>-5.0623</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2719</v>
+        <v>-0.2881</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.2537</v>
+        <v>-6.6263</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.36</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9643</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>32.7862</v>
+        <v>30.5898</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.4931</v>
       </c>
       <c r="J63" t="n">
-        <v>17.2584</v>
+        <v>16.7654</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4298</v>
+        <v>0.4226</v>
       </c>
       <c r="J64" t="n">
-        <v>14.6132</v>
+        <v>14.3684</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4035</v>
+        <v>0.3985</v>
       </c>
       <c r="J65" t="n">
-        <v>13.719</v>
+        <v>13.549</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.8491</v>
       </c>
       <c r="J66" t="n">
-        <v>-31.4466</v>
+        <v>-28.8694</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4857</v>
+        <v>0.4752</v>
       </c>
       <c r="J67" t="n">
-        <v>16.5138</v>
+        <v>16.1568</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.295</v>
+        <v>0.2971</v>
       </c>
       <c r="J68" t="n">
-        <v>10.03</v>
+        <v>10.1014</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.92</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1085</v>
+        <v>-0.1212</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.689</v>
+        <v>-4.1208</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.174</v>
+        <v>-0.1882</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.916</v>
+        <v>-6.3988</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3041</v>
+        <v>-0.3171</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3394</v>
+        <v>-10.7814</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.81</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4619</v>
+        <v>1.4549</v>
       </c>
       <c r="J72" t="n">
-        <v>29.238</v>
+        <v>29.098</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.68</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3116</v>
+        <v>1.2955</v>
       </c>
       <c r="J73" t="n">
-        <v>26.232</v>
+        <v>25.91</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8373</v>
+        <v>0.8004</v>
       </c>
       <c r="J74" t="n">
-        <v>16.746</v>
+        <v>16.008</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5847</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>11.694</v>
+        <v>11.542</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3579</v>
+        <v>0.3729</v>
       </c>
       <c r="J76" t="n">
-        <v>7.158</v>
+        <v>7.458</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.79</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1967</v>
+        <v>-0.2218</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.934</v>
+        <v>-4.436</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.68</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3083</v>
+        <v>-0.3296</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.166</v>
+        <v>-6.592</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.63</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3528</v>
+        <v>-0.3727</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.056</v>
+        <v>-7.454</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4077</v>
+        <v>-0.4249</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.154</v>
+        <v>-8.497999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4263</v>
+        <v>-0.4425</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.526</v>
+        <v>-8.85</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.84</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5149</v>
+        <v>1.5076</v>
       </c>
       <c r="J82" t="n">
-        <v>34.8427</v>
+        <v>34.6748</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.44</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0342</v>
+        <v>0.9886</v>
       </c>
       <c r="J83" t="n">
-        <v>23.7866</v>
+        <v>22.7378</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9883</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>22.7309</v>
+        <v>21.574</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4276</v>
+        <v>0.4326</v>
       </c>
       <c r="J85" t="n">
-        <v>9.8348</v>
+        <v>9.9498</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2878</v>
+        <v>-0.2635</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.6194</v>
+        <v>-6.0605</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1623</v>
+        <v>-0.1841</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.7329</v>
+        <v>-4.2343</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1731</v>
+        <v>-0.1948</v>
       </c>
       <c r="J88" t="n">
-        <v>-3.9813</v>
+        <v>-4.4804</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2149</v>
+        <v>-0.236</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.9427</v>
+        <v>-5.428</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3647</v>
+        <v>-0.3819</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.3881</v>
+        <v>-8.7837</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.52</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4676</v>
+        <v>-0.4793</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7548</v>
+        <v>-11.0239</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4615</v>
+        <v>1.4545</v>
       </c>
       <c r="J92" t="n">
-        <v>32.153</v>
+        <v>31.999</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.56</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1703</v>
+        <v>1.1442</v>
       </c>
       <c r="J93" t="n">
-        <v>25.7466</v>
+        <v>25.1724</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.37</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9019</v>
+        <v>0.8573</v>
       </c>
       <c r="J94" t="n">
-        <v>19.8418</v>
+        <v>18.8606</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.32</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7926</v>
+        <v>0.7612</v>
       </c>
       <c r="J95" t="n">
-        <v>17.4372</v>
+        <v>16.7464</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3839</v>
+        <v>0.3966</v>
       </c>
       <c r="J96" t="n">
-        <v>8.4458</v>
+        <v>8.725199999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0867</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J97" t="n">
-        <v>1.9074</v>
+        <v>1.3904</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.88</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1218</v>
+        <v>-0.1428</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.6796</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3021</v>
+        <v>-0.321</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.6462</v>
+        <v>-7.062</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3957</v>
+        <v>-0.4108</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.705399999999999</v>
+        <v>-9.037599999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.52</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4704</v>
+        <v>-0.4814</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.3488</v>
+        <v>-10.5908</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4002</v>
+        <v>0.4359</v>
       </c>
       <c r="J102" t="n">
-        <v>11.2056</v>
+        <v>12.2052</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.97</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0421</v>
+        <v>-0.0522</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.1788</v>
+        <v>-1.4616</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1777</v>
+        <v>-0.1935</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.9756</v>
+        <v>-5.418</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.84</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.188</v>
+        <v>-0.2038</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.264</v>
+        <v>-5.7064</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3823</v>
+        <v>-0.394</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.7044</v>
+        <v>-11.032</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5785</v>
       </c>
       <c r="J107" t="n">
-        <v>14.1848</v>
+        <v>16.198</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3455</v>
+        <v>0.3697</v>
       </c>
       <c r="J108" t="n">
-        <v>9.673999999999999</v>
+        <v>10.3516</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3177</v>
+        <v>0.3351</v>
       </c>
       <c r="J109" t="n">
-        <v>8.8956</v>
+        <v>9.3828</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0445</v>
+        <v>0.0587</v>
       </c>
       <c r="J110" t="n">
-        <v>1.246</v>
+        <v>1.6436</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.9</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1537</v>
+        <v>-0.1621</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.3036</v>
+        <v>-4.5388</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7866</v>
+        <v>0.8677</v>
       </c>
       <c r="J112" t="n">
-        <v>22.8114</v>
+        <v>25.1633</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7602</v>
+        <v>0.8391</v>
       </c>
       <c r="J113" t="n">
-        <v>22.0458</v>
+        <v>24.3339</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1292</v>
+        <v>0.1447</v>
       </c>
       <c r="J114" t="n">
-        <v>3.7468</v>
+        <v>4.1963</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0164</v>
+        <v>0.0333</v>
       </c>
       <c r="J115" t="n">
-        <v>0.4756</v>
+        <v>0.9657</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.364</v>
+        <v>-0.346</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.556</v>
+        <v>-10.034</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3685</v>
+        <v>0.3888</v>
       </c>
       <c r="J117" t="n">
-        <v>10.6865</v>
+        <v>11.2752</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2748</v>
+        <v>0.2778</v>
       </c>
       <c r="J118" t="n">
-        <v>7.9692</v>
+        <v>8.0562</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1459</v>
+        <v>0.1527</v>
       </c>
       <c r="J119" t="n">
-        <v>4.2311</v>
+        <v>4.4283</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1948</v>
+        <v>-0.2092</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.6492</v>
+        <v>-6.0668</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3517</v>
+        <v>-0.3633</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.1993</v>
+        <v>-10.5357</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.38</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7308</v>
+        <v>0.8051</v>
       </c>
       <c r="J122" t="n">
-        <v>20.4624</v>
+        <v>22.5428</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3882</v>
+        <v>0.4189</v>
       </c>
       <c r="J123" t="n">
-        <v>10.8696</v>
+        <v>11.7292</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2348</v>
+        <v>0.2424</v>
       </c>
       <c r="J124" t="n">
-        <v>6.5744</v>
+        <v>6.7872</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2348</v>
+        <v>0.2424</v>
       </c>
       <c r="J125" t="n">
-        <v>6.5744</v>
+        <v>6.7872</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3225</v>
+        <v>-0.3102</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.685600000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4505</v>
+        <v>0.4956</v>
       </c>
       <c r="J127" t="n">
-        <v>12.614</v>
+        <v>13.8768</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0479</v>
+        <v>0.0506</v>
       </c>
       <c r="J128" t="n">
-        <v>1.3412</v>
+        <v>1.4168</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0479</v>
+        <v>0.0506</v>
       </c>
       <c r="J129" t="n">
-        <v>1.3412</v>
+        <v>1.4168</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1061</v>
+        <v>-0.1194</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.9708</v>
+        <v>-3.3432</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4691</v>
+        <v>-0.4761</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.1348</v>
+        <v>-13.3308</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.73</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1387</v>
+        <v>1.2478</v>
       </c>
       <c r="J132" t="n">
-        <v>29.6062</v>
+        <v>32.4428</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7274</v>
+        <v>0.8077</v>
       </c>
       <c r="J133" t="n">
-        <v>18.9124</v>
+        <v>21.0002</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4178</v>
+        <v>0.4628</v>
       </c>
       <c r="J134" t="n">
-        <v>10.8628</v>
+        <v>12.0328</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2314</v>
+        <v>0.2473</v>
       </c>
       <c r="J135" t="n">
-        <v>6.0164</v>
+        <v>6.4298</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.417</v>
+        <v>-0.3897</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.842</v>
+        <v>-10.1322</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.97</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0234</v>
+        <v>-0.0376</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.9776</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0375</v>
+        <v>-0.0527</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.975</v>
+        <v>-1.3702</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1969</v>
+        <v>-0.2155</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.1194</v>
+        <v>-5.603</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2825</v>
+        <v>-0.3002</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.345</v>
+        <v>-7.8052</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.461</v>
+        <v>-0.4712</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.986</v>
+        <v>-12.2512</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2358</v>
+        <v>-0.2603</v>
       </c>
       <c r="J142" t="n">
-        <v>-4.9518</v>
+        <v>-5.4663</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.75</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2358</v>
+        <v>-0.2603</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.9518</v>
+        <v>-5.4663</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.61</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.369</v>
+        <v>-0.3885</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.749</v>
+        <v>-8.1585</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4148</v>
+        <v>-0.432</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.710800000000001</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4804</v>
+        <v>-0.4936</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.0884</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.04</v>
       </c>
       <c r="I147" t="n">
-        <v>0.7894</v>
+        <v>0.9115</v>
       </c>
       <c r="J147" t="n">
-        <v>16.5774</v>
+        <v>19.1415</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4924</v>
+        <v>0.5676</v>
       </c>
       <c r="J148" t="n">
-        <v>10.3404</v>
+        <v>11.9196</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.41</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4268</v>
+        <v>0.4894</v>
       </c>
       <c r="J149" t="n">
-        <v>8.9628</v>
+        <v>10.2774</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.4</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4205</v>
+        <v>0.4819</v>
       </c>
       <c r="J150" t="n">
-        <v>8.830500000000001</v>
+        <v>10.1199</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.12</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1469</v>
+        <v>0.173</v>
       </c>
       <c r="J151" t="n">
-        <v>3.0849</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8174</v>
+        <v>0.9052</v>
       </c>
       <c r="J152" t="n">
-        <v>20.435</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5572</v>
+        <v>0.6201</v>
       </c>
       <c r="J153" t="n">
-        <v>13.93</v>
+        <v>15.5025</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.531</v>
+        <v>0.5907</v>
       </c>
       <c r="J154" t="n">
-        <v>13.275</v>
+        <v>14.7675</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4762</v>
+        <v>0.5289</v>
       </c>
       <c r="J155" t="n">
-        <v>11.905</v>
+        <v>13.2225</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2019</v>
+        <v>0.2196</v>
       </c>
       <c r="J156" t="n">
-        <v>5.0475</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2381</v>
+        <v>0.2314</v>
       </c>
       <c r="J157" t="n">
-        <v>5.9525</v>
+        <v>5.785</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1496</v>
+        <v>-0.167</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.74</v>
+        <v>-4.175</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1703</v>
+        <v>-0.1879</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.2575</v>
+        <v>-4.6975</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2866</v>
+        <v>-0.3034</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.165</v>
+        <v>-7.585</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3627</v>
+        <v>-0.3769</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.067500000000001</v>
+        <v>-9.422499999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.485</v>
+        <v>0.4752</v>
       </c>
       <c r="J162" t="n">
-        <v>14.065</v>
+        <v>13.7808</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.92</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1041</v>
+        <v>-0.1179</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.0189</v>
+        <v>-3.4191</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.8778</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2591</v>
+        <v>-0.2742</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.5139</v>
+        <v>-7.9518</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2689</v>
+        <v>-0.2838</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.7981</v>
+        <v>-8.2302</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.38</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5008</v>
+        <v>0.508</v>
       </c>
       <c r="J167" t="n">
-        <v>14.5232</v>
+        <v>14.732</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4196</v>
+        <v>0.4309</v>
       </c>
       <c r="J168" t="n">
-        <v>12.1684</v>
+        <v>12.4961</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1148</v>
+        <v>0.1306</v>
       </c>
       <c r="J169" t="n">
-        <v>3.3292</v>
+        <v>3.7874</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0132</v>
+        <v>-0.0101</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.3828</v>
+        <v>-0.2929</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.96</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.078</v>
+        <v>-0.0839</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.262</v>
+        <v>-2.4331</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4159</v>
+        <v>1.4063</v>
       </c>
       <c r="J172" t="n">
-        <v>28.318</v>
+        <v>28.126</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.4</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9615</v>
+        <v>0.913</v>
       </c>
       <c r="J173" t="n">
-        <v>19.23</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.38</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.8763</v>
       </c>
       <c r="J174" t="n">
-        <v>18.458</v>
+        <v>17.526</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.9023</v>
+        <v>0.8575</v>
       </c>
       <c r="J175" t="n">
-        <v>18.046</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.28</v>
       </c>
       <c r="I176" t="n">
-        <v>0.7024</v>
+        <v>0.6815</v>
       </c>
       <c r="J176" t="n">
-        <v>14.048</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2425</v>
+        <v>0.2107</v>
       </c>
       <c r="J177" t="n">
-        <v>4.85</v>
+        <v>4.214</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.86</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1231</v>
+        <v>-0.1488</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.462</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3551</v>
+        <v>-0.3744</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.102</v>
+        <v>-7.488</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.54</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4385</v>
+        <v>-0.4535</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.77</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.24</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7209</v>
+        <v>-0.7149</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.418</v>
+        <v>-14.298</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0246</v>
+        <v>0.9597</v>
       </c>
       <c r="J182" t="n">
-        <v>27.6642</v>
+        <v>25.9119</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4479</v>
+        <v>0.4351</v>
       </c>
       <c r="J183" t="n">
-        <v>12.0933</v>
+        <v>11.7477</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1234</v>
+        <v>0.131</v>
       </c>
       <c r="J184" t="n">
-        <v>3.3318</v>
+        <v>3.537</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3879</v>
+        <v>-0.3755</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.4733</v>
+        <v>-10.1385</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.7298</v>
       </c>
       <c r="J186" t="n">
-        <v>-21.1896</v>
+        <v>-19.7046</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5254</v>
+        <v>0.5209</v>
       </c>
       <c r="J187" t="n">
-        <v>14.1858</v>
+        <v>14.0643</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.23</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4573</v>
+        <v>0.4579</v>
       </c>
       <c r="J188" t="n">
-        <v>12.3471</v>
+        <v>12.3633</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2045</v>
+        <v>0.2175</v>
       </c>
       <c r="J189" t="n">
-        <v>5.5215</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1194</v>
+        <v>0.1337</v>
       </c>
       <c r="J190" t="n">
-        <v>3.2238</v>
+        <v>3.6099</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.02</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0456</v>
+        <v>0.0588</v>
       </c>
       <c r="J191" t="n">
-        <v>1.2312</v>
+        <v>1.5876</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.53</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1905</v>
+        <v>1.1548</v>
       </c>
       <c r="J192" t="n">
-        <v>32.1435</v>
+        <v>31.1796</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.46</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0997</v>
+        <v>1.0568</v>
       </c>
       <c r="J193" t="n">
-        <v>29.6919</v>
+        <v>28.5336</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4692</v>
+        <v>0.4613</v>
       </c>
       <c r="J194" t="n">
-        <v>12.6684</v>
+        <v>12.4551</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4504</v>
+        <v>-0.4252</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.1608</v>
+        <v>-11.4804</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7421</v>
+        <v>-0.6865</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.0367</v>
+        <v>-18.5355</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.07</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2223</v>
+        <v>0.2198</v>
       </c>
       <c r="J197" t="n">
-        <v>6.0021</v>
+        <v>5.9346</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1258</v>
+        <v>0.1246</v>
       </c>
       <c r="J198" t="n">
-        <v>3.3966</v>
+        <v>3.3642</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.82</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2035</v>
+        <v>-0.2205</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.4945</v>
+        <v>-5.9535</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2627</v>
+        <v>-0.279</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.0929</v>
+        <v>-7.533</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3395</v>
+        <v>-0.3537</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.166499999999999</v>
+        <v>-9.549899999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1362</v>
+        <v>1.0996</v>
       </c>
       <c r="J202" t="n">
-        <v>28.405</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8481</v>
       </c>
       <c r="J203" t="n">
-        <v>22.5175</v>
+        <v>21.2025</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.8481</v>
       </c>
       <c r="J204" t="n">
-        <v>22.5175</v>
+        <v>21.2025</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0541</v>
+        <v>-0.0374</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.3525</v>
+        <v>-0.9350000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3797</v>
+        <v>-0.357</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.4925</v>
+        <v>-8.925000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1554</v>
+        <v>0.1595</v>
       </c>
       <c r="J207" t="n">
-        <v>3.885</v>
+        <v>3.9875</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1066</v>
+        <v>0.1106</v>
       </c>
       <c r="J208" t="n">
-        <v>2.665</v>
+        <v>2.765</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.99</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0147</v>
+        <v>-0.0208</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.3675</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.5275</v>
+        <v>-5.9075</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.0275</v>
+        <v>-6.4025</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.9426</v>
       </c>
       <c r="J212" t="n">
-        <v>34.616</v>
+        <v>37.704</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4099</v>
+        <v>0.4416</v>
       </c>
       <c r="J213" t="n">
-        <v>16.396</v>
+        <v>17.664</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.541</v>
+        <v>-0.5163</v>
       </c>
       <c r="J214" t="n">
-        <v>-21.64</v>
+        <v>-20.652</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.79</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6459</v>
+        <v>-0.6096</v>
       </c>
       <c r="J215" t="n">
-        <v>-25.836</v>
+        <v>-24.384</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6972</v>
+        <v>-0.6549</v>
       </c>
       <c r="J216" t="n">
-        <v>-27.888</v>
+        <v>-26.196</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.26</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4382</v>
+        <v>0.4891</v>
       </c>
       <c r="J217" t="n">
-        <v>17.528</v>
+        <v>19.564</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.16</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3323</v>
+        <v>0.3439</v>
       </c>
       <c r="J218" t="n">
-        <v>13.292</v>
+        <v>13.756</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3171</v>
+        <v>0.3268</v>
       </c>
       <c r="J219" t="n">
-        <v>12.684</v>
+        <v>13.072</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1649</v>
+        <v>0.1783</v>
       </c>
       <c r="J220" t="n">
-        <v>6.596</v>
+        <v>7.132</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.0623</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.492</v>
+        <v>-2.704</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.25</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3812</v>
+        <v>0.4114</v>
       </c>
       <c r="J222" t="n">
-        <v>11.436</v>
+        <v>12.342</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0551</v>
+        <v>0.0608</v>
       </c>
       <c r="J223" t="n">
-        <v>1.653</v>
+        <v>1.824</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1083</v>
+        <v>-0.121</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.249</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1842</v>
+        <v>-0.1986</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.526</v>
+        <v>-5.958</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.056</v>
+        <v>-7.485</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4631</v>
+        <v>0.524</v>
       </c>
       <c r="J227" t="n">
-        <v>13.893</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1654</v>
+        <v>0.18</v>
       </c>
       <c r="J228" t="n">
-        <v>4.962</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1225</v>
+        <v>0.1362</v>
       </c>
       <c r="J229" t="n">
-        <v>3.675</v>
+        <v>4.086</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.04</v>
       </c>
       <c r="I230" t="n">
-        <v>0.076</v>
+        <v>0.0877</v>
       </c>
       <c r="J230" t="n">
-        <v>2.28</v>
+        <v>2.631</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3246</v>
+        <v>-0.335</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.738</v>
+        <v>-10.05</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9462</v>
+        <v>1.0336</v>
       </c>
       <c r="J232" t="n">
-        <v>25.5474</v>
+        <v>27.9072</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.28</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6039</v>
+        <v>0.664</v>
       </c>
       <c r="J233" t="n">
-        <v>16.3053</v>
+        <v>17.928</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4108</v>
+        <v>0.4473</v>
       </c>
       <c r="J234" t="n">
-        <v>11.0916</v>
+        <v>12.0771</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5886</v>
+        <v>-0.5547</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.8922</v>
+        <v>-14.9769</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.2264</v>
+        <v>-1.1098</v>
       </c>
       <c r="J236" t="n">
-        <v>-33.1128</v>
+        <v>-29.9646</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.525</v>
+        <v>0.5828</v>
       </c>
       <c r="J237" t="n">
-        <v>14.175</v>
+        <v>15.7356</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.12</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2909</v>
+        <v>0.2941</v>
       </c>
       <c r="J238" t="n">
-        <v>7.8543</v>
+        <v>7.9407</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1325</v>
+        <v>-0.1456</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.5775</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2371</v>
+        <v>-0.251</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.4017</v>
+        <v>-6.777</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.257</v>
+        <v>-0.2706</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.939</v>
+        <v>-7.3062</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.05</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1714</v>
+        <v>0.1712</v>
       </c>
       <c r="J242" t="n">
-        <v>4.6278</v>
+        <v>4.6224</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.95</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0648</v>
+        <v>-0.0776</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.7496</v>
+        <v>-2.0952</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.83</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1948</v>
+        <v>-0.2115</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.2596</v>
+        <v>-5.7105</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2149</v>
+        <v>-0.2315</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.8023</v>
+        <v>-6.2505</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2447</v>
+        <v>-0.261</v>
       </c>
       <c r="J246" t="n">
-        <v>-6.6069</v>
+        <v>-7.047</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6786</v>
+        <v>0.7508</v>
       </c>
       <c r="J247" t="n">
-        <v>18.3222</v>
+        <v>20.2716</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.34</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6651</v>
+        <v>0.736</v>
       </c>
       <c r="J248" t="n">
-        <v>17.9577</v>
+        <v>19.872</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3524</v>
+        <v>0.3663</v>
       </c>
       <c r="J249" t="n">
-        <v>9.514799999999999</v>
+        <v>9.8901</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3524</v>
+        <v>0.3663</v>
       </c>
       <c r="J250" t="n">
-        <v>9.514799999999999</v>
+        <v>9.8901</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3948</v>
+        <v>-0.3741</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.6596</v>
+        <v>-10.1007</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2044</v>
+        <v>0.2164</v>
       </c>
       <c r="J252" t="n">
-        <v>6.132</v>
+        <v>6.492</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1902</v>
+        <v>0.2023</v>
       </c>
       <c r="J253" t="n">
-        <v>5.706</v>
+        <v>6.069</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.1</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1758</v>
+        <v>0.1879</v>
       </c>
       <c r="J254" t="n">
-        <v>5.274</v>
+        <v>5.637</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0498</v>
+        <v>-0.0581</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.494</v>
+        <v>-1.743</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3455</v>
+        <v>-0.3567</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.365</v>
+        <v>-10.701</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4479</v>
+        <v>0.4993</v>
       </c>
       <c r="J257" t="n">
-        <v>13.437</v>
+        <v>14.979</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2566</v>
+        <v>0.2657</v>
       </c>
       <c r="J258" t="n">
-        <v>7.698</v>
+        <v>7.971</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.135</v>
+        <v>0.1461</v>
       </c>
       <c r="J259" t="n">
-        <v>4.05</v>
+        <v>4.383</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1816</v>
+        <v>-0.1941</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.448</v>
+        <v>-5.823</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.75</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2923</v>
+        <v>-0.3041</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.769</v>
+        <v>-9.122999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I262" t="n">
-        <v>0.0649</v>
+        <v>0.063</v>
       </c>
       <c r="J262" t="n">
-        <v>1.8172</v>
+        <v>1.764</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.93</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J263" t="n">
-        <v>-2.4976</v>
+        <v>-2.8924</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1009</v>
+        <v>-0.1154</v>
       </c>
       <c r="J264" t="n">
-        <v>-2.8252</v>
+        <v>-3.2312</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.79</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2348</v>
+        <v>-0.2512</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.5744</v>
+        <v>-7.0336</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2545</v>
+        <v>-0.2706</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.126</v>
+        <v>-7.5768</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9179</v>
+        <v>1.0085</v>
       </c>
       <c r="J267" t="n">
-        <v>25.7012</v>
+        <v>28.238</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.571</v>
+        <v>0.632</v>
       </c>
       <c r="J268" t="n">
-        <v>15.988</v>
+        <v>17.696</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I269" t="n">
-        <v>0.1949</v>
+        <v>0.2071</v>
       </c>
       <c r="J269" t="n">
-        <v>5.4572</v>
+        <v>5.7988</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.0856</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.5844</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3026</v>
+        <v>-0.2892</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.472799999999999</v>
+        <v>-8.0976</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.93</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0735</v>
+        <v>-0.0911</v>
       </c>
       <c r="J272" t="n">
-        <v>-1.6905</v>
+        <v>-2.0953</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.132</v>
+        <v>-0.1508</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.036</v>
+        <v>-3.4684</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1749</v>
+        <v>-0.1939</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.0227</v>
+        <v>-4.4597</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3186</v>
+        <v>-0.3356</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.3278</v>
+        <v>-7.7188</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3939</v>
+        <v>-0.4079</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.059699999999999</v>
+        <v>-9.3817</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.67</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0509</v>
+        <v>1.1575</v>
       </c>
       <c r="J277" t="n">
-        <v>24.1707</v>
+        <v>26.6225</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>0.756</v>
+        <v>0.8409</v>
       </c>
       <c r="J278" t="n">
-        <v>17.388</v>
+        <v>19.3407</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.3</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5915</v>
+        <v>0.6597</v>
       </c>
       <c r="J279" t="n">
-        <v>13.6045</v>
+        <v>15.1731</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4687</v>
+        <v>0.5225</v>
       </c>
       <c r="J280" t="n">
-        <v>10.7801</v>
+        <v>12.0175</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2098</v>
+        <v>-0.191</v>
       </c>
       <c r="J281" t="n">
-        <v>-4.8254</v>
+        <v>-4.393</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0709</v>
+        <v>0.0673</v>
       </c>
       <c r="J282" t="n">
-        <v>2.4815</v>
+        <v>2.3555</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.88</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1427</v>
+        <v>-0.159</v>
       </c>
       <c r="J283" t="n">
-        <v>-4.9945</v>
+        <v>-5.565</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1529</v>
+        <v>-0.1695</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.3515</v>
+        <v>-5.9325</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1628</v>
+        <v>-0.1796</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.698</v>
+        <v>-6.286</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.8535</v>
+        <v>-11.389</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8008</v>
+        <v>0.8828</v>
       </c>
       <c r="J287" t="n">
-        <v>28.028</v>
+        <v>30.898</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.6536</v>
+        <v>0.723</v>
       </c>
       <c r="J288" t="n">
-        <v>22.876</v>
+        <v>25.305</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3846</v>
+        <v>0.4152</v>
       </c>
       <c r="J289" t="n">
-        <v>13.461</v>
+        <v>14.532</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1707</v>
+        <v>-0.1636</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.9745</v>
+        <v>-5.726</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3922</v>
+        <v>-0.3722</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.727</v>
+        <v>-13.027</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.96</v>
       </c>
       <c r="I292" t="n">
-        <v>1.3411</v>
+        <v>1.4711</v>
       </c>
       <c r="J292" t="n">
-        <v>26.822</v>
+        <v>29.422</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.82</v>
       </c>
       <c r="I293" t="n">
-        <v>1.1846</v>
+        <v>1.3064</v>
       </c>
       <c r="J293" t="n">
-        <v>23.692</v>
+        <v>26.128</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>0.9223</v>
+        <v>1.0266</v>
       </c>
       <c r="J294" t="n">
-        <v>18.446</v>
+        <v>20.532</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3543</v>
+        <v>0.3857</v>
       </c>
       <c r="J295" t="n">
-        <v>7.086</v>
+        <v>7.714</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.07</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1446</v>
+        <v>0.1794</v>
       </c>
       <c r="J296" t="n">
-        <v>2.892</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I297" t="n">
-        <v>0.0484</v>
+        <v>-0.0091</v>
       </c>
       <c r="J297" t="n">
-        <v>0.968</v>
+        <v>-0.182</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.68</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2862</v>
+        <v>-0.3125</v>
       </c>
       <c r="J298" t="n">
-        <v>-5.724</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.41</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5527</v>
       </c>
       <c r="J299" t="n">
-        <v>-10.836</v>
+        <v>-11.054</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5708</v>
+        <v>-0.5794</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.416</v>
+        <v>-11.588</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.37</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5805</v>
+        <v>-0.5883</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.61</v>
+        <v>-11.766</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.088</v>
+        <v>1.1883</v>
       </c>
       <c r="J302" t="n">
-        <v>29.376</v>
+        <v>32.0841</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4005</v>
+        <v>0.4371</v>
       </c>
       <c r="J303" t="n">
-        <v>10.8135</v>
+        <v>11.8017</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2288</v>
+        <v>0.2383</v>
       </c>
       <c r="J304" t="n">
-        <v>6.1776</v>
+        <v>6.4341</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.95</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2355</v>
+        <v>-0.2268</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.3585</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.88</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4457</v>
+        <v>-0.4219</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.0339</v>
+        <v>-11.3913</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.23</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4436</v>
+        <v>0.4868</v>
       </c>
       <c r="J307" t="n">
-        <v>11.9772</v>
+        <v>13.1436</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="J308" t="n">
-        <v>2.1897</v>
+        <v>2.2734</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0702</v>
+        <v>-0.0818</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.8954</v>
+        <v>-2.2086</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2406</v>
+        <v>-0.2557</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.4962</v>
+        <v>-6.9039</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3658</v>
+        <v>-0.3777</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.8766</v>
+        <v>-10.1979</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7055</v>
+        <v>0.7801</v>
       </c>
       <c r="J312" t="n">
-        <v>21.165</v>
+        <v>23.403</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5413</v>
+        <v>0.5995</v>
       </c>
       <c r="J313" t="n">
-        <v>16.239</v>
+        <v>17.985</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.23</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5132</v>
+        <v>0.5681</v>
       </c>
       <c r="J314" t="n">
-        <v>15.396</v>
+        <v>17.043</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.11</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3338</v>
+        <v>0.3413</v>
       </c>
       <c r="J315" t="n">
-        <v>10.014</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4799</v>
+        <v>-0.4517</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.397</v>
+        <v>-13.551</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.4719</v>
+        <v>0.5201</v>
       </c>
       <c r="J317" t="n">
-        <v>14.157</v>
+        <v>15.603</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3958</v>
+        <v>0.4284</v>
       </c>
       <c r="J318" t="n">
-        <v>11.874</v>
+        <v>12.852</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.179</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.71</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3204</v>
+        <v>-0.3335</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.612</v>
+        <v>-10.005</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.68</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3489</v>
+        <v>-0.3611</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.467</v>
+        <v>-10.833</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>0.8214</v>
+        <v>0.9035</v>
       </c>
       <c r="J322" t="n">
-        <v>23.8206</v>
+        <v>26.2015</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5194</v>
+        <v>0.5735</v>
       </c>
       <c r="J323" t="n">
-        <v>15.0626</v>
+        <v>16.6315</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.11</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3395</v>
+        <v>0.3465</v>
       </c>
       <c r="J324" t="n">
-        <v>9.845499999999999</v>
+        <v>10.0485</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1025</v>
+        <v>0.1167</v>
       </c>
       <c r="J325" t="n">
-        <v>2.9725</v>
+        <v>3.3843</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.6049</v>
+        <v>-0.5662</v>
       </c>
       <c r="J326" t="n">
-        <v>-17.5421</v>
+        <v>-16.4198</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.22</v>
       </c>
       <c r="I327" t="n">
-        <v>0.427</v>
+        <v>0.4689</v>
       </c>
       <c r="J327" t="n">
-        <v>12.383</v>
+        <v>13.5981</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.12</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2999</v>
+        <v>0.3007</v>
       </c>
       <c r="J328" t="n">
-        <v>8.697100000000001</v>
+        <v>8.7203</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0597</v>
+        <v>-0.0699</v>
       </c>
       <c r="J329" t="n">
-        <v>-1.7313</v>
+        <v>-2.0271</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.74</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2925</v>
+        <v>-0.3062</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.4825</v>
+        <v>-8.879799999999999</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.73</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3022</v>
+        <v>-0.3156</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.7638</v>
+        <v>-9.1524</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.54</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9004</v>
+        <v>0.9954</v>
       </c>
       <c r="J332" t="n">
-        <v>23.4104</v>
+        <v>25.8804</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.27</v>
       </c>
       <c r="I333" t="n">
-        <v>0.5556</v>
+        <v>0.6188</v>
       </c>
       <c r="J333" t="n">
-        <v>14.4456</v>
+        <v>16.0888</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.27</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5556</v>
+        <v>0.6188</v>
       </c>
       <c r="J334" t="n">
-        <v>14.4456</v>
+        <v>16.0888</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.16</v>
       </c>
       <c r="I335" t="n">
-        <v>0.3999</v>
+        <v>0.4415</v>
       </c>
       <c r="J335" t="n">
-        <v>10.3974</v>
+        <v>11.479</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.15</v>
       </c>
       <c r="I336" t="n">
-        <v>0.3847</v>
+        <v>0.4207</v>
       </c>
       <c r="J336" t="n">
-        <v>10.0022</v>
+        <v>10.9382</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.02</v>
       </c>
       <c r="I337" t="n">
-        <v>0.098</v>
+        <v>0.0965</v>
       </c>
       <c r="J337" t="n">
-        <v>2.548</v>
+        <v>2.509</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0503</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.3078</v>
+        <v>-1.6302</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1735</v>
+        <v>-0.1903</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.511</v>
+        <v>-4.9478</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1735</v>
+        <v>-0.1903</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.511</v>
+        <v>-4.9478</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3303</v>
+        <v>-0.3447</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.5878</v>
+        <v>-8.962199999999999</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.64</v>
       </c>
       <c r="I342" t="n">
-        <v>1.0174</v>
+        <v>1.1214</v>
       </c>
       <c r="J342" t="n">
-        <v>23.4002</v>
+        <v>25.7922</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.62</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9931</v>
+        <v>1.0956</v>
       </c>
       <c r="J343" t="n">
-        <v>22.8413</v>
+        <v>25.1988</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.656</v>
+        <v>0.7311</v>
       </c>
       <c r="J344" t="n">
-        <v>15.088</v>
+        <v>16.8153</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.21</v>
       </c>
       <c r="I345" t="n">
-        <v>0.4702</v>
+        <v>0.5238</v>
       </c>
       <c r="J345" t="n">
-        <v>10.8146</v>
+        <v>12.0474</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.9458</v>
+        <v>-0.86</v>
       </c>
       <c r="J346" t="n">
-        <v>-21.7534</v>
+        <v>-19.78</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.011</v>
+        <v>-0.0235</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.253</v>
+        <v>-0.5405</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.87</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1472</v>
+        <v>-0.1651</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.3856</v>
+        <v>-3.7973</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1784</v>
+        <v>-0.1966</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.1032</v>
+        <v>-4.5218</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2361</v>
+        <v>-0.2544</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.4303</v>
+        <v>-5.8512</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.61</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3977</v>
+        <v>-0.4108</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.1471</v>
+        <v>-9.448399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5607/event_5607_evp_summary.xlsx
+++ b/database/event/5607/event_5607_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.474600000000001</v>
+        <v>8.3093</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7741</v>
+        <v>2.72</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2336</v>
+        <v>3.1795</v>
       </c>
       <c r="E2" t="n">
-        <v>8.474600000000001</v>
+        <v>8.3093</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5322</v>
+        <v>2.5543</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9424</v>
+        <v>5.7551</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8172</v>
+        <v>2.9035</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9643</v>
+        <v>3.0607</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9424</v>
+        <v>5.7551</v>
       </c>
       <c r="K2" t="n">
         <v>123</v>
@@ -529,7 +529,7 @@
         <v>219</v>
       </c>
       <c r="M2" t="n">
-        <v>8.906700000000001</v>
+        <v>8.815799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>342</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5134</v>
+        <v>7.4648</v>
       </c>
       <c r="C3" t="n">
-        <v>2.4594</v>
+        <v>2.4435</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7961</v>
+        <v>2.7948</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5134</v>
+        <v>7.4648</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8097</v>
+        <v>1.8068</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7037</v>
+        <v>5.6579</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8097</v>
+        <v>1.8068</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9042</v>
+        <v>1.9047</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7037</v>
+        <v>5.6579</v>
       </c>
       <c r="K3" t="n">
         <v>45</v>
@@ -575,7 +575,7 @@
         <v>205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.607900000000001</v>
+        <v>7.5626</v>
       </c>
       <c r="N3" t="n">
         <v>250</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.836</v>
+        <v>6.7143</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2377</v>
+        <v>2.1979</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4877</v>
+        <v>2.4529</v>
       </c>
       <c r="E4" t="n">
-        <v>6.836</v>
+        <v>6.7143</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9789</v>
+        <v>1.9842</v>
       </c>
       <c r="G4" t="n">
-        <v>4.8571</v>
+        <v>4.73</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9789</v>
+        <v>1.9842</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0822</v>
+        <v>2.0917</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8571</v>
+        <v>4.73</v>
       </c>
       <c r="K4" t="n">
         <v>45</v>
@@ -621,7 +621,7 @@
         <v>205</v>
       </c>
       <c r="M4" t="n">
-        <v>6.939299999999999</v>
+        <v>6.8217</v>
       </c>
       <c r="N4" t="n">
         <v>250</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.7087</v>
+        <v>6.4681</v>
       </c>
       <c r="C5" t="n">
-        <v>2.196</v>
+        <v>2.1173</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4297</v>
+        <v>2.3407</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7087</v>
+        <v>6.4681</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3991</v>
+        <v>2.3404</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3096</v>
+        <v>4.1276</v>
       </c>
       <c r="H5" t="n">
-        <v>2.526</v>
+        <v>2.4134</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7264</v>
+        <v>2.6121</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3096</v>
+        <v>4.1276</v>
       </c>
       <c r="K5" t="n">
         <v>132</v>
@@ -667,7 +667,7 @@
         <v>227</v>
       </c>
       <c r="M5" t="n">
-        <v>7.036</v>
+        <v>6.7397</v>
       </c>
       <c r="N5" t="n">
         <v>359</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.1988</v>
+        <v>6.1652</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0291</v>
+        <v>2.0181</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1976</v>
+        <v>2.2028</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1988</v>
+        <v>6.1652</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3059</v>
+        <v>2.3104</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8929</v>
+        <v>3.8548</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3219</v>
+        <v>2.3445</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4431</v>
+        <v>2.4715</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8929</v>
+        <v>3.8548</v>
       </c>
       <c r="K6" t="n">
         <v>45</v>
@@ -713,7 +713,7 @@
         <v>205</v>
       </c>
       <c r="M6" t="n">
-        <v>6.336</v>
+        <v>6.3263</v>
       </c>
       <c r="N6" t="n">
         <v>250</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6414</v>
+        <v>4.4845</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5193</v>
+        <v>1.468</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4887</v>
+        <v>1.4371</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6414</v>
+        <v>4.4845</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0465</v>
+        <v>0.9788</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5949</v>
+        <v>3.5057</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0465</v>
+        <v>0.9788</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1295</v>
+        <v>1.0594</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5949</v>
+        <v>3.5057</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>227</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7244</v>
+        <v>4.5651</v>
       </c>
       <c r="N7" t="n">
         <v>359</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.607</v>
+        <v>2.5247</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8534</v>
+        <v>0.8264</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5626</v>
+        <v>0.5443</v>
       </c>
       <c r="E8" t="n">
-        <v>2.607</v>
+        <v>2.5247</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4787</v>
+        <v>2.4744</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1283</v>
+        <v>0.0503</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7002</v>
+        <v>2.7204</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8412</v>
+        <v>2.8677</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1283</v>
+        <v>0.0503</v>
       </c>
       <c r="K8" t="n">
         <v>76</v>
@@ -805,7 +805,7 @@
         <v>134</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9695</v>
+        <v>2.918</v>
       </c>
       <c r="N8" t="n">
         <v>210</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3205</v>
+        <v>2.2331</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.731</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4321</v>
+        <v>0.4115</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3205</v>
+        <v>2.2331</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8104</v>
+        <v>1.7939</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5101</v>
+        <v>0.4392</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8104</v>
+        <v>1.7939</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9049</v>
+        <v>1.8911</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5101</v>
+        <v>0.4392</v>
       </c>
       <c r="K9" t="n">
         <v>52</v>
@@ -851,7 +851,7 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>2.415</v>
+        <v>2.3303</v>
       </c>
       <c r="N9" t="n">
         <v>183</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2923</v>
+        <v>2.2057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7504</v>
+        <v>0.722</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4193</v>
+        <v>0.399</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2923</v>
+        <v>2.2057</v>
       </c>
       <c r="F10" t="n">
-        <v>1.062</v>
+        <v>1.0782</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2303</v>
+        <v>1.1275</v>
       </c>
       <c r="H10" t="n">
-        <v>1.062</v>
+        <v>1.0782</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1174</v>
+        <v>1.1366</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2303</v>
+        <v>1.1275</v>
       </c>
       <c r="K10" t="n">
         <v>52</v>
@@ -897,7 +897,7 @@
         <v>131</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3477</v>
+        <v>2.2641</v>
       </c>
       <c r="N10" t="n">
         <v>183</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.089</v>
+        <v>2.1524</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6838</v>
+        <v>0.7046</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3268</v>
+        <v>0.3747</v>
       </c>
       <c r="E11" t="n">
-        <v>2.089</v>
+        <v>2.1524</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6398</v>
+        <v>1.1852</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4492</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6398</v>
+        <v>1.1852</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7699</v>
+        <v>1.2494</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4492</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2191</v>
+        <v>2.2166</v>
       </c>
       <c r="N11" t="n">
-        <v>359</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0699</v>
+        <v>2.0765</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6776</v>
+        <v>0.6797</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3181</v>
+        <v>0.3402</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0699</v>
+        <v>2.0765</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2259</v>
+        <v>1.6298</v>
       </c>
       <c r="G12" t="n">
-        <v>0.844</v>
+        <v>0.4467</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2259</v>
+        <v>1.6298</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2899</v>
+        <v>1.764</v>
       </c>
       <c r="J12" t="n">
-        <v>0.844</v>
+        <v>0.4467</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="L12" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1339</v>
+        <v>2.2107</v>
       </c>
       <c r="N12" t="n">
-        <v>250</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.976</v>
+        <v>1.8899</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6468</v>
+        <v>0.6186</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2753</v>
+        <v>0.2552</v>
       </c>
       <c r="E13" t="n">
-        <v>1.976</v>
+        <v>1.8899</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8274</v>
+        <v>-0.1888</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1486</v>
+        <v>2.0787</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8274</v>
+        <v>-0.1888</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8706</v>
+        <v>-0.1888</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1486</v>
+        <v>2.0787</v>
       </c>
       <c r="K13" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L13" t="n">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0192</v>
+        <v>1.8899</v>
       </c>
       <c r="N13" t="n">
-        <v>210</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9603</v>
+        <v>1.8039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6417</v>
+        <v>0.5905</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2682</v>
+        <v>0.216</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9603</v>
+        <v>1.8039</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1454</v>
+        <v>0.8086</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1057</v>
+        <v>0.9953</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1454</v>
+        <v>0.8086</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1454</v>
+        <v>0.8524</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1057</v>
+        <v>0.9953</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L14" t="n">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9603</v>
+        <v>1.8477</v>
       </c>
       <c r="N14" t="n">
-        <v>283</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7107</v>
+        <v>1.6331</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5346</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1545</v>
+        <v>0.1382</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7107</v>
+        <v>1.6331</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6898</v>
+        <v>-0.6622</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4005</v>
+        <v>2.2953</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6898</v>
+        <v>-0.6622</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6898</v>
+        <v>-0.6622</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4005</v>
+        <v>2.2953</v>
       </c>
       <c r="K15" t="n">
         <v>54</v>
@@ -1127,7 +1127,7 @@
         <v>229</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7107</v>
+        <v>1.6331</v>
       </c>
       <c r="N15" t="n">
         <v>283</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6202</v>
+        <v>1.5487</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5304</v>
+        <v>0.507</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1133</v>
+        <v>0.0997</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6202</v>
+        <v>1.5487</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7341</v>
+        <v>0.6808</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8861</v>
+        <v>0.8678</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7341</v>
+        <v>0.6808</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7923</v>
+        <v>0.7369</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8861</v>
+        <v>0.8678</v>
       </c>
       <c r="K16" t="n">
         <v>132</v>
@@ -1173,7 +1173,7 @@
         <v>227</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6784</v>
+        <v>1.6047</v>
       </c>
       <c r="N16" t="n">
         <v>359</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5914</v>
+        <v>1.4945</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5209</v>
+        <v>0.4892</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1002</v>
+        <v>0.075</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5914</v>
+        <v>1.4945</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3867</v>
+        <v>-0.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9781</v>
+        <v>1.8945</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3867</v>
+        <v>-0.4</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4069</v>
+        <v>-0.4217</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9781</v>
+        <v>1.8945</v>
       </c>
       <c r="K17" t="n">
         <v>123</v>
@@ -1219,7 +1219,7 @@
         <v>219</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5712</v>
+        <v>1.4728</v>
       </c>
       <c r="N17" t="n">
         <v>342</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0724</v>
+        <v>0.9754</v>
       </c>
       <c r="C18" t="n">
-        <v>0.351</v>
+        <v>0.3193</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.136</v>
+        <v>-0.1614</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0724</v>
+        <v>0.9754</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2444</v>
+        <v>1.1881</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.172</v>
+        <v>-0.2127</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2444</v>
+        <v>1.1881</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3094</v>
+        <v>1.2524</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.172</v>
+        <v>-0.2127</v>
       </c>
       <c r="K18" t="n">
         <v>52</v>
@@ -1265,7 +1265,7 @@
         <v>131</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1374</v>
+        <v>1.0397</v>
       </c>
       <c r="N18" t="n">
         <v>183</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7852</v>
+        <v>0.8227</v>
       </c>
       <c r="C19" t="n">
-        <v>0.257</v>
+        <v>0.2693</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2668</v>
+        <v>-0.231</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7852</v>
+        <v>0.8227</v>
       </c>
       <c r="F19" t="n">
-        <v>0.306</v>
+        <v>0.3653</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4792</v>
+        <v>0.4574</v>
       </c>
       <c r="H19" t="n">
-        <v>0.306</v>
+        <v>0.3653</v>
       </c>
       <c r="I19" t="n">
-        <v>0.322</v>
+        <v>0.3851</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4792</v>
+        <v>0.4574</v>
       </c>
       <c r="K19" t="n">
         <v>123</v>
@@ -1311,7 +1311,7 @@
         <v>219</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8012</v>
+        <v>0.8425</v>
       </c>
       <c r="N19" t="n">
         <v>342</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.498</v>
+        <v>0.516</v>
       </c>
       <c r="C20" t="n">
-        <v>0.163</v>
+        <v>0.1689</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3975</v>
+        <v>-0.3707</v>
       </c>
       <c r="E20" t="n">
-        <v>0.498</v>
+        <v>0.516</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6131</v>
+        <v>-0.5844</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1111</v>
+        <v>1.1004</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6131</v>
+        <v>-0.5844</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6131</v>
+        <v>-0.5844</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1111</v>
+        <v>1.1004</v>
       </c>
       <c r="K20" t="n">
         <v>54</v>
@@ -1357,7 +1357,7 @@
         <v>229</v>
       </c>
       <c r="M20" t="n">
-        <v>0.498</v>
+        <v>0.516</v>
       </c>
       <c r="N20" t="n">
         <v>283</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3926</v>
+        <v>0.4728</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1285</v>
+        <v>0.1548</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4455</v>
+        <v>-0.3904</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3926</v>
+        <v>0.4728</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6409</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2483</v>
+        <v>-0.2172</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6409</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6744</v>
+        <v>0.7274</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2483</v>
+        <v>-0.2172</v>
       </c>
       <c r="K21" t="n">
         <v>52</v>
@@ -1403,7 +1403,7 @@
         <v>131</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4261</v>
+        <v>0.5102</v>
       </c>
       <c r="N21" t="n">
         <v>183</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3541</v>
+        <v>0.3315</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1159</v>
+        <v>0.1085</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.463</v>
+        <v>-0.4548</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3541</v>
+        <v>0.3315</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0115</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6574</v>
+        <v>-0.6509</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0115</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0643</v>
+        <v>1.0356</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6574</v>
+        <v>-0.6509</v>
       </c>
       <c r="K22" t="n">
         <v>76</v>
@@ -1449,7 +1449,7 @@
         <v>134</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4069</v>
+        <v>0.3847</v>
       </c>
       <c r="N22" t="n">
         <v>210</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2776</v>
+        <v>0.2932</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4978</v>
+        <v>-0.4722</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2776</v>
+        <v>0.2932</v>
       </c>
       <c r="F23" t="n">
-        <v>0.473</v>
+        <v>0.4887</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1954</v>
+        <v>-0.1955</v>
       </c>
       <c r="H23" t="n">
-        <v>0.473</v>
+        <v>0.4887</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4977</v>
+        <v>0.5152</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1954</v>
+        <v>-0.1955</v>
       </c>
       <c r="K23" t="n">
         <v>45</v>
@@ -1495,7 +1495,7 @@
         <v>205</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3023</v>
+        <v>0.3197</v>
       </c>
       <c r="N23" t="n">
         <v>250</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.274</v>
+        <v>0.1641</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0897</v>
+        <v>0.0537</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4995</v>
+        <v>-0.531</v>
       </c>
       <c r="E24" t="n">
-        <v>0.274</v>
+        <v>0.1641</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0538</v>
+        <v>0.0348</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2202</v>
+        <v>0.1293</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0538</v>
+        <v>0.0348</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0566</v>
+        <v>0.0367</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2202</v>
+        <v>0.1293</v>
       </c>
       <c r="K24" t="n">
         <v>123</v>
@@ -1541,7 +1541,7 @@
         <v>219</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2768</v>
+        <v>0.166</v>
       </c>
       <c r="N24" t="n">
         <v>342</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1697</v>
+        <v>0.103</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0555</v>
+        <v>0.0337</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.547</v>
+        <v>-0.5589</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1697</v>
+        <v>0.103</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5427999999999999</v>
+        <v>0.3995</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7125</v>
+        <v>-0.2965</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5427999999999999</v>
+        <v>0.3995</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5858</v>
+        <v>0.4101</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7125</v>
+        <v>-0.2965</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1267</v>
+        <v>0.1136</v>
       </c>
       <c r="N25" t="n">
-        <v>359</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1566</v>
+        <v>0.0674</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0513</v>
+        <v>0.0221</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1566</v>
+        <v>0.0674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.487</v>
+        <v>-0.5776</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3304</v>
+        <v>0.645</v>
       </c>
       <c r="H26" t="n">
-        <v>0.487</v>
+        <v>-0.5776</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4996</v>
+        <v>-0.6252</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3304</v>
+        <v>0.645</v>
       </c>
       <c r="K26" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
-        <v>58</v>
+        <v>227</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1692</v>
+        <v>0.01980000000000004</v>
       </c>
       <c r="N26" t="n">
-        <v>134</v>
+        <v>359</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0931</v>
+        <v>0.0432</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0305</v>
+        <v>0.0141</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5818</v>
+        <v>-0.5861</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0931</v>
+        <v>0.0432</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4508</v>
+        <v>-0.4215</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.4647</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4508</v>
+        <v>-0.4215</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4508</v>
+        <v>-0.4215</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.4647</v>
       </c>
       <c r="K27" t="n">
         <v>54</v>
@@ -1679,7 +1679,7 @@
         <v>229</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09310000000000007</v>
+        <v>0.04320000000000002</v>
       </c>
       <c r="N27" t="n">
         <v>283</v>
@@ -1688,35 +1688,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.061</v>
+        <v>0.0049</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02</v>
+        <v>0.0016</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5964</v>
+        <v>-0.6036</v>
       </c>
       <c r="E28" t="n">
-        <v>0.061</v>
+        <v>0.0049</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1876</v>
+        <v>0.2239</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1266</v>
+        <v>-0.219</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1876</v>
+        <v>0.2239</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1924</v>
+        <v>0.2299</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1266</v>
+        <v>-0.219</v>
       </c>
       <c r="K28" t="n">
         <v>76</v>
@@ -1725,7 +1725,7 @@
         <v>58</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0658</v>
+        <v>0.01089999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>134</v>
@@ -1734,35 +1734,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0039</v>
+        <v>-0.0141</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0013</v>
+        <v>-0.0046</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6224</v>
+        <v>-0.6122</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0039</v>
+        <v>-0.0141</v>
       </c>
       <c r="F29" t="n">
-        <v>0.254</v>
+        <v>0.1151</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1292</v>
       </c>
       <c r="H29" t="n">
-        <v>0.254</v>
+        <v>0.1151</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2605</v>
+        <v>0.1182</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2501</v>
+        <v>-0.1292</v>
       </c>
       <c r="K29" t="n">
         <v>76</v>
@@ -1771,7 +1771,7 @@
         <v>58</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01040000000000002</v>
+        <v>-0.01100000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>134</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1045</v>
+        <v>-0.0755</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0342</v>
+        <v>-0.0247</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6718</v>
+        <v>-0.6402</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1045</v>
+        <v>-0.0755</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1161</v>
+        <v>0.156</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2206</v>
+        <v>-0.2314</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1161</v>
+        <v>0.156</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1222</v>
+        <v>0.1644</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2206</v>
+        <v>-0.2314</v>
       </c>
       <c r="K30" t="n">
         <v>76</v>
@@ -1817,7 +1817,7 @@
         <v>134</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.09839999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="N30" t="n">
         <v>210</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1102</v>
+        <v>-0.1542</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0361</v>
+        <v>-0.0505</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6744</v>
+        <v>-0.676</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1102</v>
+        <v>-0.1542</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2841</v>
+        <v>0.2158</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3943</v>
+        <v>-0.37</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2841</v>
+        <v>0.2158</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2841</v>
+        <v>0.2158</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3943</v>
+        <v>-0.37</v>
       </c>
       <c r="K31" t="n">
         <v>52</v>
@@ -1863,7 +1863,7 @@
         <v>47</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1102</v>
+        <v>-0.1542</v>
       </c>
       <c r="N31" t="n">
         <v>99</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1737</v>
+        <v>-0.2802</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0569</v>
+        <v>-0.0917</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7033</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1737</v>
+        <v>-0.2802</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3304</v>
+        <v>0.2571</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5041</v>
+        <v>-0.5373</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3304</v>
+        <v>0.2571</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3304</v>
+        <v>0.2571</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5041</v>
+        <v>-0.5373</v>
       </c>
       <c r="K32" t="n">
         <v>52</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1737</v>
+        <v>-0.2802</v>
       </c>
       <c r="N32" t="n">
         <v>99</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6392</v>
+        <v>-0.6149</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2092</v>
+        <v>-0.2013</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9152</v>
+        <v>-0.8859</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6392</v>
+        <v>-0.6149</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0618</v>
+        <v>-0.4174</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5774</v>
+        <v>-0.1975</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0618</v>
+        <v>-0.4174</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0634</v>
+        <v>-0.4174</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5774</v>
+        <v>-0.1975</v>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L33" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6408</v>
+        <v>-0.6149</v>
       </c>
       <c r="N33" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6666</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2182</v>
+        <v>-0.2229</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9277</v>
+        <v>-0.916</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6666</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0056</v>
+        <v>-0.0522</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.661</v>
+        <v>-0.6287</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0056</v>
+        <v>-0.0522</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0057</v>
+        <v>-0.0536</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.661</v>
+        <v>-0.6287</v>
       </c>
       <c r="K34" t="n">
         <v>76</v>
@@ -2001,7 +2001,7 @@
         <v>58</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6667000000000001</v>
+        <v>-0.6823</v>
       </c>
       <c r="N34" t="n">
         <v>134</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7024</v>
+        <v>-0.7156</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2299</v>
+        <v>-0.2342</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.944</v>
+        <v>-0.9318</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7024</v>
+        <v>-0.7156</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6098</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0926</v>
+        <v>-0.1405</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6098</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6098</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0926</v>
+        <v>-0.1405</v>
       </c>
       <c r="K35" t="n">
         <v>52</v>
@@ -2047,7 +2047,7 @@
         <v>47</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7024</v>
+        <v>-0.7156</v>
       </c>
       <c r="N35" t="n">
         <v>99</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7216</v>
+        <v>-0.731</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2362</v>
+        <v>-0.2393</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9527</v>
+        <v>-0.9388</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7216</v>
+        <v>-0.731</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4568</v>
+        <v>-0.1825</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2648</v>
+        <v>-0.5485</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4568</v>
+        <v>-0.1825</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4568</v>
+        <v>-0.1874</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2648</v>
+        <v>-0.5485</v>
       </c>
       <c r="K36" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L36" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7216</v>
+        <v>-0.7359</v>
       </c>
       <c r="N36" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.7705</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2731</v>
+        <v>-0.2522</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0039</v>
+        <v>-0.9568</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.7705</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1214</v>
+        <v>-0.0818</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7128</v>
+        <v>-0.6887</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1214</v>
+        <v>-0.0818</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1277</v>
+        <v>-0.0862</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7128</v>
+        <v>-0.6887</v>
       </c>
       <c r="K37" t="n">
         <v>76</v>
@@ -2139,7 +2139,7 @@
         <v>134</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8405</v>
+        <v>-0.7748999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>210</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2302</v>
+        <v>-1.1975</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4027</v>
+        <v>-0.392</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1842</v>
+        <v>-1.1513</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2302</v>
+        <v>-1.1975</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2998</v>
+        <v>-0.2758</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.9304</v>
+        <v>-0.9217</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2998</v>
+        <v>-0.2758</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2998</v>
+        <v>-0.2758</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9304</v>
+        <v>-0.9217</v>
       </c>
       <c r="K38" t="n">
         <v>52</v>
@@ -2185,7 +2185,7 @@
         <v>47</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2302</v>
+        <v>-1.1975</v>
       </c>
       <c r="N38" t="n">
         <v>99</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2628</v>
+        <v>-1.2175</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4134</v>
+        <v>-0.3985</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1991</v>
+        <v>-1.1604</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2628</v>
+        <v>-1.2175</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2534</v>
+        <v>0.2087</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.5162</v>
+        <v>-1.4262</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2534</v>
+        <v>0.2087</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2534</v>
+        <v>0.2087</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5162</v>
+        <v>-1.4262</v>
       </c>
       <c r="K39" t="n">
         <v>54</v>
@@ -2231,7 +2231,7 @@
         <v>229</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2628</v>
+        <v>-1.2175</v>
       </c>
       <c r="N39" t="n">
         <v>283</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3912</v>
+        <v>-1.371</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4554</v>
+        <v>-0.4488</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2575</v>
+        <v>-1.2303</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3912</v>
+        <v>-1.371</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9917</v>
+        <v>-0.9223</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.3995</v>
+        <v>-0.4487</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9917</v>
+        <v>-0.9223</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0435</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3995</v>
+        <v>-0.4487</v>
       </c>
       <c r="K40" t="n">
         <v>52</v>
@@ -2277,7 +2277,7 @@
         <v>131</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.443</v>
+        <v>-1.421</v>
       </c>
       <c r="N40" t="n">
         <v>183</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.9203</v>
+        <v>-2.8951</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9559</v>
+        <v>-0.9477</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9536</v>
+        <v>-1.9246</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.9203</v>
+        <v>-2.8951</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7415</v>
+        <v>-0.7494</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.1788</v>
+        <v>-2.1457</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7415</v>
+        <v>-0.7494</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7802</v>
+        <v>-0.79</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.1788</v>
+        <v>-2.1457</v>
       </c>
       <c r="K41" t="n">
         <v>123</v>
@@ -2323,7 +2323,7 @@
         <v>219</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.959</v>
+        <v>-2.9357</v>
       </c>
       <c r="N41" t="n">
         <v>342</v>
@@ -2429,10 +2429,10 @@
         <v>1.91</v>
       </c>
       <c r="I2" t="n">
-        <v>1.756</v>
+        <v>1.7967</v>
       </c>
       <c r="J2" t="n">
-        <v>49.168</v>
+        <v>50.3076</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7612</v>
+        <v>0.7379</v>
       </c>
       <c r="J3" t="n">
-        <v>21.3136</v>
+        <v>20.6612</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.16</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4462</v>
+        <v>0.414</v>
       </c>
       <c r="J4" t="n">
-        <v>12.4936</v>
+        <v>11.592</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0553</v>
+        <v>0.0389</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5484</v>
+        <v>1.0892</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2177</v>
+        <v>-0.1845</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.0956</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3533</v>
+        <v>0.3034</v>
       </c>
       <c r="J7" t="n">
-        <v>9.8924</v>
+        <v>8.495200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1568</v>
+        <v>-0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.3904</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1883</v>
+        <v>-0.1705</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.2724</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.76</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2757</v>
+        <v>-0.2574</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.7196</v>
+        <v>-7.2072</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.58</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.44</v>
+        <v>-0.4324</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.32</v>
+        <v>-12.1072</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.243</v>
+        <v>0.2302</v>
       </c>
       <c r="J12" t="n">
-        <v>5.346</v>
+        <v>5.0644</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1597</v>
+        <v>0.1441</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5134</v>
+        <v>3.1702</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2284</v>
+        <v>-0.2095</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.0248</v>
+        <v>-4.609</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.7</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.333</v>
+        <v>-0.3168</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.326</v>
+        <v>-6.9696</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.57</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4498</v>
+        <v>-0.4434</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.8956</v>
+        <v>-9.754799999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.53</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.5759</v>
       </c>
       <c r="J17" t="n">
-        <v>14.2494</v>
+        <v>12.6698</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.41</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5255</v>
+        <v>0.4571</v>
       </c>
       <c r="J18" t="n">
-        <v>11.561</v>
+        <v>10.0562</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.31</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4193</v>
+        <v>0.3571</v>
       </c>
       <c r="J19" t="n">
-        <v>9.224600000000001</v>
+        <v>7.8562</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1799</v>
+        <v>0.1427</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9578</v>
+        <v>3.1394</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.89</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1783</v>
+        <v>-0.1592</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.9226</v>
+        <v>-3.5024</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.57</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2363</v>
+        <v>1.2566</v>
       </c>
       <c r="J22" t="n">
-        <v>28.4349</v>
+        <v>28.9018</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8518</v>
+        <v>0.8359</v>
       </c>
       <c r="J23" t="n">
-        <v>19.5914</v>
+        <v>19.2257</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.32</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7759</v>
+        <v>0.7556</v>
       </c>
       <c r="J24" t="n">
-        <v>17.8457</v>
+        <v>17.3788</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6783</v>
+        <v>0.6536</v>
       </c>
       <c r="J25" t="n">
-        <v>15.6009</v>
+        <v>15.0328</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1504</v>
+        <v>0.1242</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4592</v>
+        <v>2.8566</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.18</v>
       </c>
       <c r="I27" t="n">
-        <v>0.491</v>
+        <v>0.4503</v>
       </c>
       <c r="J27" t="n">
-        <v>11.293</v>
+        <v>10.3569</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.77</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2583</v>
+        <v>-0.2426</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.9409</v>
+        <v>-5.5798</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.74</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2855</v>
+        <v>-0.2698</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.5665</v>
+        <v>-6.2054</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.66</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3578</v>
+        <v>-0.3439</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.2294</v>
+        <v>-7.9097</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.38</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6031</v>
+        <v>-0.6171</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.8713</v>
+        <v>-14.1933</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7523</v>
+        <v>0.8082</v>
       </c>
       <c r="J32" t="n">
-        <v>21.0644</v>
+        <v>22.6296</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3614</v>
+        <v>0.3543</v>
       </c>
       <c r="J33" t="n">
-        <v>10.1192</v>
+        <v>9.920400000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2448</v>
+        <v>-0.2248</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.8544</v>
+        <v>-6.2944</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2646</v>
+        <v>-0.2452</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.4088</v>
+        <v>-6.8656</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.76</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2937</v>
+        <v>-0.2756</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.223599999999999</v>
+        <v>-7.7168</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3707</v>
+        <v>0.3093</v>
       </c>
       <c r="J37" t="n">
-        <v>10.3796</v>
+        <v>8.660399999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3588</v>
+        <v>0.2983</v>
       </c>
       <c r="J38" t="n">
-        <v>10.0464</v>
+        <v>8.352399999999999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2467</v>
+        <v>0.1974</v>
       </c>
       <c r="J39" t="n">
-        <v>6.9076</v>
+        <v>5.5272</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1039</v>
+        <v>0.077</v>
       </c>
       <c r="J40" t="n">
-        <v>2.9092</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3452</v>
+        <v>-0.3309</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.6656</v>
+        <v>-9.2652</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2703</v>
+        <v>1.2907</v>
       </c>
       <c r="J42" t="n">
-        <v>34.2981</v>
+        <v>34.8489</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5538</v>
+        <v>0.5165</v>
       </c>
       <c r="J43" t="n">
-        <v>14.9526</v>
+        <v>13.9455</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.04</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J44" t="n">
-        <v>4.0203</v>
+        <v>3.3507</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1153</v>
+        <v>0.094</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1131</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6142</v>
+        <v>-0.5782</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.5834</v>
+        <v>-15.6114</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.43</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7731</v>
       </c>
       <c r="J47" t="n">
-        <v>22.1157</v>
+        <v>20.8737</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.05</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1587</v>
+        <v>0.1223</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2849</v>
+        <v>3.3021</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2062</v>
+        <v>-0.186</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.5674</v>
+        <v>-5.022</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.314</v>
+        <v>-0.2967</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.478</v>
+        <v>-8.010899999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.64</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3964</v>
+        <v>-0.3853</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.7028</v>
+        <v>-10.4031</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1969</v>
+        <v>1.2116</v>
       </c>
       <c r="J52" t="n">
-        <v>27.5287</v>
+        <v>27.8668</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0626</v>
+        <v>1.0706</v>
       </c>
       <c r="J53" t="n">
-        <v>24.4398</v>
+        <v>24.6238</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.14</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3988</v>
+        <v>0.3663</v>
       </c>
       <c r="J54" t="n">
-        <v>9.1724</v>
+        <v>8.424899999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3244</v>
+        <v>0.2923</v>
       </c>
       <c r="J55" t="n">
-        <v>7.4612</v>
+        <v>6.7229</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1573</v>
+        <v>0.1314</v>
       </c>
       <c r="J56" t="n">
-        <v>3.6179</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0635</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.7434</v>
+        <v>-1.4605</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0635</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.7434</v>
+        <v>-1.4605</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.87</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1696</v>
+        <v>-0.1515</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.9008</v>
+        <v>-3.4845</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.82</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2201</v>
+        <v>-0.2009</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.0623</v>
+        <v>-4.6207</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2881</v>
+        <v>-0.2698</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.6263</v>
+        <v>-6.2054</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.36</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>30.5898</v>
+        <v>29.9744</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4931</v>
+        <v>0.4533</v>
       </c>
       <c r="J63" t="n">
-        <v>16.7654</v>
+        <v>15.4122</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4226</v>
+        <v>0.3829</v>
       </c>
       <c r="J64" t="n">
-        <v>14.3684</v>
+        <v>13.0186</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.13</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3985</v>
+        <v>0.3592</v>
       </c>
       <c r="J65" t="n">
-        <v>13.549</v>
+        <v>12.2128</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8491</v>
+        <v>-0.8307</v>
       </c>
       <c r="J66" t="n">
-        <v>-28.8694</v>
+        <v>-28.2438</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.22</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4752</v>
+        <v>0.4171</v>
       </c>
       <c r="J67" t="n">
-        <v>16.1568</v>
+        <v>14.1814</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2971</v>
+        <v>0.2465</v>
       </c>
       <c r="J68" t="n">
-        <v>10.1014</v>
+        <v>8.381</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.92</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1212</v>
+        <v>-0.1032</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.1208</v>
+        <v>-3.5088</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1882</v>
+        <v>-0.1678</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.3988</v>
+        <v>-5.7052</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3171</v>
+        <v>-0.3</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.7814</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.81</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4549</v>
+        <v>1.4832</v>
       </c>
       <c r="J72" t="n">
-        <v>29.098</v>
+        <v>29.664</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.68</v>
       </c>
       <c r="I73" t="n">
-        <v>1.2955</v>
+        <v>1.3157</v>
       </c>
       <c r="J73" t="n">
-        <v>25.91</v>
+        <v>26.314</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.34</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8004</v>
+        <v>0.7872</v>
       </c>
       <c r="J74" t="n">
-        <v>16.008</v>
+        <v>15.744</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5513</v>
       </c>
       <c r="J75" t="n">
-        <v>11.542</v>
+        <v>11.026</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3729</v>
+        <v>0.3406</v>
       </c>
       <c r="J76" t="n">
-        <v>7.458</v>
+        <v>6.812</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.79</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.2218</v>
+        <v>-0.2069</v>
       </c>
       <c r="J77" t="n">
-        <v>-4.436</v>
+        <v>-4.138</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.68</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3296</v>
+        <v>-0.3183</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.592</v>
+        <v>-6.366</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.63</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3727</v>
+        <v>-0.3622</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.454</v>
+        <v>-7.244</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4249</v>
+        <v>-0.4166</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.497999999999999</v>
+        <v>-8.332000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4425</v>
+        <v>-0.4353</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.85</v>
+        <v>-8.706</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.84</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5076</v>
+        <v>1.54</v>
       </c>
       <c r="J82" t="n">
-        <v>34.6748</v>
+        <v>35.42</v>
       </c>
     </row>
     <row r="83">
@@ -5709,10 +5709,10 @@
         <v>1.41</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9312</v>
       </c>
       <c r="J84" t="n">
-        <v>21.574</v>
+        <v>21.4176</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4326</v>
+        <v>0.4014</v>
       </c>
       <c r="J85" t="n">
-        <v>9.9498</v>
+        <v>9.232200000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.95</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2635</v>
+        <v>-0.2304</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.0605</v>
+        <v>-5.2992</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.84</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1841</v>
+        <v>-0.1686</v>
       </c>
       <c r="J87" t="n">
-        <v>-4.2343</v>
+        <v>-3.8778</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.83</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1948</v>
+        <v>-0.1794</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.4804</v>
+        <v>-4.1262</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.236</v>
+        <v>-0.2209</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.428</v>
+        <v>-5.0807</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3819</v>
+        <v>-0.3696</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.7837</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.52</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4793</v>
+        <v>-0.4752</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.0239</v>
+        <v>-10.9296</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.81</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4545</v>
+        <v>1.4829</v>
       </c>
       <c r="J92" t="n">
-        <v>31.999</v>
+        <v>32.6238</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.56</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1442</v>
+        <v>1.1605</v>
       </c>
       <c r="J93" t="n">
-        <v>25.1724</v>
+        <v>25.531</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.37</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8573</v>
+        <v>0.848</v>
       </c>
       <c r="J94" t="n">
-        <v>18.8606</v>
+        <v>18.656</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.32</v>
       </c>
       <c r="I95" t="n">
-        <v>0.7612</v>
+        <v>0.7456</v>
       </c>
       <c r="J95" t="n">
-        <v>16.7464</v>
+        <v>16.4032</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3966</v>
+        <v>0.3647</v>
       </c>
       <c r="J96" t="n">
-        <v>8.725199999999999</v>
+        <v>8.023400000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0598</v>
       </c>
       <c r="J97" t="n">
-        <v>1.3904</v>
+        <v>1.3156</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.88</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1428</v>
+        <v>-0.1274</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.1416</v>
+        <v>-2.8028</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.321</v>
+        <v>-0.306</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.062</v>
+        <v>-6.732</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.6</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4108</v>
+        <v>-0.4003</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.037599999999999</v>
+        <v>-8.8066</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.52</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4814</v>
+        <v>-0.4778</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.5908</v>
+        <v>-10.5116</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.26</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4359</v>
+        <v>0.4432</v>
       </c>
       <c r="J102" t="n">
-        <v>12.2052</v>
+        <v>12.4096</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.97</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0522</v>
+        <v>-0.042</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.4616</v>
+        <v>-1.176</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.85</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1935</v>
+        <v>-0.1738</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.418</v>
+        <v>-4.8664</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.84</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2038</v>
+        <v>-0.1839</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.7064</v>
+        <v>-5.1492</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.394</v>
+        <v>-0.3824</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.032</v>
+        <v>-10.7072</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.5</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5785</v>
+        <v>0.5429</v>
       </c>
       <c r="J107" t="n">
-        <v>16.198</v>
+        <v>15.2012</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.26</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3697</v>
+        <v>0.31</v>
       </c>
       <c r="J108" t="n">
-        <v>10.3516</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.23</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3351</v>
+        <v>0.2785</v>
       </c>
       <c r="J109" t="n">
-        <v>9.3828</v>
+        <v>7.798</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.03</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0587</v>
+        <v>0.0417</v>
       </c>
       <c r="J110" t="n">
-        <v>1.6436</v>
+        <v>1.1676</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.9</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1621</v>
+        <v>-0.1425</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.5388</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.43</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8677</v>
+        <v>0.8521</v>
       </c>
       <c r="J112" t="n">
-        <v>25.1633</v>
+        <v>24.7109</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.41</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8391</v>
+        <v>0.8232</v>
       </c>
       <c r="J113" t="n">
-        <v>24.3339</v>
+        <v>23.8728</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1447</v>
+        <v>0.1205</v>
       </c>
       <c r="J114" t="n">
-        <v>4.1963</v>
+        <v>3.4945</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.01</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0333</v>
+        <v>0.0233</v>
       </c>
       <c r="J115" t="n">
-        <v>0.9657</v>
+        <v>0.6757</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.346</v>
+        <v>-0.3045</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.034</v>
+        <v>-8.830500000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.17</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3888</v>
+        <v>0.333</v>
       </c>
       <c r="J117" t="n">
-        <v>11.2752</v>
+        <v>9.657</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2778</v>
+        <v>0.2288</v>
       </c>
       <c r="J118" t="n">
-        <v>8.0562</v>
+        <v>6.6352</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.05</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1527</v>
+        <v>0.1174</v>
       </c>
       <c r="J119" t="n">
-        <v>4.4283</v>
+        <v>3.4046</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.84</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2092</v>
+        <v>-0.1887</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.0668</v>
+        <v>-5.4723</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.68</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3633</v>
+        <v>-0.3495</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.5357</v>
+        <v>-10.1355</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.38</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8051</v>
+        <v>0.789</v>
       </c>
       <c r="J122" t="n">
-        <v>22.5428</v>
+        <v>22.092</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4189</v>
+        <v>0.3812</v>
       </c>
       <c r="J123" t="n">
-        <v>11.7292</v>
+        <v>10.6736</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2424</v>
+        <v>0.2102</v>
       </c>
       <c r="J124" t="n">
-        <v>6.7872</v>
+        <v>5.8856</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2424</v>
+        <v>0.2102</v>
       </c>
       <c r="J125" t="n">
-        <v>6.7872</v>
+        <v>5.8856</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.92</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3102</v>
+        <v>-0.2689</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.685600000000001</v>
+        <v>-7.5292</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4956</v>
+        <v>0.4578</v>
       </c>
       <c r="J127" t="n">
-        <v>13.8768</v>
+        <v>12.8184</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.01</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0506</v>
+        <v>0.0339</v>
       </c>
       <c r="J128" t="n">
-        <v>1.4168</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0506</v>
+        <v>0.0339</v>
       </c>
       <c r="J129" t="n">
-        <v>1.4168</v>
+        <v>0.9492</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1194</v>
+        <v>-0.102</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.3432</v>
+        <v>-2.856</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.55</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4761</v>
+        <v>-0.4739</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.3308</v>
+        <v>-13.2692</v>
       </c>
     </row>
     <row r="132">
@@ -7669,10 +7669,10 @@
         <v>1.4</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8077</v>
+        <v>0.7932</v>
       </c>
       <c r="J133" t="n">
-        <v>21.0002</v>
+        <v>20.6232</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4628</v>
+        <v>0.4393</v>
       </c>
       <c r="J134" t="n">
-        <v>12.0328</v>
+        <v>11.4218</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2473</v>
+        <v>0.2171</v>
       </c>
       <c r="J135" t="n">
-        <v>6.4298</v>
+        <v>5.6446</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.9</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3897</v>
+        <v>-0.35</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.1322</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.97</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0376</v>
+        <v>-0.0283</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.9776</v>
+        <v>-0.7358</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.96</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0527</v>
+        <v>-0.0419</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.3702</v>
+        <v>-1.0894</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.82</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2155</v>
+        <v>-0.1982</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.603</v>
+        <v>-5.1532</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.73</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3002</v>
+        <v>-0.2831</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.8052</v>
+        <v>-7.3606</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.54</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4712</v>
+        <v>-0.4668</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.2512</v>
+        <v>-12.1368</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2603</v>
+        <v>-0.247</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.4663</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.75</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2603</v>
+        <v>-0.247</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.4663</v>
+        <v>-5.187</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.61</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3885</v>
+        <v>-0.379</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.1585</v>
+        <v>-7.959</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.432</v>
+        <v>-0.4244</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.071999999999999</v>
+        <v>-8.9124</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4936</v>
+        <v>-0.491</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.3656</v>
+        <v>-10.311</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.04</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9115</v>
+        <v>0.8542</v>
       </c>
       <c r="J147" t="n">
-        <v>19.1415</v>
+        <v>17.9382</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.52</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5676</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>11.9196</v>
+        <v>11.2518</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.41</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4894</v>
+        <v>0.4453</v>
       </c>
       <c r="J149" t="n">
-        <v>10.2774</v>
+        <v>9.3513</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.4</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4819</v>
+        <v>0.4357</v>
       </c>
       <c r="J150" t="n">
-        <v>10.1199</v>
+        <v>9.149699999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.12</v>
       </c>
       <c r="I151" t="n">
-        <v>0.173</v>
+        <v>0.1359</v>
       </c>
       <c r="J151" t="n">
-        <v>3.633</v>
+        <v>2.8539</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.47</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9052</v>
+        <v>0.8907</v>
       </c>
       <c r="J152" t="n">
-        <v>22.63</v>
+        <v>22.2675</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6201</v>
+        <v>0.6112</v>
       </c>
       <c r="J153" t="n">
-        <v>15.5025</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.25</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5907</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>14.7675</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5289</v>
+        <v>0.523</v>
       </c>
       <c r="J155" t="n">
-        <v>13.2225</v>
+        <v>13.075</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2196</v>
+        <v>0.1904</v>
       </c>
       <c r="J156" t="n">
-        <v>5.49</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.07</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2314</v>
+        <v>0.1896</v>
       </c>
       <c r="J157" t="n">
-        <v>5.785</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.167</v>
+        <v>-0.15</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.175</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1879</v>
+        <v>-0.1703</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.6975</v>
+        <v>-4.2575</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.73</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3034</v>
+        <v>-0.286</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.585</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3769</v>
+        <v>-0.3636</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.422499999999999</v>
+        <v>-9.09</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4752</v>
+        <v>0.4847</v>
       </c>
       <c r="J162" t="n">
-        <v>13.7808</v>
+        <v>14.0563</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.92</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.4191</v>
+        <v>-2.9348</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.86</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.3302</v>
+        <v>-4.756</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2742</v>
+        <v>-0.2551</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.9518</v>
+        <v>-7.3979</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2838</v>
+        <v>-0.265</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.2302</v>
+        <v>-7.685</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.38</v>
       </c>
       <c r="I167" t="n">
-        <v>0.508</v>
+        <v>0.4393</v>
       </c>
       <c r="J167" t="n">
-        <v>14.732</v>
+        <v>12.7397</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4309</v>
+        <v>0.3661</v>
       </c>
       <c r="J168" t="n">
-        <v>12.4961</v>
+        <v>10.6169</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.07</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1306</v>
+        <v>0.0998</v>
       </c>
       <c r="J169" t="n">
-        <v>3.7874</v>
+        <v>2.8942</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0101</v>
+        <v>-0.0077</v>
       </c>
       <c r="J170" t="n">
-        <v>-0.2929</v>
+        <v>-0.2233</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.96</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0839</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.4331</v>
+        <v>-1.9749</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.77</v>
       </c>
       <c r="I172" t="n">
-        <v>1.4063</v>
+        <v>1.4317</v>
       </c>
       <c r="J172" t="n">
-        <v>28.126</v>
+        <v>28.634</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.4</v>
       </c>
       <c r="I173" t="n">
-        <v>0.913</v>
+        <v>0.9077</v>
       </c>
       <c r="J173" t="n">
-        <v>18.26</v>
+        <v>18.154</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.38</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8763</v>
+        <v>0.8682</v>
       </c>
       <c r="J174" t="n">
-        <v>17.526</v>
+        <v>17.364</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8575</v>
+        <v>0.8482</v>
       </c>
       <c r="J175" t="n">
-        <v>17.15</v>
+        <v>16.964</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.28</v>
       </c>
       <c r="I176" t="n">
-        <v>0.6815</v>
+        <v>0.661</v>
       </c>
       <c r="J176" t="n">
-        <v>13.63</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.03</v>
       </c>
       <c r="I177" t="n">
-        <v>0.2107</v>
+        <v>0.1942</v>
       </c>
       <c r="J177" t="n">
-        <v>4.214</v>
+        <v>3.884</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.86</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1488</v>
+        <v>-0.1317</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.976</v>
+        <v>-2.634</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.63</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3744</v>
+        <v>-0.3633</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.488</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.54</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4535</v>
+        <v>-0.447</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.07</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.24</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7149</v>
+        <v>-0.7494</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.298</v>
+        <v>-14.988</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9597</v>
+        <v>0.9513</v>
       </c>
       <c r="J182" t="n">
-        <v>25.9119</v>
+        <v>25.6851</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.14</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4351</v>
+        <v>0.3929</v>
       </c>
       <c r="J183" t="n">
-        <v>11.7477</v>
+        <v>10.6083</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.03</v>
       </c>
       <c r="I184" t="n">
-        <v>0.131</v>
+        <v>0.1054</v>
       </c>
       <c r="J184" t="n">
-        <v>3.537</v>
+        <v>2.8458</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.89</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3755</v>
+        <v>-0.3326</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.1385</v>
+        <v>-8.9802</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7298</v>
+        <v>-0.6993</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.7046</v>
+        <v>-18.8811</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5209</v>
+        <v>0.4622</v>
       </c>
       <c r="J187" t="n">
-        <v>14.0643</v>
+        <v>12.4794</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.23</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4579</v>
+        <v>0.4011</v>
       </c>
       <c r="J188" t="n">
-        <v>12.3633</v>
+        <v>10.8297</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2175</v>
+        <v>0.1786</v>
       </c>
       <c r="J189" t="n">
-        <v>5.8725</v>
+        <v>4.8222</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1337</v>
+        <v>0.1054</v>
       </c>
       <c r="J190" t="n">
-        <v>3.6099</v>
+        <v>2.8458</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.02</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0588</v>
+        <v>0.043</v>
       </c>
       <c r="J191" t="n">
-        <v>1.5876</v>
+        <v>1.161</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.53</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1548</v>
+        <v>1.1685</v>
       </c>
       <c r="J192" t="n">
-        <v>31.1796</v>
+        <v>31.5495</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.46</v>
       </c>
       <c r="I193" t="n">
-        <v>1.0568</v>
+        <v>1.0633</v>
       </c>
       <c r="J193" t="n">
-        <v>28.5336</v>
+        <v>28.7091</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4613</v>
+        <v>0.4246</v>
       </c>
       <c r="J194" t="n">
-        <v>12.4551</v>
+        <v>11.4642</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.88</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4252</v>
+        <v>-0.3834</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.4804</v>
+        <v>-10.3518</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.77</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6865</v>
+        <v>-0.6556</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.5355</v>
+        <v>-17.7012</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.07</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2198</v>
+        <v>0.1773</v>
       </c>
       <c r="J197" t="n">
-        <v>5.9346</v>
+        <v>4.7871</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1246</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>3.3642</v>
+        <v>2.5461</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.82</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2205</v>
+        <v>-0.2012</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.9535</v>
+        <v>-5.4324</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.279</v>
+        <v>-0.2603</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.533</v>
+        <v>-7.0281</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3537</v>
+        <v>-0.3387</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.549899999999999</v>
+        <v>-9.1449</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.5</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0996</v>
+        <v>1.1108</v>
       </c>
       <c r="J202" t="n">
-        <v>27.49</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8481</v>
+        <v>0.8278</v>
       </c>
       <c r="J203" t="n">
-        <v>21.2025</v>
+        <v>20.695</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.35</v>
       </c>
       <c r="I204" t="n">
-        <v>0.8481</v>
+        <v>0.8278</v>
       </c>
       <c r="J204" t="n">
-        <v>21.2025</v>
+        <v>20.695</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0374</v>
+        <v>-0.0319</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.7975</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.357</v>
+        <v>-0.3167</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.925000000000001</v>
+        <v>-7.9175</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.05</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1595</v>
+        <v>0.123</v>
       </c>
       <c r="J207" t="n">
-        <v>3.9875</v>
+        <v>3.075</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.03</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1106</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>2.765</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.99</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0208</v>
+        <v>-0.0155</v>
       </c>
       <c r="J209" t="n">
-        <v>-0.52</v>
+        <v>-0.3875</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.9075</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.4025</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.45</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9426</v>
+        <v>0.9335</v>
       </c>
       <c r="J212" t="n">
-        <v>37.704</v>
+        <v>37.34</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4416</v>
+        <v>0.4025</v>
       </c>
       <c r="J213" t="n">
-        <v>17.664</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.83</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5163</v>
+        <v>-0.4745</v>
       </c>
       <c r="J214" t="n">
-        <v>-20.652</v>
+        <v>-18.98</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.79</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6096</v>
+        <v>-0.5712</v>
       </c>
       <c r="J215" t="n">
-        <v>-24.384</v>
+        <v>-22.848</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.77</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6549</v>
+        <v>-0.6189</v>
       </c>
       <c r="J216" t="n">
-        <v>-26.196</v>
+        <v>-24.756</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.26</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4891</v>
+        <v>0.4484</v>
       </c>
       <c r="J217" t="n">
-        <v>19.564</v>
+        <v>17.936</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.16</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3439</v>
+        <v>0.2931</v>
       </c>
       <c r="J218" t="n">
-        <v>13.756</v>
+        <v>11.724</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.15</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3268</v>
+        <v>0.2772</v>
       </c>
       <c r="J219" t="n">
-        <v>13.072</v>
+        <v>11.088</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.07</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1783</v>
+        <v>0.1438</v>
       </c>
       <c r="J220" t="n">
-        <v>7.132</v>
+        <v>5.752</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.97</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0534</v>
       </c>
       <c r="J221" t="n">
-        <v>-2.704</v>
+        <v>-2.136</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.25</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4114</v>
+        <v>0.4108</v>
       </c>
       <c r="J222" t="n">
-        <v>12.342</v>
+        <v>12.324</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.02</v>
       </c>
       <c r="I223" t="n">
-        <v>0.0608</v>
+        <v>0.0485</v>
       </c>
       <c r="J223" t="n">
-        <v>1.824</v>
+        <v>1.455</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.121</v>
+        <v>-0.1031</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.63</v>
+        <v>-3.093</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1986</v>
+        <v>-0.1781</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.958</v>
+        <v>-5.343</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.8</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.485</v>
+        <v>-6.885</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.41</v>
       </c>
       <c r="I227" t="n">
-        <v>0.524</v>
+        <v>0.4838</v>
       </c>
       <c r="J227" t="n">
-        <v>15.72</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.18</v>
+        <v>0.1396</v>
       </c>
       <c r="J228" t="n">
-        <v>5.4</v>
+        <v>4.188</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.07</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1362</v>
+        <v>0.103</v>
       </c>
       <c r="J229" t="n">
-        <v>4.086</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.04</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0877</v>
+        <v>0.0639</v>
       </c>
       <c r="J230" t="n">
-        <v>2.631</v>
+        <v>1.917</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.72</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.335</v>
+        <v>-0.3198</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.05</v>
+        <v>-9.593999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.53</v>
       </c>
       <c r="I232" t="n">
-        <v>1.0336</v>
+        <v>1.0257</v>
       </c>
       <c r="J232" t="n">
-        <v>27.9072</v>
+        <v>27.6939</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.28</v>
       </c>
       <c r="I233" t="n">
-        <v>0.664</v>
+        <v>0.6492</v>
       </c>
       <c r="J233" t="n">
-        <v>17.928</v>
+        <v>17.5284</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.15</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4473</v>
+        <v>0.411</v>
       </c>
       <c r="J234" t="n">
-        <v>12.0771</v>
+        <v>11.097</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.82</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5547</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J235" t="n">
-        <v>-14.9769</v>
+        <v>-13.8942</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.1098</v>
+        <v>-1.1228</v>
       </c>
       <c r="J236" t="n">
-        <v>-29.9646</v>
+        <v>-30.3156</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.32</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5828</v>
+        <v>0.5566</v>
       </c>
       <c r="J237" t="n">
-        <v>15.7356</v>
+        <v>15.0282</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.12</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2941</v>
+        <v>0.2438</v>
       </c>
       <c r="J238" t="n">
-        <v>7.9407</v>
+        <v>6.5826</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1456</v>
+        <v>-0.1261</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.9312</v>
+        <v>-3.4047</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.251</v>
+        <v>-0.231</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.777</v>
+        <v>-6.237</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.78</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2706</v>
+        <v>-0.2513</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3062</v>
+        <v>-6.7851</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.05</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1712</v>
+        <v>0.1338</v>
       </c>
       <c r="J242" t="n">
-        <v>4.6224</v>
+        <v>3.6126</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.95</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0776</v>
+        <v>-0.065</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.0952</v>
+        <v>-1.755</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.83</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2115</v>
+        <v>-0.192</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.7105</v>
+        <v>-5.184</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2315</v>
+        <v>-0.212</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.2505</v>
+        <v>-5.724</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.78</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.261</v>
+        <v>-0.2417</v>
       </c>
       <c r="J246" t="n">
-        <v>-7.047</v>
+        <v>-6.5259</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.35</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7508</v>
+        <v>0.7352</v>
       </c>
       <c r="J247" t="n">
-        <v>20.2716</v>
+        <v>19.8504</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.34</v>
       </c>
       <c r="I248" t="n">
-        <v>0.736</v>
+        <v>0.7206</v>
       </c>
       <c r="J248" t="n">
-        <v>19.872</v>
+        <v>19.4562</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.12</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3663</v>
+        <v>0.3311</v>
       </c>
       <c r="J249" t="n">
-        <v>9.8901</v>
+        <v>8.9397</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.12</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3663</v>
+        <v>0.3311</v>
       </c>
       <c r="J250" t="n">
-        <v>9.8901</v>
+        <v>8.9397</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.9</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3741</v>
+        <v>-0.3324</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1007</v>
+        <v>-8.9748</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.12</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2164</v>
+        <v>0.1697</v>
       </c>
       <c r="J252" t="n">
-        <v>6.492</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.11</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2023</v>
+        <v>0.1574</v>
       </c>
       <c r="J253" t="n">
-        <v>6.069</v>
+        <v>4.722</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.1</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1879</v>
+        <v>0.145</v>
       </c>
       <c r="J254" t="n">
-        <v>5.637</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0581</v>
+        <v>-0.0456</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.743</v>
+        <v>-1.368</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3567</v>
+        <v>-0.3426</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.701</v>
+        <v>-10.278</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4993</v>
+        <v>0.5258</v>
       </c>
       <c r="J257" t="n">
-        <v>14.979</v>
+        <v>15.774</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.15</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2657</v>
+        <v>0.2518</v>
       </c>
       <c r="J258" t="n">
-        <v>7.971</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1461</v>
+        <v>0.1303</v>
       </c>
       <c r="J259" t="n">
-        <v>4.383</v>
+        <v>3.909</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.86</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1941</v>
+        <v>-0.1734</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.823</v>
+        <v>-5.202</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.75</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3041</v>
+        <v>-0.2867</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.122999999999999</v>
+        <v>-8.601000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.01</v>
       </c>
       <c r="I262" t="n">
-        <v>0.063</v>
+        <v>0.0442</v>
       </c>
       <c r="J262" t="n">
-        <v>1.764</v>
+        <v>1.2376</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.93</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J263" t="n">
-        <v>-2.8924</v>
+        <v>-2.4808</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.92</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1154</v>
+        <v>-0.0998</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.2312</v>
+        <v>-2.7944</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.79</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2512</v>
+        <v>-0.2318</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.0336</v>
+        <v>-6.4904</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2706</v>
+        <v>-0.2516</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.5768</v>
+        <v>-7.0448</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0085</v>
+        <v>0.9968</v>
       </c>
       <c r="J267" t="n">
-        <v>28.238</v>
+        <v>27.9104</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.27</v>
       </c>
       <c r="I268" t="n">
-        <v>0.632</v>
+        <v>0.6193</v>
       </c>
       <c r="J268" t="n">
-        <v>17.696</v>
+        <v>17.3404</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.06</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2071</v>
+        <v>0.1781</v>
       </c>
       <c r="J269" t="n">
-        <v>5.7988</v>
+        <v>4.9868</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.99</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0856</v>
+        <v>-0.0646</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.3968</v>
+        <v>-1.8088</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.93</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2892</v>
+        <v>-0.2492</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.0976</v>
+        <v>-6.9776</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.93</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.0911</v>
+        <v>-0.0775</v>
       </c>
       <c r="J272" t="n">
-        <v>-2.0953</v>
+        <v>-1.7825</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.88</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.1508</v>
+        <v>-0.1352</v>
       </c>
       <c r="J273" t="n">
-        <v>-3.4684</v>
+        <v>-3.1096</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.84</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1939</v>
+        <v>-0.1774</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.4597</v>
+        <v>-4.0802</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3356</v>
+        <v>-0.32</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.7188</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.61</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4079</v>
+        <v>-0.397</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.3817</v>
+        <v>-9.131</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.67</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1575</v>
+        <v>1.1515</v>
       </c>
       <c r="J277" t="n">
-        <v>26.6225</v>
+        <v>26.4845</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.43</v>
       </c>
       <c r="I278" t="n">
-        <v>0.8409</v>
+        <v>0.8276</v>
       </c>
       <c r="J278" t="n">
-        <v>19.3407</v>
+        <v>19.0348</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.3</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6597</v>
+        <v>0.6511</v>
       </c>
       <c r="J279" t="n">
-        <v>15.1731</v>
+        <v>14.9753</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5225</v>
+        <v>0.5177</v>
       </c>
       <c r="J280" t="n">
-        <v>12.0175</v>
+        <v>11.9071</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.97</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.191</v>
+        <v>-0.1616</v>
       </c>
       <c r="J281" t="n">
-        <v>-4.393</v>
+        <v>-3.7168</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0673</v>
+        <v>0.0482</v>
       </c>
       <c r="J282" t="n">
-        <v>2.3555</v>
+        <v>1.687</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.88</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.159</v>
+        <v>-0.1415</v>
       </c>
       <c r="J283" t="n">
-        <v>-5.565</v>
+        <v>-4.9525</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.87</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1695</v>
+        <v>-0.1515</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.9325</v>
+        <v>-5.3025</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1796</v>
+        <v>-0.1613</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.286</v>
+        <v>-5.6455</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.71</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.389</v>
+        <v>-10.8045</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8828</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="J287" t="n">
-        <v>30.898</v>
+        <v>30.359</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.33</v>
       </c>
       <c r="I288" t="n">
-        <v>0.723</v>
+        <v>0.7077</v>
       </c>
       <c r="J288" t="n">
-        <v>25.305</v>
+        <v>24.7695</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.14</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4152</v>
+        <v>0.3793</v>
       </c>
       <c r="J289" t="n">
-        <v>14.532</v>
+        <v>13.2755</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1636</v>
+        <v>-0.1321</v>
       </c>
       <c r="J290" t="n">
-        <v>-5.726</v>
+        <v>-4.6235</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3722</v>
+        <v>-0.3304</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.027</v>
+        <v>-11.564</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.96</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4711</v>
+        <v>1.486</v>
       </c>
       <c r="J292" t="n">
-        <v>29.422</v>
+        <v>29.72</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.82</v>
       </c>
       <c r="I293" t="n">
-        <v>1.3064</v>
+        <v>1.3099</v>
       </c>
       <c r="J293" t="n">
-        <v>26.128</v>
+        <v>26.198</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.59</v>
       </c>
       <c r="I294" t="n">
-        <v>1.0266</v>
+        <v>1.0201</v>
       </c>
       <c r="J294" t="n">
-        <v>20.532</v>
+        <v>20.402</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.15</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3857</v>
+        <v>0.3528</v>
       </c>
       <c r="J295" t="n">
-        <v>7.714</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.07</v>
       </c>
       <c r="I296" t="n">
-        <v>0.1794</v>
+        <v>0.1467</v>
       </c>
       <c r="J296" t="n">
-        <v>3.588</v>
+        <v>2.934</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.0091</v>
+        <v>0.0385</v>
       </c>
       <c r="J297" t="n">
-        <v>-0.182</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.68</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3125</v>
+        <v>-0.3021</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.25</v>
+        <v>-6.042</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.41</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.5527</v>
+        <v>-0.5569</v>
       </c>
       <c r="J299" t="n">
-        <v>-11.054</v>
+        <v>-11.138</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.38</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5794</v>
+        <v>-0.5871</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.588</v>
+        <v>-11.742</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.37</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5883</v>
+        <v>-0.5974</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.766</v>
+        <v>-11.948</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.66</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1883</v>
+        <v>1.1874</v>
       </c>
       <c r="J302" t="n">
-        <v>32.0841</v>
+        <v>32.0598</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4371</v>
+        <v>0.4026</v>
       </c>
       <c r="J303" t="n">
-        <v>11.8017</v>
+        <v>10.8702</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.07</v>
       </c>
       <c r="I304" t="n">
-        <v>0.2383</v>
+        <v>0.2071</v>
       </c>
       <c r="J304" t="n">
-        <v>6.4341</v>
+        <v>5.5917</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.95</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2268</v>
+        <v>-0.1898</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.1236</v>
+        <v>-5.1246</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.88</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4219</v>
+        <v>-0.3798</v>
       </c>
       <c r="J306" t="n">
-        <v>-11.3913</v>
+        <v>-10.2546</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.23</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4868</v>
+        <v>0.4466</v>
       </c>
       <c r="J307" t="n">
-        <v>13.1436</v>
+        <v>12.0582</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.0842</v>
+        <v>0.0601</v>
       </c>
       <c r="J308" t="n">
-        <v>2.2734</v>
+        <v>1.6227</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.95</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0818</v>
+        <v>-0.0679</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.2086</v>
+        <v>-1.8333</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.79</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2557</v>
+        <v>-0.236</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.9039</v>
+        <v>-6.372</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.66</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3777</v>
+        <v>-0.3648</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.1979</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.37</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7801</v>
+        <v>0.7642</v>
       </c>
       <c r="J312" t="n">
-        <v>23.403</v>
+        <v>22.926</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.25</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5995</v>
+        <v>0.5886</v>
       </c>
       <c r="J313" t="n">
-        <v>17.985</v>
+        <v>17.658</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.23</v>
       </c>
       <c r="I314" t="n">
-        <v>0.5681</v>
+        <v>0.5589</v>
       </c>
       <c r="J314" t="n">
-        <v>17.043</v>
+        <v>16.767</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.11</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3413</v>
+        <v>0.3067</v>
       </c>
       <c r="J315" t="n">
-        <v>10.239</v>
+        <v>9.201000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.87</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4517</v>
+        <v>-0.4103</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.551</v>
+        <v>-12.309</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.26</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5201</v>
+        <v>0.49</v>
       </c>
       <c r="J317" t="n">
-        <v>15.603</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.19</v>
       </c>
       <c r="I318" t="n">
-        <v>0.4284</v>
+        <v>0.3735</v>
       </c>
       <c r="J318" t="n">
-        <v>12.852</v>
+        <v>11.205</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.89</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J319" t="n">
-        <v>-4.608</v>
+        <v>-4.032</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.71</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3335</v>
+        <v>-0.3173</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.005</v>
+        <v>-9.519</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.68</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3611</v>
+        <v>-0.3469</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.833</v>
+        <v>-10.407</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.45</v>
       </c>
       <c r="I322" t="n">
-        <v>0.9035</v>
+        <v>0.8888</v>
       </c>
       <c r="J322" t="n">
-        <v>26.2015</v>
+        <v>25.7752</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.23</v>
       </c>
       <c r="I323" t="n">
-        <v>0.5735</v>
+        <v>0.5629</v>
       </c>
       <c r="J323" t="n">
-        <v>16.6315</v>
+        <v>16.3241</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.11</v>
       </c>
       <c r="I324" t="n">
-        <v>0.3465</v>
+        <v>0.3101</v>
       </c>
       <c r="J324" t="n">
-        <v>10.0485</v>
+        <v>8.992900000000001</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1167</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J325" t="n">
-        <v>3.3843</v>
+        <v>2.7608</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.82</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5662</v>
+        <v>-0.5276</v>
       </c>
       <c r="J326" t="n">
-        <v>-16.4198</v>
+        <v>-15.3004</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.22</v>
       </c>
       <c r="I327" t="n">
-        <v>0.4689</v>
+        <v>0.4218</v>
       </c>
       <c r="J327" t="n">
-        <v>13.5981</v>
+        <v>12.2322</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.12</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3007</v>
+        <v>0.2499</v>
       </c>
       <c r="J328" t="n">
-        <v>8.7203</v>
+        <v>7.2471</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.96</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0699</v>
+        <v>-0.0568</v>
       </c>
       <c r="J329" t="n">
-        <v>-2.0271</v>
+        <v>-1.6472</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.74</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3062</v>
+        <v>-0.2884</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.879799999999999</v>
+        <v>-8.3636</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.73</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3156</v>
+        <v>-0.2983</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.1524</v>
+        <v>-8.650700000000001</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.54</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9954</v>
+        <v>0.9829</v>
       </c>
       <c r="J332" t="n">
-        <v>25.8804</v>
+        <v>25.5554</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.27</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6188</v>
+        <v>0.6107</v>
       </c>
       <c r="J333" t="n">
-        <v>16.0888</v>
+        <v>15.8782</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.27</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6188</v>
+        <v>0.6107</v>
       </c>
       <c r="J334" t="n">
-        <v>16.0888</v>
+        <v>15.8782</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.16</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4415</v>
+        <v>0.4132</v>
       </c>
       <c r="J335" t="n">
-        <v>11.479</v>
+        <v>10.7432</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>1.15</v>
       </c>
       <c r="I336" t="n">
-        <v>0.4207</v>
+        <v>0.3895</v>
       </c>
       <c r="J336" t="n">
-        <v>10.9382</v>
+        <v>10.127</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.02</v>
       </c>
       <c r="I337" t="n">
-        <v>0.0965</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J337" t="n">
-        <v>2.509</v>
+        <v>1.846</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.96</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0516</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.6302</v>
+        <v>-1.3416</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1903</v>
+        <v>-0.1715</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.9478</v>
+        <v>-4.459</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.1903</v>
+        <v>-0.1715</v>
       </c>
       <c r="J340" t="n">
-        <v>-4.9478</v>
+        <v>-4.459</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3447</v>
+        <v>-0.3292</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.962199999999999</v>
+        <v>-8.559200000000001</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.64</v>
       </c>
       <c r="I342" t="n">
-        <v>1.1214</v>
+        <v>1.1136</v>
       </c>
       <c r="J342" t="n">
-        <v>25.7922</v>
+        <v>25.6128</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.62</v>
       </c>
       <c r="I343" t="n">
-        <v>1.0956</v>
+        <v>1.0866</v>
       </c>
       <c r="J343" t="n">
-        <v>25.1988</v>
+        <v>24.9918</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.35</v>
       </c>
       <c r="I344" t="n">
-        <v>0.7311</v>
+        <v>0.7195</v>
       </c>
       <c r="J344" t="n">
-        <v>16.8153</v>
+        <v>16.5485</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.21</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5238</v>
+        <v>0.5189</v>
       </c>
       <c r="J345" t="n">
-        <v>12.0474</v>
+        <v>11.9347</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.7</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.86</v>
+        <v>-0.8488</v>
       </c>
       <c r="J346" t="n">
-        <v>-19.78</v>
+        <v>-19.5224</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.98</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.0235</v>
+        <v>-0.0162</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.5405</v>
+        <v>-0.3726</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.87</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1651</v>
+        <v>-0.1487</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.7973</v>
+        <v>-3.4201</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.84</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1966</v>
+        <v>-0.1793</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.5218</v>
+        <v>-4.1239</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.78</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2544</v>
+        <v>-0.2363</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.8512</v>
+        <v>-5.4349</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.61</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4108</v>
+        <v>-0.4002</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.448399999999999</v>
+        <v>-9.204599999999999</v>
       </c>
     </row>
   </sheetData>
